--- a/superwood-datacenter-investor/analyses/materials-mass-and-replacement.xlsx
+++ b/superwood-datacenter-investor/analyses/materials-mass-and-replacement.xlsx
@@ -689,7 +689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -1439,14 +1439,14 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Share of all concrete that is foundations, footings, piers and equipment pads</t>
+          <t>Share of IT mass that is server and equipment enclosures (boxes), replaceable long term</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
         <v>0.4</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1455,26 +1455,26 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>estimated [L]</t>
+          <t>estimated [L]; Alex 2026-09-04</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Remainder is slab on grade, paving and yard</t>
+          <t>Server boxes eventually; the electronics never</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Long-term technical potential: share of slab-on-grade and paving concrete replaceable</t>
+          <t>Share of all concrete that is foundations, footings, piers and equipment pads</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1483,26 +1483,26 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>asserted-internal (Alex, 2026-09-01) [L]</t>
+          <t>estimated [L]</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Technical potential, not a plan; no design or code pathway yet</t>
+          <t>Remainder is slab on grade, paving and yard</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Long-term technical potential: share of foundations, footings, piers and pads replaceable</t>
+          <t>Long-term technical potential: share of slab-on-grade and paving concrete replaceable</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1516,53 +1516,53 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Technical potential, not a plan</t>
+          <t>Technical potential, not a plan; no design or code pathway yet</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>kg SUPERWOOD per kg of concrete replaced</t>
+          <t>Long-term technical potential: share of foundations, footings, piers and pads replaceable</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>0.05</v>
+        <v>0.9</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>0.15</v>
+        <v>0.9</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>kg/kg</t>
+          <t>share</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>estimated [L]</t>
+          <t>asserted-internal (Alex, 2026-09-01) [L]</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lightweight insulated wood-foundation concept; no design exists yet</t>
+          <t>Technical potential, not a plan</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Ducting, plenums and air-distribution sheet metal</t>
+          <t>kg SUPERWOOD per kg of concrete replaced</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>3</v>
+        <v>0.05</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>8</v>
+        <v>0.15</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>t/MW</t>
+          <t>kg/kg</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1572,82 +1572,86 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Separate from the mechanical-equipment row</t>
+          <t>Lightweight insulated wood-foundation concept; no design exists yet</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Concrete emissions</t>
+          <t>Ducting, plenums and air-distribution sheet metal</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>0.12</v>
+        <v>3</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>0.12</v>
+        <v>8</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>kg CO₂e/kg</t>
+          <t>t/MW</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>industry range [M]</t>
+          <t>estimated [L]</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ready-mix, cradle to gate; typical 0.10–0.15</t>
+          <t>Separate from the mechanical-equipment row</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SUPERWOOD average board thickness</t>
+          <t>Concrete emissions</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>7.2</v>
+        <v>0.12</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>7.2</v>
+        <v>0.12</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>kg CO₂e/kg</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>internal TEM basis [H]</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
+          <t>industry range [M]</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Ready-mix, cradle to gate; typical 0.10–0.15</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SUPERWOOD density</t>
+          <t>SUPERWOOD average board thickness</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>1300</v>
+        <v>7.2</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>1300</v>
+        <v>7.2</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>kg/m³</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>internal TEM [H]</t>
+          <t>internal TEM basis [H]</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -1655,23 +1659,23 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SuperMill One output</t>
+          <t>SUPERWOOD density</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>1000000</v>
+        <v>1300</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>1000000</v>
+        <v>1300</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>sf/yr</t>
+          <t>kg/m³</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>internal [H]</t>
+          <t>internal TEM [H]</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -1679,14 +1683,14 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SuperMill Two output</t>
+          <t>SuperMill One output</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>36000000</v>
+        <v>1000000</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>36000000</v>
+        <v>1000000</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1703,46 +1707,42 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Structural substitution: kg SUPERWOOD per kg steel replaced</t>
+          <t>SuperMill Two output</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>0.3</v>
+        <v>36000000</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>0.6</v>
+        <v>36000000</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>kg/kg</t>
+          <t>sf/yr</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>estimated [L]</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Engineering-stamped per element (Fast + Epp) before external use</t>
-        </is>
-      </c>
+          <t>internal [H]</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SUPERWOOD in a hybrid wall panel replacing precast</t>
+          <t>Structural substitution: kg SUPERWOOD per kg steel replaced</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>20</v>
+        <v>0.3</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>40</v>
+        <v>0.6</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>kg/m²</t>
+          <t>kg/kg</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1752,25 +1752,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Panel design unsettled</t>
+          <t>Engineering-stamped per element (Fast + Epp) before external use</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Addressable share of other tray / containment / doors (medium term)</t>
+          <t>SUPERWOOD in a hybrid wall panel replacing precast</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>0.5</v>
+        <v>20</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>0.5</v>
+        <v>40</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>share</t>
+          <t>kg/m²</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1778,71 +1778,75 @@
           <t>estimated [L]</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Panel design unsettled</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Count rebar as addressable in the long term? (0/1)</t>
+          <t>Addressable share of other tray / containment / doors (medium term)</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>flag</t>
+          <t>share</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>choice</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Rebar is a frontier market with no pathway; off by default</t>
-        </is>
-      </c>
+          <t>estimated [L]</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Steel emissions, global average (BF-BOF)</t>
+          <t>Count rebar as addressable in the long term? (0/1)</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>kg CO₂e/kg</t>
+          <t>flag</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>published-class [M]</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
+          <t>choice</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Rebar is a frontier market with no pathway; off by default</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Steel emissions, recycled (EAF)</t>
+          <t>Steel emissions, global average (BF-BOF)</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1851,7 +1855,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>industry range [M]</t>
+          <t>published-class [M]</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -1859,14 +1863,14 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SUPERWOOD manufacturing emissions</t>
+          <t>Steel emissions, recycled (EAF)</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1875,38 +1879,62 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>internal, pre-LCA [L]</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Canva DCII deck; LCA under way, Prof. Ming Hu, Notre Dame</t>
-        </is>
-      </c>
+          <t>industry range [M]</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>SUPERWOOD manufacturing emissions</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>kg CO₂e/kg</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>internal, pre-LCA [L]</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Canva DCII deck; LCA under way, Prof. Ming Hu, Notre Dame</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>SUPERWOOD biogenic carbon stored</t>
         </is>
       </c>
-      <c r="B46" s="2" t="n">
+      <c r="B47" s="2" t="n">
         <v>1.3</v>
       </c>
-      <c r="C46" s="2" t="n">
+      <c r="C47" s="2" t="n">
         <v>1.3</v>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>kg CO₂e/kg</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>internal, pre-LCA [L]</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Report separately; module C release under EN 15804</t>
         </is>
@@ -2099,20 +2127,20 @@
         </is>
       </c>
       <c r="B3" s="5">
-        <f>Inputs!$B$11*(1-Inputs!$B$29)*Inputs!$B$12*Inputs!$B$2-B5</f>
-        <v>720000.0</v>
+        <f>Inputs!$B$11*(1-Inputs!$B$30)*Inputs!$B$12*Inputs!$B$2-B5</f>
+        <v/>
       </c>
       <c r="C3" s="5">
-        <f>Inputs!$C$11*(1-Inputs!$C$29)*Inputs!$C$12*Inputs!$C$2-C5</f>
-        <v>1200000.0</v>
+        <f>Inputs!$C$11*(1-Inputs!$C$30)*Inputs!$C$12*Inputs!$C$2-C5</f>
+        <v/>
       </c>
       <c r="D3" s="5">
         <f>B3</f>
-        <v>720000.0</v>
+        <v/>
       </c>
       <c r="E3" s="5">
         <f>C3</f>
-        <v>1200000.0</v>
+        <v/>
       </c>
       <c r="F3" s="6" t="n">
         <v>0</v>
@@ -2124,24 +2152,24 @@
         <v>0</v>
       </c>
       <c r="I3" s="6">
-        <f>Inputs!$B$30</f>
-        <v>0.75</v>
+        <f>Inputs!$B$31</f>
+        <v/>
       </c>
       <c r="J3" s="5">
         <f>B3*SUM($F3:$I3)</f>
-        <v>540000.0</v>
+        <v/>
       </c>
       <c r="K3" s="5">
         <f>C3*SUM($F3:$I3)</f>
-        <v>900000.0</v>
+        <v/>
       </c>
       <c r="L3" s="5">
-        <f>J3*Inputs!$B$32</f>
-        <v>27000.0</v>
+        <f>J3*Inputs!$B$33</f>
+        <v/>
       </c>
       <c r="M3" s="5">
-        <f>K3*Inputs!$C$32</f>
-        <v>135000.0</v>
+        <f>K3*Inputs!$C$33</f>
+        <v/>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -2150,39 +2178,39 @@
       </c>
       <c r="O3" s="5">
         <f>C3-K3</f>
-        <v>300000.0</v>
+        <v/>
       </c>
       <c r="P3" s="5">
         <f>IF(SUM($F3:$I3)=0,0,L3*F3/SUM($F3:$I3))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="Q3" s="5">
         <f>IF(SUM($F3:$I3)=0,0,L3*G3/SUM($F3:$I3))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="R3" s="5">
         <f>IF(SUM($F3:$I3)=0,0,L3*H3/SUM($F3:$I3))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="S3" s="5">
         <f>IF(SUM($F3:$I3)=0,0,L3*I3/SUM($F3:$I3))</f>
-        <v>27000.0</v>
+        <v/>
       </c>
       <c r="T3" s="5">
         <f>IF(SUM($F3:$I3)=0,0,M3*F3/SUM($F3:$I3))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="U3" s="5">
         <f>IF(SUM($F3:$I3)=0,0,M3*G3/SUM($F3:$I3))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="V3" s="5">
         <f>IF(SUM($F3:$I3)=0,0,M3*H3/SUM($F3:$I3))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="W3" s="5">
         <f>IF(SUM($F3:$I3)=0,0,M3*I3/SUM($F3:$I3))</f>
-        <v>135000.0</v>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -2192,20 +2220,20 @@
         </is>
       </c>
       <c r="B4" s="5">
-        <f>Inputs!$B$11*Inputs!$B$29*Inputs!$B$12*Inputs!$B$2</f>
-        <v>480000.0</v>
+        <f>Inputs!$B$11*Inputs!$B$30*Inputs!$B$12*Inputs!$B$2</f>
+        <v/>
       </c>
       <c r="C4" s="5">
-        <f>Inputs!$C$11*Inputs!$C$29*Inputs!$C$12*Inputs!$C$2</f>
-        <v>1200000.0</v>
+        <f>Inputs!$C$11*Inputs!$C$30*Inputs!$C$12*Inputs!$C$2</f>
+        <v/>
       </c>
       <c r="D4" s="5">
         <f>D3+B4</f>
-        <v>1200000.0</v>
+        <v/>
       </c>
       <c r="E4" s="5">
         <f>E3+C4</f>
-        <v>2400000.0</v>
+        <v/>
       </c>
       <c r="F4" s="6" t="n">
         <v>0</v>
@@ -2217,24 +2245,24 @@
         <v>0</v>
       </c>
       <c r="I4" s="6">
-        <f>Inputs!$B$31</f>
-        <v>0.9</v>
+        <f>Inputs!$B$32</f>
+        <v/>
       </c>
       <c r="J4" s="5">
         <f>B4*SUM($F4:$I4)</f>
-        <v>432000.0</v>
+        <v/>
       </c>
       <c r="K4" s="5">
         <f>C4*SUM($F4:$I4)</f>
-        <v>1080000.0</v>
+        <v/>
       </c>
       <c r="L4" s="5">
-        <f>J4*Inputs!$B$32</f>
-        <v>21600.0</v>
+        <f>J4*Inputs!$B$33</f>
+        <v/>
       </c>
       <c r="M4" s="5">
-        <f>K4*Inputs!$C$32</f>
-        <v>162000.0</v>
+        <f>K4*Inputs!$C$33</f>
+        <v/>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -2243,39 +2271,39 @@
       </c>
       <c r="O4" s="5">
         <f>C4-K4</f>
-        <v>120000.0</v>
+        <v/>
       </c>
       <c r="P4" s="5">
         <f>IF(SUM($F4:$I4)=0,0,L4*F4/SUM($F4:$I4))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="Q4" s="5">
         <f>IF(SUM($F4:$I4)=0,0,L4*G4/SUM($F4:$I4))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="R4" s="5">
         <f>IF(SUM($F4:$I4)=0,0,L4*H4/SUM($F4:$I4))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="S4" s="5">
         <f>IF(SUM($F4:$I4)=0,0,L4*I4/SUM($F4:$I4))</f>
-        <v>21600.0</v>
+        <v/>
       </c>
       <c r="T4" s="5">
         <f>IF(SUM($F4:$I4)=0,0,M4*F4/SUM($F4:$I4))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="U4" s="5">
         <f>IF(SUM($F4:$I4)=0,0,M4*G4/SUM($F4:$I4))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="V4" s="5">
         <f>IF(SUM($F4:$I4)=0,0,M4*H4/SUM($F4:$I4))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="W4" s="5">
         <f>IF(SUM($F4:$I4)=0,0,M4*I4/SUM($F4:$I4))</f>
-        <v>162000.0</v>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -2286,19 +2314,19 @@
       </c>
       <c r="B5" s="5">
         <f>Inputs!$B$13*Derived!B4*Inputs!$B$14*Inputs!$B$12</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="C5" s="5">
         <f>Inputs!$C$13*Derived!C4*Inputs!$C$14*Inputs!$C$12</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="D5" s="5">
         <f>D4+B5</f>
-        <v>1200000.0</v>
+        <v/>
       </c>
       <c r="E5" s="5">
         <f>E4+C5</f>
-        <v>2400000.0</v>
+        <v/>
       </c>
       <c r="F5" s="6" t="n">
         <v>0</v>
@@ -2314,19 +2342,19 @@
       </c>
       <c r="J5" s="5">
         <f>B5*SUM($F5:$I5)</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="K5" s="5">
         <f>C5*SUM($F5:$I5)</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="L5" s="5">
-        <f>SUM($F5:$I5)*Inputs!$B$13*Derived!B4*Inputs!$B$40/1000</f>
-        <v>0.0</v>
+        <f>SUM($F5:$I5)*Inputs!$B$13*Derived!B4*Inputs!$B$41/1000</f>
+        <v/>
       </c>
       <c r="M5" s="5">
-        <f>SUM($F5:$I5)*Inputs!$C$13*Derived!C4*Inputs!$C$40/1000</f>
-        <v>0.0</v>
+        <f>SUM($F5:$I5)*Inputs!$C$13*Derived!C4*Inputs!$C$41/1000</f>
+        <v/>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -2335,39 +2363,39 @@
       </c>
       <c r="O5" s="5">
         <f>C5-K5</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="P5" s="5">
         <f>IF(SUM($F5:$I5)=0,0,L5*F5/SUM($F5:$I5))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="Q5" s="5">
         <f>IF(SUM($F5:$I5)=0,0,L5*G5/SUM($F5:$I5))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="R5" s="5">
         <f>IF(SUM($F5:$I5)=0,0,L5*H5/SUM($F5:$I5))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="S5" s="5">
         <f>IF(SUM($F5:$I5)=0,0,L5*I5/SUM($F5:$I5))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="T5" s="5">
         <f>IF(SUM($F5:$I5)=0,0,M5*F5/SUM($F5:$I5))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="U5" s="5">
         <f>IF(SUM($F5:$I5)=0,0,M5*G5/SUM($F5:$I5))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="V5" s="5">
         <f>IF(SUM($F5:$I5)=0,0,M5*H5/SUM($F5:$I5))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="W5" s="5">
         <f>IF(SUM($F5:$I5)=0,0,M5*I5/SUM($F5:$I5))</f>
-        <v>0.0</v>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -2378,19 +2406,19 @@
       </c>
       <c r="B6" s="5">
         <f>Inputs!$B$11*Inputs!$B$17/1000*Inputs!$B$2</f>
-        <v>30000.0</v>
+        <v/>
       </c>
       <c r="C6" s="5">
         <f>Inputs!$C$11*Inputs!$C$17/1000*Inputs!$C$2</f>
-        <v>100000.0</v>
+        <v/>
       </c>
       <c r="D6" s="5">
         <f>D5+B6</f>
-        <v>1230000.0</v>
+        <v/>
       </c>
       <c r="E6" s="5">
         <f>E5+C6</f>
-        <v>2500000.0</v>
+        <v/>
       </c>
       <c r="F6" s="6" t="n">
         <v>0</v>
@@ -2402,24 +2430,24 @@
         <v>0</v>
       </c>
       <c r="I6" s="6">
-        <f>Inputs!$B$29*Inputs!$B$31+(1-Inputs!$B$29)*Inputs!$B$30</f>
-        <v>0.81</v>
+        <f>Inputs!$B$30*Inputs!$B$32+(1-Inputs!$B$30)*Inputs!$B$31</f>
+        <v/>
       </c>
       <c r="J6" s="5">
         <f>B6*SUM($F6:$I6)</f>
-        <v>24300.0</v>
+        <v/>
       </c>
       <c r="K6" s="5">
         <f>C6*SUM($F6:$I6)</f>
-        <v>81000.0</v>
+        <v/>
       </c>
       <c r="L6" s="5">
-        <f>J6*Inputs!$B$39</f>
-        <v>7290.0</v>
+        <f>J6*Inputs!$B$40</f>
+        <v/>
       </c>
       <c r="M6" s="5">
-        <f>K6*Inputs!$C$39</f>
-        <v>48600.0</v>
+        <f>K6*Inputs!$C$40</f>
+        <v/>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -2428,39 +2456,39 @@
       </c>
       <c r="O6" s="5">
         <f>C6-K6</f>
-        <v>19000.0</v>
+        <v/>
       </c>
       <c r="P6" s="5">
         <f>IF(SUM($F6:$I6)=0,0,L6*F6/SUM($F6:$I6))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="Q6" s="5">
         <f>IF(SUM($F6:$I6)=0,0,L6*G6/SUM($F6:$I6))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="R6" s="5">
         <f>IF(SUM($F6:$I6)=0,0,L6*H6/SUM($F6:$I6))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="S6" s="5">
         <f>IF(SUM($F6:$I6)=0,0,L6*I6/SUM($F6:$I6))</f>
-        <v>7290.0</v>
+        <v/>
       </c>
       <c r="T6" s="5">
         <f>IF(SUM($F6:$I6)=0,0,M6*F6/SUM($F6:$I6))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="U6" s="5">
         <f>IF(SUM($F6:$I6)=0,0,M6*G6/SUM($F6:$I6))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="V6" s="5">
         <f>IF(SUM($F6:$I6)=0,0,M6*H6/SUM($F6:$I6))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="W6" s="5">
         <f>IF(SUM($F6:$I6)=0,0,M6*I6/SUM($F6:$I6))</f>
-        <v>48600.0</v>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -2471,19 +2499,19 @@
       </c>
       <c r="B7" s="5">
         <f>Inputs!$B$15*(1-Inputs!$B$16)*Inputs!$B$2</f>
-        <v>30000.0</v>
+        <v/>
       </c>
       <c r="C7" s="5">
         <f>Inputs!$C$15*(1-Inputs!$C$16)*Inputs!$C$2</f>
-        <v>40000.0</v>
+        <v/>
       </c>
       <c r="D7" s="5">
         <f>D6+B7</f>
-        <v>1260000.0</v>
+        <v/>
       </c>
       <c r="E7" s="5">
         <f>E6+C7</f>
-        <v>2540000.0</v>
+        <v/>
       </c>
       <c r="F7" s="6" t="n">
         <v>0</v>
@@ -2499,19 +2527,19 @@
       </c>
       <c r="J7" s="5">
         <f>B7*SUM($F7:$I7)</f>
-        <v>30000.0</v>
+        <v/>
       </c>
       <c r="K7" s="5">
         <f>C7*SUM($F7:$I7)</f>
-        <v>40000.0</v>
+        <v/>
       </c>
       <c r="L7" s="5">
-        <f>J7*Inputs!$B$39</f>
-        <v>9000.0</v>
+        <f>J7*Inputs!$B$40</f>
+        <v/>
       </c>
       <c r="M7" s="5">
-        <f>K7*Inputs!$C$39</f>
-        <v>24000.0</v>
+        <f>K7*Inputs!$C$40</f>
+        <v/>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -2520,39 +2548,39 @@
       </c>
       <c r="O7" s="5">
         <f>C7-K7</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="P7" s="5">
         <f>IF(SUM($F7:$I7)=0,0,L7*F7/SUM($F7:$I7))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="Q7" s="5">
         <f>IF(SUM($F7:$I7)=0,0,L7*G7/SUM($F7:$I7))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="R7" s="5">
         <f>IF(SUM($F7:$I7)=0,0,L7*H7/SUM($F7:$I7))</f>
-        <v>9000.0</v>
+        <v/>
       </c>
       <c r="S7" s="5">
         <f>IF(SUM($F7:$I7)=0,0,L7*I7/SUM($F7:$I7))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="T7" s="5">
         <f>IF(SUM($F7:$I7)=0,0,M7*F7/SUM($F7:$I7))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="U7" s="5">
         <f>IF(SUM($F7:$I7)=0,0,M7*G7/SUM($F7:$I7))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="V7" s="5">
         <f>IF(SUM($F7:$I7)=0,0,M7*H7/SUM($F7:$I7))</f>
-        <v>24000.0</v>
+        <v/>
       </c>
       <c r="W7" s="5">
         <f>IF(SUM($F7:$I7)=0,0,M7*I7/SUM($F7:$I7))</f>
-        <v>0.0</v>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -2563,19 +2591,19 @@
       </c>
       <c r="B8" s="5">
         <f>Inputs!$B$15*Inputs!$B$16*Inputs!$B$2</f>
-        <v>20000.0</v>
+        <v/>
       </c>
       <c r="C8" s="5">
         <f>Inputs!$C$15*Inputs!$C$16*Inputs!$C$2</f>
-        <v>60000.0</v>
+        <v/>
       </c>
       <c r="D8" s="5">
         <f>D7+B8</f>
-        <v>1280000.0</v>
+        <v/>
       </c>
       <c r="E8" s="5">
         <f>E7+C8</f>
-        <v>2600000.0</v>
+        <v/>
       </c>
       <c r="F8" s="6" t="n">
         <v>0</v>
@@ -2591,19 +2619,19 @@
       </c>
       <c r="J8" s="5">
         <f>B8*SUM($F8:$I8)</f>
-        <v>20000.0</v>
+        <v/>
       </c>
       <c r="K8" s="5">
         <f>C8*SUM($F8:$I8)</f>
-        <v>60000.0</v>
+        <v/>
       </c>
       <c r="L8" s="5">
-        <f>J8*Inputs!$B$39</f>
-        <v>6000.0</v>
+        <f>J8*Inputs!$B$40</f>
+        <v/>
       </c>
       <c r="M8" s="5">
-        <f>K8*Inputs!$C$39</f>
-        <v>36000.0</v>
+        <f>K8*Inputs!$C$40</f>
+        <v/>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -2612,39 +2640,39 @@
       </c>
       <c r="O8" s="5">
         <f>C8-K8</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="P8" s="5">
         <f>IF(SUM($F8:$I8)=0,0,L8*F8/SUM($F8:$I8))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="Q8" s="5">
         <f>IF(SUM($F8:$I8)=0,0,L8*G8/SUM($F8:$I8))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="R8" s="5">
         <f>IF(SUM($F8:$I8)=0,0,L8*H8/SUM($F8:$I8))</f>
-        <v>6000.0</v>
+        <v/>
       </c>
       <c r="S8" s="5">
         <f>IF(SUM($F8:$I8)=0,0,L8*I8/SUM($F8:$I8))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="T8" s="5">
         <f>IF(SUM($F8:$I8)=0,0,M8*F8/SUM($F8:$I8))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="U8" s="5">
         <f>IF(SUM($F8:$I8)=0,0,M8*G8/SUM($F8:$I8))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="V8" s="5">
         <f>IF(SUM($F8:$I8)=0,0,M8*H8/SUM($F8:$I8))</f>
-        <v>36000.0</v>
+        <v/>
       </c>
       <c r="W8" s="5">
         <f>IF(SUM($F8:$I8)=0,0,M8*I8/SUM($F8:$I8))</f>
-        <v>0.0</v>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -2655,19 +2683,19 @@
       </c>
       <c r="B9" s="5">
         <f>(1-Inputs!$B$13)*Derived!B4*Inputs!$B$19/1000</f>
-        <v>1858.0599999999997</v>
+        <v/>
       </c>
       <c r="C9" s="5">
         <f>(1-Inputs!$C$13)*Derived!C4*Inputs!$C$19/1000</f>
-        <v>7432.239999999999</v>
+        <v/>
       </c>
       <c r="D9" s="5">
         <f>D8+B9</f>
-        <v>1281858.06</v>
+        <v/>
       </c>
       <c r="E9" s="5">
         <f>E8+C9</f>
-        <v>2607432.24</v>
+        <v/>
       </c>
       <c r="F9" s="6" t="n">
         <v>1</v>
@@ -2683,19 +2711,19 @@
       </c>
       <c r="J9" s="5">
         <f>B9*SUM($F9:$I9)</f>
-        <v>1858.0599999999997</v>
+        <v/>
       </c>
       <c r="K9" s="5">
         <f>C9*SUM($F9:$I9)</f>
-        <v>7432.239999999999</v>
+        <v/>
       </c>
       <c r="L9" s="5">
         <f>SUM($F9:$I9)*(1-Inputs!$B$13)*Derived!B3*Derived!B6/1000</f>
-        <v>695.657664</v>
+        <v/>
       </c>
       <c r="M9" s="5">
         <f>SUM($F9:$I9)*(1-Inputs!$C$13)*Derived!C3*Derived!C6/1000</f>
-        <v>1391.315328</v>
+        <v/>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -2704,39 +2732,39 @@
       </c>
       <c r="O9" s="5">
         <f>C9-K9</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="P9" s="5">
         <f>IF(SUM($F9:$I9)=0,0,L9*F9/SUM($F9:$I9))</f>
-        <v>695.657664</v>
+        <v/>
       </c>
       <c r="Q9" s="5">
         <f>IF(SUM($F9:$I9)=0,0,L9*G9/SUM($F9:$I9))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="R9" s="5">
         <f>IF(SUM($F9:$I9)=0,0,L9*H9/SUM($F9:$I9))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="S9" s="5">
         <f>IF(SUM($F9:$I9)=0,0,L9*I9/SUM($F9:$I9))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="T9" s="5">
         <f>IF(SUM($F9:$I9)=0,0,M9*F9/SUM($F9:$I9))</f>
-        <v>1391.315328</v>
+        <v/>
       </c>
       <c r="U9" s="5">
         <f>IF(SUM($F9:$I9)=0,0,M9*G9/SUM($F9:$I9))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="V9" s="5">
         <f>IF(SUM($F9:$I9)=0,0,M9*H9/SUM($F9:$I9))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="W9" s="5">
         <f>IF(SUM($F9:$I9)=0,0,M9*I9/SUM($F9:$I9))</f>
-        <v>0.0</v>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -2747,19 +2775,19 @@
       </c>
       <c r="B10" s="5">
         <f>Inputs!$B$6*0.092903*Inputs!$B$20/1000</f>
-        <v>185.806</v>
+        <v/>
       </c>
       <c r="C10" s="5">
         <f>Inputs!$C$6*0.092903*Inputs!$C$20/1000</f>
-        <v>929.03</v>
+        <v/>
       </c>
       <c r="D10" s="5">
         <f>D9+B10</f>
-        <v>1282043.8660000002</v>
+        <v/>
       </c>
       <c r="E10" s="5">
         <f>E9+C10</f>
-        <v>2608361.27</v>
+        <v/>
       </c>
       <c r="F10" s="6" t="n">
         <v>1</v>
@@ -2775,19 +2803,19 @@
       </c>
       <c r="J10" s="5">
         <f>B10*SUM($F10:$I10)</f>
-        <v>185.806</v>
+        <v/>
       </c>
       <c r="K10" s="5">
         <f>C10*SUM($F10:$I10)</f>
-        <v>929.03</v>
+        <v/>
       </c>
       <c r="L10" s="5">
         <f>SUM($F10:$I10)*Inputs!$B$6*Derived!B6/1000</f>
-        <v>173.914416</v>
+        <v/>
       </c>
       <c r="M10" s="5">
         <f>SUM($F10:$I10)*Inputs!$C$6*Derived!C6/1000</f>
-        <v>434.78603999999996</v>
+        <v/>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -2796,39 +2824,39 @@
       </c>
       <c r="O10" s="5">
         <f>C10-K10</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="P10" s="5">
         <f>IF(SUM($F10:$I10)=0,0,L10*F10/SUM($F10:$I10))</f>
-        <v>173.914416</v>
+        <v/>
       </c>
       <c r="Q10" s="5">
         <f>IF(SUM($F10:$I10)=0,0,L10*G10/SUM($F10:$I10))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="R10" s="5">
         <f>IF(SUM($F10:$I10)=0,0,L10*H10/SUM($F10:$I10))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="S10" s="5">
         <f>IF(SUM($F10:$I10)=0,0,L10*I10/SUM($F10:$I10))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="T10" s="5">
         <f>IF(SUM($F10:$I10)=0,0,M10*F10/SUM($F10:$I10))</f>
-        <v>434.78603999999996</v>
+        <v/>
       </c>
       <c r="U10" s="5">
         <f>IF(SUM($F10:$I10)=0,0,M10*G10/SUM($F10:$I10))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="V10" s="5">
         <f>IF(SUM($F10:$I10)=0,0,M10*H10/SUM($F10:$I10))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="W10" s="5">
         <f>IF(SUM($F10:$I10)=0,0,M10*I10/SUM($F10:$I10))</f>
-        <v>0.0</v>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -2839,19 +2867,19 @@
       </c>
       <c r="B11" s="5">
         <f>Inputs!$B$7*1000*Inputs!$B$21/1000</f>
-        <v>300.0</v>
+        <v/>
       </c>
       <c r="C11" s="5">
         <f>Inputs!$C$7*1000*Inputs!$C$21/1000</f>
-        <v>1000.0</v>
+        <v/>
       </c>
       <c r="D11" s="5">
         <f>D10+B11</f>
-        <v>1282343.8660000002</v>
+        <v/>
       </c>
       <c r="E11" s="5">
         <f>E10+C11</f>
-        <v>2609361.27</v>
+        <v/>
       </c>
       <c r="F11" s="6" t="n">
         <v>1</v>
@@ -2867,19 +2895,19 @@
       </c>
       <c r="J11" s="5">
         <f>B11*SUM($F11:$I11)</f>
-        <v>300.0</v>
+        <v/>
       </c>
       <c r="K11" s="5">
         <f>C11*SUM($F11:$I11)</f>
-        <v>1000.0</v>
+        <v/>
       </c>
       <c r="L11" s="5">
         <f>SUM($F11:$I11)*Derived!B5*Derived!B6/1000</f>
-        <v>233.99999999999997</v>
+        <v/>
       </c>
       <c r="M11" s="5">
         <f>SUM($F11:$I11)*Derived!C5*Derived!C6/1000</f>
-        <v>467.99999999999994</v>
+        <v/>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -2888,39 +2916,39 @@
       </c>
       <c r="O11" s="5">
         <f>C11-K11</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="P11" s="5">
         <f>IF(SUM($F11:$I11)=0,0,L11*F11/SUM($F11:$I11))</f>
-        <v>233.99999999999997</v>
+        <v/>
       </c>
       <c r="Q11" s="5">
         <f>IF(SUM($F11:$I11)=0,0,L11*G11/SUM($F11:$I11))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="R11" s="5">
         <f>IF(SUM($F11:$I11)=0,0,L11*H11/SUM($F11:$I11))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="S11" s="5">
         <f>IF(SUM($F11:$I11)=0,0,L11*I11/SUM($F11:$I11))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="T11" s="5">
         <f>IF(SUM($F11:$I11)=0,0,M11*F11/SUM($F11:$I11))</f>
-        <v>467.99999999999994</v>
+        <v/>
       </c>
       <c r="U11" s="5">
         <f>IF(SUM($F11:$I11)=0,0,M11*G11/SUM($F11:$I11))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="V11" s="5">
         <f>IF(SUM($F11:$I11)=0,0,M11*H11/SUM($F11:$I11))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="W11" s="5">
         <f>IF(SUM($F11:$I11)=0,0,M11*I11/SUM($F11:$I11))</f>
-        <v>0.0</v>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -2955,19 +2983,19 @@
       </c>
       <c r="B13" s="5">
         <f>Inputs!$B$18*Inputs!$B$2</f>
-        <v>5000.0</v>
+        <v/>
       </c>
       <c r="C13" s="5">
         <f>Inputs!$C$18*Inputs!$C$2</f>
-        <v>15000.0</v>
+        <v/>
       </c>
       <c r="D13" s="5">
         <f>D11+B13</f>
-        <v>1287343.8660000002</v>
+        <v/>
       </c>
       <c r="E13" s="5">
         <f>E11+C13</f>
-        <v>2624361.27</v>
+        <v/>
       </c>
       <c r="F13" s="6" t="n">
         <v>0</v>
@@ -2983,19 +3011,19 @@
       </c>
       <c r="J13" s="5">
         <f>B13*SUM($F13:$I13)</f>
-        <v>5000.0</v>
+        <v/>
       </c>
       <c r="K13" s="5">
         <f>C13*SUM($F13:$I13)</f>
-        <v>15000.0</v>
+        <v/>
       </c>
       <c r="L13" s="5">
-        <f>J13*Inputs!$B$39</f>
-        <v>1500.0</v>
+        <f>J13*Inputs!$B$40</f>
+        <v/>
       </c>
       <c r="M13" s="5">
-        <f>K13*Inputs!$C$39</f>
-        <v>9000.0</v>
+        <f>K13*Inputs!$C$40</f>
+        <v/>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -3004,39 +3032,39 @@
       </c>
       <c r="O13" s="5">
         <f>C13-K13</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="P13" s="5">
         <f>IF(SUM($F13:$I13)=0,0,L13*F13/SUM($F13:$I13))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="Q13" s="5">
         <f>IF(SUM($F13:$I13)=0,0,L13*G13/SUM($F13:$I13))</f>
-        <v>1500.0</v>
+        <v/>
       </c>
       <c r="R13" s="5">
         <f>IF(SUM($F13:$I13)=0,0,L13*H13/SUM($F13:$I13))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="S13" s="5">
         <f>IF(SUM($F13:$I13)=0,0,L13*I13/SUM($F13:$I13))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="T13" s="5">
         <f>IF(SUM($F13:$I13)=0,0,M13*F13/SUM($F13:$I13))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="U13" s="5">
         <f>IF(SUM($F13:$I13)=0,0,M13*G13/SUM($F13:$I13))</f>
-        <v>9000.0</v>
+        <v/>
       </c>
       <c r="V13" s="5">
         <f>IF(SUM($F13:$I13)=0,0,M13*H13/SUM($F13:$I13))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="W13" s="5">
         <f>IF(SUM($F13:$I13)=0,0,M13*I13/SUM($F13:$I13))</f>
-        <v>0.0</v>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -3047,19 +3075,19 @@
       </c>
       <c r="B14" s="5">
         <f>Inputs!$B$22*Inputs!$B$2</f>
-        <v>2000.0</v>
+        <v/>
       </c>
       <c r="C14" s="5">
         <f>Inputs!$C$22*Inputs!$C$2</f>
-        <v>5000.0</v>
+        <v/>
       </c>
       <c r="D14" s="5">
         <f>D13+B14</f>
-        <v>1289343.8660000002</v>
+        <v/>
       </c>
       <c r="E14" s="5">
         <f>E13+C14</f>
-        <v>2629361.27</v>
+        <v/>
       </c>
       <c r="F14" s="6" t="n">
         <v>0</v>
@@ -3075,19 +3103,19 @@
       </c>
       <c r="J14" s="5">
         <f>B14*SUM($F14:$I14)</f>
-        <v>2000.0</v>
+        <v/>
       </c>
       <c r="K14" s="5">
         <f>C14*SUM($F14:$I14)</f>
-        <v>5000.0</v>
+        <v/>
       </c>
       <c r="L14" s="5">
-        <f>J14*Inputs!$B$39</f>
-        <v>600.0</v>
+        <f>J14*Inputs!$B$40</f>
+        <v/>
       </c>
       <c r="M14" s="5">
-        <f>K14*Inputs!$C$39</f>
-        <v>3000.0</v>
+        <f>K14*Inputs!$C$40</f>
+        <v/>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -3096,39 +3124,39 @@
       </c>
       <c r="O14" s="5">
         <f>C14-K14</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="P14" s="5">
         <f>IF(SUM($F14:$I14)=0,0,L14*F14/SUM($F14:$I14))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="Q14" s="5">
         <f>IF(SUM($F14:$I14)=0,0,L14*G14/SUM($F14:$I14))</f>
-        <v>600.0</v>
+        <v/>
       </c>
       <c r="R14" s="5">
         <f>IF(SUM($F14:$I14)=0,0,L14*H14/SUM($F14:$I14))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="S14" s="5">
         <f>IF(SUM($F14:$I14)=0,0,L14*I14/SUM($F14:$I14))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="T14" s="5">
         <f>IF(SUM($F14:$I14)=0,0,M14*F14/SUM($F14:$I14))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="U14" s="5">
         <f>IF(SUM($F14:$I14)=0,0,M14*G14/SUM($F14:$I14))</f>
-        <v>3000.0</v>
+        <v/>
       </c>
       <c r="V14" s="5">
         <f>IF(SUM($F14:$I14)=0,0,M14*H14/SUM($F14:$I14))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="W14" s="5">
         <f>IF(SUM($F14:$I14)=0,0,M14*I14/SUM($F14:$I14))</f>
-        <v>0.0</v>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -3139,19 +3167,19 @@
       </c>
       <c r="B15" s="5">
         <f>Inputs!$B$23*Inputs!$B$2</f>
-        <v>2000.0</v>
+        <v/>
       </c>
       <c r="C15" s="5">
         <f>Inputs!$C$23*Inputs!$C$2</f>
-        <v>5000.0</v>
+        <v/>
       </c>
       <c r="D15" s="5">
         <f>D14+B15</f>
-        <v>1291343.8660000002</v>
+        <v/>
       </c>
       <c r="E15" s="5">
         <f>E14+C15</f>
-        <v>2634361.27</v>
+        <v/>
       </c>
       <c r="F15" s="6" t="n">
         <v>0</v>
@@ -3167,60 +3195,60 @@
       </c>
       <c r="J15" s="5">
         <f>B15*SUM($F15:$I15)</f>
-        <v>2000.0</v>
+        <v/>
       </c>
       <c r="K15" s="5">
         <f>C15*SUM($F15:$I15)</f>
-        <v>5000.0</v>
+        <v/>
       </c>
       <c r="L15" s="5">
-        <f>J15*Inputs!$B$39</f>
-        <v>600.0</v>
+        <f>J15*Inputs!$B$40</f>
+        <v/>
       </c>
       <c r="M15" s="5">
-        <f>K15*Inputs!$C$39</f>
-        <v>3000.0</v>
+        <f>K15*Inputs!$C$40</f>
+        <v/>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Design values, seismic qualification</t>
+          <t>A few months of design and load-data development (Alex 2026-09-04)</t>
         </is>
       </c>
       <c r="O15" s="5">
         <f>C15-K15</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="P15" s="5">
         <f>IF(SUM($F15:$I15)=0,0,L15*F15/SUM($F15:$I15))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="Q15" s="5">
         <f>IF(SUM($F15:$I15)=0,0,L15*G15/SUM($F15:$I15))</f>
-        <v>600.0</v>
+        <v/>
       </c>
       <c r="R15" s="5">
         <f>IF(SUM($F15:$I15)=0,0,L15*H15/SUM($F15:$I15))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="S15" s="5">
         <f>IF(SUM($F15:$I15)=0,0,L15*I15/SUM($F15:$I15))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="T15" s="5">
         <f>IF(SUM($F15:$I15)=0,0,M15*F15/SUM($F15:$I15))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="U15" s="5">
         <f>IF(SUM($F15:$I15)=0,0,M15*G15/SUM($F15:$I15))</f>
-        <v>3000.0</v>
+        <v/>
       </c>
       <c r="V15" s="5">
         <f>IF(SUM($F15:$I15)=0,0,M15*H15/SUM($F15:$I15))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="W15" s="5">
         <f>IF(SUM($F15:$I15)=0,0,M15*I15/SUM($F15:$I15))</f>
-        <v>0.0</v>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -3231,26 +3259,26 @@
       </c>
       <c r="B16" s="5">
         <f>Inputs!$B$24*Inputs!$B$2</f>
-        <v>5000.0</v>
+        <v/>
       </c>
       <c r="C16" s="5">
         <f>Inputs!$C$24*Inputs!$C$2</f>
-        <v>10000.0</v>
+        <v/>
       </c>
       <c r="D16" s="5">
         <f>D15+B16</f>
-        <v>1296343.8660000002</v>
+        <v/>
       </c>
       <c r="E16" s="5">
         <f>E15+C16</f>
-        <v>2644361.27</v>
+        <v/>
       </c>
       <c r="F16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="6">
-        <f>Inputs!$B$41</f>
-        <v>0.5</v>
+        <f>Inputs!$B$42</f>
+        <v/>
       </c>
       <c r="H16" s="6" t="n">
         <v>0</v>
@@ -3260,19 +3288,19 @@
       </c>
       <c r="J16" s="5">
         <f>B16*SUM($F16:$I16)</f>
-        <v>2500.0</v>
+        <v/>
       </c>
       <c r="K16" s="5">
         <f>C16*SUM($F16:$I16)</f>
-        <v>5000.0</v>
+        <v/>
       </c>
       <c r="L16" s="5">
-        <f>J16*Inputs!$B$39</f>
-        <v>750.0</v>
+        <f>J16*Inputs!$B$40</f>
+        <v/>
       </c>
       <c r="M16" s="5">
-        <f>K16*Inputs!$C$39</f>
-        <v>3000.0</v>
+        <f>K16*Inputs!$C$40</f>
+        <v/>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -3281,39 +3309,39 @@
       </c>
       <c r="O16" s="5">
         <f>C16-K16</f>
-        <v>5000.0</v>
+        <v/>
       </c>
       <c r="P16" s="5">
         <f>IF(SUM($F16:$I16)=0,0,L16*F16/SUM($F16:$I16))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="Q16" s="5">
         <f>IF(SUM($F16:$I16)=0,0,L16*G16/SUM($F16:$I16))</f>
-        <v>750.0</v>
+        <v/>
       </c>
       <c r="R16" s="5">
         <f>IF(SUM($F16:$I16)=0,0,L16*H16/SUM($F16:$I16))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="S16" s="5">
         <f>IF(SUM($F16:$I16)=0,0,L16*I16/SUM($F16:$I16))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="T16" s="5">
         <f>IF(SUM($F16:$I16)=0,0,M16*F16/SUM($F16:$I16))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="U16" s="5">
         <f>IF(SUM($F16:$I16)=0,0,M16*G16/SUM($F16:$I16))</f>
-        <v>3000.0</v>
+        <v/>
       </c>
       <c r="V16" s="5">
         <f>IF(SUM($F16:$I16)=0,0,M16*H16/SUM($F16:$I16))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="W16" s="5">
         <f>IF(SUM($F16:$I16)=0,0,M16*I16/SUM($F16:$I16))</f>
-        <v>0.0</v>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -3323,20 +3351,20 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>Inputs!$B$33*Inputs!$B$2</f>
-        <v>3000.0</v>
+        <f>Inputs!$B$34*Inputs!$B$2</f>
+        <v/>
       </c>
       <c r="C17" s="5">
-        <f>Inputs!$C$33*Inputs!$C$2</f>
-        <v>8000.0</v>
+        <f>Inputs!$C$34*Inputs!$C$2</f>
+        <v/>
       </c>
       <c r="D17" s="5">
         <f>D16+B17</f>
-        <v>1299343.8660000002</v>
+        <v/>
       </c>
       <c r="E17" s="5">
         <f>E16+C17</f>
-        <v>2652361.27</v>
+        <v/>
       </c>
       <c r="F17" s="6" t="n">
         <v>0</v>
@@ -3352,19 +3380,19 @@
       </c>
       <c r="J17" s="5">
         <f>B17*SUM($F17:$I17)</f>
-        <v>3000.0</v>
+        <v/>
       </c>
       <c r="K17" s="5">
         <f>C17*SUM($F17:$I17)</f>
-        <v>8000.0</v>
+        <v/>
       </c>
       <c r="L17" s="5">
-        <f>J17*Inputs!$B$39</f>
-        <v>900.0</v>
+        <f>J17*Inputs!$B$40</f>
+        <v/>
       </c>
       <c r="M17" s="5">
-        <f>K17*Inputs!$C$39</f>
-        <v>4800.0</v>
+        <f>K17*Inputs!$C$40</f>
+        <v/>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -3373,39 +3401,39 @@
       </c>
       <c r="O17" s="5">
         <f>C17-K17</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="P17" s="5">
         <f>IF(SUM($F17:$I17)=0,0,L17*F17/SUM($F17:$I17))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="Q17" s="5">
         <f>IF(SUM($F17:$I17)=0,0,L17*G17/SUM($F17:$I17))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="R17" s="5">
         <f>IF(SUM($F17:$I17)=0,0,L17*H17/SUM($F17:$I17))</f>
-        <v>900.0</v>
+        <v/>
       </c>
       <c r="S17" s="5">
         <f>IF(SUM($F17:$I17)=0,0,L17*I17/SUM($F17:$I17))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="T17" s="5">
         <f>IF(SUM($F17:$I17)=0,0,M17*F17/SUM($F17:$I17))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="U17" s="5">
         <f>IF(SUM($F17:$I17)=0,0,M17*G17/SUM($F17:$I17))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="V17" s="5">
         <f>IF(SUM($F17:$I17)=0,0,M17*H17/SUM($F17:$I17))</f>
-        <v>4800.0</v>
+        <v/>
       </c>
       <c r="W17" s="5">
         <f>IF(SUM($F17:$I17)=0,0,M17*I17/SUM($F17:$I17))</f>
-        <v>0.0</v>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -3416,19 +3444,19 @@
       </c>
       <c r="B18" s="5">
         <f>Inputs!$B$25*Inputs!$B$2</f>
-        <v>1000.0</v>
+        <v/>
       </c>
       <c r="C18" s="5">
         <f>Inputs!$C$25*Inputs!$C$2</f>
-        <v>3000.0</v>
+        <v/>
       </c>
       <c r="D18" s="5">
         <f>D17+B18</f>
-        <v>1300343.8660000002</v>
+        <v/>
       </c>
       <c r="E18" s="5">
         <f>E17+C18</f>
-        <v>2655361.27</v>
+        <v/>
       </c>
       <c r="F18" s="6" t="n">
         <v>1</v>
@@ -3444,19 +3472,19 @@
       </c>
       <c r="J18" s="5">
         <f>B18*SUM($F18:$I18)</f>
-        <v>1000.0</v>
+        <v/>
       </c>
       <c r="K18" s="5">
         <f>C18*SUM($F18:$I18)</f>
-        <v>3000.0</v>
+        <v/>
       </c>
       <c r="L18" s="5">
         <f>SUM($F18:$I18)*(Inputs!$B$9+Inputs!$B$10)*Derived!B6/1000</f>
-        <v>130.435812</v>
+        <v/>
       </c>
       <c r="M18" s="5">
         <f>SUM($F18:$I18)*(Inputs!$C$9+Inputs!$C$10)*Derived!C6/1000</f>
-        <v>391.307436</v>
+        <v/>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -3465,39 +3493,39 @@
       </c>
       <c r="O18" s="5">
         <f>C18-K18</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="P18" s="5">
         <f>IF(SUM($F18:$I18)=0,0,L18*F18/SUM($F18:$I18))</f>
-        <v>130.435812</v>
+        <v/>
       </c>
       <c r="Q18" s="5">
         <f>IF(SUM($F18:$I18)=0,0,L18*G18/SUM($F18:$I18))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="R18" s="5">
         <f>IF(SUM($F18:$I18)=0,0,L18*H18/SUM($F18:$I18))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="S18" s="5">
         <f>IF(SUM($F18:$I18)=0,0,L18*I18/SUM($F18:$I18))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="T18" s="5">
         <f>IF(SUM($F18:$I18)=0,0,M18*F18/SUM($F18:$I18))</f>
-        <v>391.307436</v>
+        <v/>
       </c>
       <c r="U18" s="5">
         <f>IF(SUM($F18:$I18)=0,0,M18*G18/SUM($F18:$I18))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="V18" s="5">
         <f>IF(SUM($F18:$I18)=0,0,M18*H18/SUM($F18:$I18))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="W18" s="5">
         <f>IF(SUM($F18:$I18)=0,0,M18*I18/SUM($F18:$I18))</f>
-        <v>0.0</v>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -3508,19 +3536,19 @@
       </c>
       <c r="B19" s="5">
         <f>Inputs!$B$26*Inputs!$B$2</f>
-        <v>50000.0</v>
+        <v/>
       </c>
       <c r="C19" s="5">
         <f>Inputs!$C$26*Inputs!$C$2</f>
-        <v>100000.0</v>
+        <v/>
       </c>
       <c r="D19" s="5">
         <f>D18+B19</f>
-        <v>1350343.8660000002</v>
+        <v/>
       </c>
       <c r="E19" s="5">
         <f>E18+C19</f>
-        <v>2755361.27</v>
+        <v/>
       </c>
       <c r="F19" s="6" t="n">
         <v>0</v>
@@ -3536,19 +3564,19 @@
       </c>
       <c r="J19" s="5">
         <f>B19*SUM($F19:$I19)</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="K19" s="5">
         <f>C19*SUM($F19:$I19)</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="L19" s="5">
         <f>0</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="M19" s="5">
         <f>0</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -3557,39 +3585,39 @@
       </c>
       <c r="O19" s="5">
         <f>C19-K19</f>
-        <v>100000.0</v>
+        <v/>
       </c>
       <c r="P19" s="5">
         <f>IF(SUM($F19:$I19)=0,0,L19*F19/SUM($F19:$I19))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="Q19" s="5">
         <f>IF(SUM($F19:$I19)=0,0,L19*G19/SUM($F19:$I19))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="R19" s="5">
         <f>IF(SUM($F19:$I19)=0,0,L19*H19/SUM($F19:$I19))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="S19" s="5">
         <f>IF(SUM($F19:$I19)=0,0,L19*I19/SUM($F19:$I19))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="T19" s="5">
         <f>IF(SUM($F19:$I19)=0,0,M19*F19/SUM($F19:$I19))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="U19" s="5">
         <f>IF(SUM($F19:$I19)=0,0,M19*G19/SUM($F19:$I19))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="V19" s="5">
         <f>IF(SUM($F19:$I19)=0,0,M19*H19/SUM($F19:$I19))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="W19" s="5">
         <f>IF(SUM($F19:$I19)=0,0,M19*I19/SUM($F19:$I19))</f>
-        <v>0.0</v>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -3600,19 +3628,19 @@
       </c>
       <c r="B20" s="5">
         <f>Inputs!$B$27*Inputs!$B$2</f>
-        <v>20000.0</v>
+        <v/>
       </c>
       <c r="C20" s="5">
         <f>Inputs!$C$27*Inputs!$C$2</f>
-        <v>50000.0</v>
+        <v/>
       </c>
       <c r="D20" s="5">
         <f>D19+B20</f>
-        <v>1370343.8660000002</v>
+        <v/>
       </c>
       <c r="E20" s="5">
         <f>E19+C20</f>
-        <v>2805361.27</v>
+        <v/>
       </c>
       <c r="F20" s="6" t="n">
         <v>0</v>
@@ -3628,19 +3656,19 @@
       </c>
       <c r="J20" s="5">
         <f>B20*SUM($F20:$I20)</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="K20" s="5">
         <f>C20*SUM($F20:$I20)</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="L20" s="5">
         <f>0</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="M20" s="5">
         <f>0</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -3649,39 +3677,39 @@
       </c>
       <c r="O20" s="5">
         <f>C20-K20</f>
-        <v>50000.0</v>
+        <v/>
       </c>
       <c r="P20" s="5">
         <f>IF(SUM($F20:$I20)=0,0,L20*F20/SUM($F20:$I20))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="Q20" s="5">
         <f>IF(SUM($F20:$I20)=0,0,L20*G20/SUM($F20:$I20))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="R20" s="5">
         <f>IF(SUM($F20:$I20)=0,0,L20*H20/SUM($F20:$I20))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="S20" s="5">
         <f>IF(SUM($F20:$I20)=0,0,L20*I20/SUM($F20:$I20))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="T20" s="5">
         <f>IF(SUM($F20:$I20)=0,0,M20*F20/SUM($F20:$I20))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="U20" s="5">
         <f>IF(SUM($F20:$I20)=0,0,M20*G20/SUM($F20:$I20))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="V20" s="5">
         <f>IF(SUM($F20:$I20)=0,0,M20*H20/SUM($F20:$I20))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="W20" s="5">
         <f>IF(SUM($F20:$I20)=0,0,M20*I20/SUM($F20:$I20))</f>
-        <v>0.0</v>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -3692,19 +3720,19 @@
       </c>
       <c r="B21" s="5">
         <f>Inputs!$B$28*Inputs!$B$2</f>
-        <v>15000.0</v>
+        <v/>
       </c>
       <c r="C21" s="5">
         <f>Inputs!$C$28*Inputs!$C$2</f>
-        <v>70000.0</v>
+        <v/>
       </c>
       <c r="D21" s="5">
         <f>D20+B21</f>
-        <v>1385343.8660000002</v>
+        <v/>
       </c>
       <c r="E21" s="5">
         <f>E20+C21</f>
-        <v>2875361.27</v>
+        <v/>
       </c>
       <c r="F21" s="6" t="n">
         <v>0</v>
@@ -3715,65 +3743,66 @@
       <c r="H21" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I21" s="6" t="n">
-        <v>0</v>
+      <c r="I21" s="6">
+        <f>Inputs!$B$29</f>
+        <v/>
       </c>
       <c r="J21" s="5">
         <f>B21*SUM($F21:$I21)</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="K21" s="5">
         <f>C21*SUM($F21:$I21)</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="L21" s="5">
-        <f>0</f>
-        <v>0.0</v>
+        <f>J21*Inputs!$B$40</f>
+        <v/>
       </c>
       <c r="M21" s="5">
-        <f>0</f>
-        <v>0.0</v>
+        <f>K21*Inputs!$C$40</f>
+        <v/>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Rack masses [H]; aggregate [L]</t>
+          <t>Server and equipment enclosures only (40% of IT mass, estimate); electronics never. Rack masses [H]; aggregate [L]</t>
         </is>
       </c>
       <c r="O21" s="5">
         <f>C21-K21</f>
-        <v>70000.0</v>
+        <v/>
       </c>
       <c r="P21" s="5">
         <f>IF(SUM($F21:$I21)=0,0,L21*F21/SUM($F21:$I21))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="Q21" s="5">
         <f>IF(SUM($F21:$I21)=0,0,L21*G21/SUM($F21:$I21))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="R21" s="5">
         <f>IF(SUM($F21:$I21)=0,0,L21*H21/SUM($F21:$I21))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="S21" s="5">
         <f>IF(SUM($F21:$I21)=0,0,L21*I21/SUM($F21:$I21))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="T21" s="5">
         <f>IF(SUM($F21:$I21)=0,0,M21*F21/SUM($F21:$I21))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="U21" s="5">
         <f>IF(SUM($F21:$I21)=0,0,M21*G21/SUM($F21:$I21))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="V21" s="5">
         <f>IF(SUM($F21:$I21)=0,0,M21*H21/SUM($F21:$I21))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="W21" s="5">
         <f>IF(SUM($F21:$I21)=0,0,M21*I21/SUM($F21:$I21))</f>
-        <v>0.0</v>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -3791,11 +3820,11 @@
       </c>
       <c r="B24" s="8">
         <f>SUM(B3:B21)</f>
-        <v>1385343.866</v>
+        <v/>
       </c>
       <c r="C24" s="8">
         <f>SUM(C3:C21)</f>
-        <v>2875361.27</v>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -3806,11 +3835,11 @@
       </c>
       <c r="B25" s="8">
         <f>B24-B3-B4-B5</f>
-        <v>185343.86599999992</v>
+        <v/>
       </c>
       <c r="C25" s="8">
         <f>C24-C3-C4-C5</f>
-        <v>475361.27</v>
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -3828,11 +3857,11 @@
       </c>
       <c r="B28" s="10">
         <f>SUMPRODUCT(B3:B21,F3:F21)</f>
-        <v>3343.866</v>
+        <v/>
       </c>
       <c r="C28" s="10">
         <f>SUMPRODUCT(C3:C21,F3:F21)</f>
-        <v>12361.269999999999</v>
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -3843,11 +3872,11 @@
       </c>
       <c r="B29" s="10">
         <f>SUM(P3:P21)</f>
-        <v>1234.0078919999999</v>
+        <v/>
       </c>
       <c r="C29" s="10">
         <f>SUM(T3:T21)</f>
-        <v>2685.4088039999997</v>
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -3858,11 +3887,11 @@
       </c>
       <c r="B30" s="10">
         <f>B29*1000/Derived!B6</f>
-        <v>1419097.8762795602</v>
+        <v/>
       </c>
       <c r="C30" s="10">
         <f>C29*1000/Derived!C6</f>
-        <v>3088195.7525591203</v>
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -3873,11 +3902,11 @@
       </c>
       <c r="B31" s="11">
         <f>B29/Derived!B7</f>
-        <v>1.4190978762795603</v>
+        <v/>
       </c>
       <c r="C31" s="11">
         <f>C29/Derived!C7</f>
-        <v>3.0881957525591206</v>
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -3888,11 +3917,11 @@
       </c>
       <c r="B33" s="10">
         <f>SUMPRODUCT(B3:B21,G3:G21)</f>
-        <v>11500.0</v>
+        <v/>
       </c>
       <c r="C33" s="10">
         <f>SUMPRODUCT(C3:C21,G3:G21)</f>
-        <v>30000.0</v>
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -3903,11 +3932,11 @@
       </c>
       <c r="B34" s="10">
         <f>SUM(Q3:Q21)</f>
-        <v>3450.0</v>
+        <v/>
       </c>
       <c r="C34" s="10">
         <f>SUM(U3:U21)</f>
-        <v>18000.0</v>
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -3918,11 +3947,11 @@
       </c>
       <c r="B35" s="11">
         <f>B34/Derived!B8</f>
-        <v>0.11020746357603078</v>
+        <v/>
       </c>
       <c r="C35" s="11">
         <f>C34/Derived!C8</f>
-        <v>0.5749954621358128</v>
+        <v/>
       </c>
     </row>
     <row r="37">
@@ -3933,11 +3962,11 @@
       </c>
       <c r="B37" s="10">
         <f>SUMPRODUCT(B3:B21,H3:H21)</f>
-        <v>53000.0</v>
+        <v/>
       </c>
       <c r="C37" s="10">
         <f>SUMPRODUCT(C3:C21,H3:H21)</f>
-        <v>108000.0</v>
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -3948,11 +3977,11 @@
       </c>
       <c r="B38" s="10">
         <f>SUM(R3:R21)</f>
-        <v>15900.0</v>
+        <v/>
       </c>
       <c r="C38" s="10">
         <f>SUM(V3:V21)</f>
-        <v>64800.0</v>
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -3963,11 +3992,11 @@
       </c>
       <c r="B39" s="11">
         <f>B38/Derived!B8</f>
-        <v>0.507912658219968</v>
+        <v/>
       </c>
       <c r="C39" s="11">
         <f>C38/Derived!C8</f>
-        <v>2.069983663688926</v>
+        <v/>
       </c>
     </row>
     <row r="41">
@@ -3978,11 +4007,11 @@
       </c>
       <c r="B41" s="10">
         <f>SUMPRODUCT(B3:B21,I3:I21)</f>
-        <v>996300.0</v>
+        <v/>
       </c>
       <c r="C41" s="10">
         <f>SUMPRODUCT(C3:C21,I3:I21)</f>
-        <v>2061000.0</v>
+        <v/>
       </c>
     </row>
     <row r="42">
@@ -3993,11 +4022,11 @@
       </c>
       <c r="B42" s="10">
         <f>SUM(S3:S21)</f>
-        <v>55890.0</v>
+        <v/>
       </c>
       <c r="C42" s="10">
         <f>SUM(W3:W21)</f>
-        <v>345600.0</v>
+        <v/>
       </c>
     </row>
     <row r="43">
@@ -4008,11 +4037,11 @@
       </c>
       <c r="B43" s="11">
         <f>B42/Derived!B8</f>
-        <v>1.7853609099316987</v>
+        <v/>
       </c>
       <c r="C43" s="11">
         <f>C42/Derived!C8</f>
-        <v>11.039912873007607</v>
+        <v/>
       </c>
     </row>
     <row r="45">
@@ -4023,11 +4052,11 @@
       </c>
       <c r="B45" s="8">
         <f>SUM(J3:J21)</f>
-        <v>1064143.866</v>
+        <v/>
       </c>
       <c r="C45" s="8">
         <f>SUM(K3:K21)</f>
-        <v>2211361.27</v>
+        <v/>
       </c>
     </row>
     <row r="46">
@@ -4038,11 +4067,11 @@
       </c>
       <c r="B46" s="8">
         <f>SUM(L3:L21)</f>
-        <v>76474.007892</v>
+        <v/>
       </c>
       <c r="C46" s="8">
         <f>SUM(M3:M21)</f>
-        <v>431085.408804</v>
+        <v/>
       </c>
     </row>
     <row r="47">
@@ -4053,11 +4082,11 @@
       </c>
       <c r="B47" s="11">
         <f>B46/Derived!B8</f>
-        <v>2.4429004171799074</v>
+        <v/>
       </c>
       <c r="C47" s="11">
         <f>C46/Derived!C8</f>
-        <v>13.77067521418121</v>
+        <v/>
       </c>
     </row>
     <row r="48">
@@ -4068,11 +4097,11 @@
       </c>
       <c r="B48" s="12">
         <f>B45/B24</f>
-        <v>0.7681442074541224</v>
+        <v/>
       </c>
       <c r="C48" s="12">
         <f>C45/C24</f>
-        <v>0.7690724964101642</v>
+        <v/>
       </c>
     </row>
     <row r="49">
@@ -4083,11 +4112,11 @@
       </c>
       <c r="B49" s="12">
         <f>(B45-B41)/B25</f>
-        <v>0.36604322260117284</v>
+        <v/>
       </c>
       <c r="C49" s="12">
         <f>(C45-C41)/C25</f>
-        <v>0.3163094671132968</v>
+        <v/>
       </c>
     </row>
     <row r="50">
@@ -4098,11 +4127,11 @@
       </c>
       <c r="B50" s="8">
         <f>B24-B45</f>
-        <v>321200.0</v>
+        <v/>
       </c>
       <c r="C50" s="8">
         <f>C24-C45</f>
-        <v>664000.0</v>
+        <v/>
       </c>
     </row>
     <row r="51">
@@ -4113,11 +4142,11 @@
       </c>
       <c r="B51" s="12">
         <f>B50/B24</f>
-        <v>0.23185579254587757</v>
+        <v/>
       </c>
       <c r="C51" s="12">
         <f>C50/C24</f>
-        <v>0.23092750358983585</v>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -4171,11 +4200,11 @@
       </c>
       <c r="B2" s="13">
         <f>Inputs!$B$3*Inputs!$B$2/Inputs!$B$4</f>
-        <v>5.0</v>
+        <v/>
       </c>
       <c r="C2" s="13">
         <f>Inputs!$C$3*Inputs!$C$2/Inputs!$C$4</f>
-        <v>10.0</v>
+        <v/>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4191,11 +4220,11 @@
       </c>
       <c r="B3" s="13">
         <f>B2*Inputs!$B$5</f>
-        <v>800000.0</v>
+        <v/>
       </c>
       <c r="C3" s="13">
         <f>C2*Inputs!$C$5</f>
-        <v>1600000.0</v>
+        <v/>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -4211,11 +4240,11 @@
       </c>
       <c r="B4" s="13">
         <f>B3*0.092903</f>
-        <v>74322.4</v>
+        <v/>
       </c>
       <c r="C4" s="13">
         <f>C3*0.092903</f>
-        <v>148644.8</v>
+        <v/>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4231,11 +4260,11 @@
       </c>
       <c r="B5" s="13">
         <f>Inputs!$B$7*1000*Inputs!$B$8/0.092903</f>
-        <v>269097.8762795604</v>
+        <v/>
       </c>
       <c r="C5" s="13">
         <f>Inputs!$C$7*1000*Inputs!$C$8/0.092903</f>
-        <v>538195.7525591208</v>
+        <v/>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -4250,12 +4279,12 @@
         </is>
       </c>
       <c r="B6" s="13">
-        <f>Inputs!$B$35/1000*Inputs!$B$36*0.092903</f>
-        <v>0.86957208</v>
+        <f>Inputs!$B$36/1000*Inputs!$B$37*0.092903</f>
+        <v/>
       </c>
       <c r="C6" s="13">
-        <f>Inputs!$C$35/1000*Inputs!$C$36*0.092903</f>
-        <v>0.86957208</v>
+        <f>Inputs!$C$36/1000*Inputs!$C$37*0.092903</f>
+        <v/>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -4270,12 +4299,12 @@
         </is>
       </c>
       <c r="B7" s="13">
-        <f>Inputs!$B$37*B6/1000</f>
-        <v>869.5720799999999</v>
+        <f>Inputs!$B$38*B6/1000</f>
+        <v/>
       </c>
       <c r="C7" s="13">
-        <f>Inputs!$C$37*C6/1000</f>
-        <v>869.5720799999999</v>
+        <f>Inputs!$C$38*C6/1000</f>
+        <v/>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4290,12 +4319,12 @@
         </is>
       </c>
       <c r="B8" s="13">
-        <f>Inputs!$B$38*B6/1000</f>
-        <v>31304.59488</v>
+        <f>Inputs!$B$39*B6/1000</f>
+        <v/>
       </c>
       <c r="C8" s="13">
-        <f>Inputs!$C$38*C6/1000</f>
-        <v>31304.59488</v>
+        <f>Inputs!$C$39*C6/1000</f>
+        <v/>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -4394,44 +4423,44 @@
         </is>
       </c>
       <c r="B2" s="4">
-        <f>'1 GW data center'!B28*Inputs!$B$43</f>
-        <v>6018.9588</v>
+        <f>'1 GW data center'!B28*Inputs!$B$44</f>
+        <v/>
       </c>
       <c r="C2" s="4">
-        <f>'1 GW data center'!C28*Inputs!$C$43</f>
-        <v>22250.285999999996</v>
+        <f>'1 GW data center'!C28*Inputs!$C$44</f>
+        <v/>
       </c>
       <c r="D2" s="4">
-        <f>'1 GW data center'!B29*Inputs!$B$45</f>
-        <v>617.0039459999999</v>
+        <f>'1 GW data center'!B29*Inputs!$B$46</f>
+        <v/>
       </c>
       <c r="E2" s="4">
-        <f>'1 GW data center'!C29*Inputs!$C$45</f>
-        <v>1342.7044019999998</v>
+        <f>'1 GW data center'!C29*Inputs!$C$46</f>
+        <v/>
       </c>
       <c r="F2" s="4">
         <f>B2-D2</f>
-        <v>5401.9548540000005</v>
+        <v/>
       </c>
       <c r="G2" s="4">
         <f>C2-E2</f>
-        <v>20907.581597999997</v>
+        <v/>
       </c>
       <c r="H2" s="4">
-        <f>'1 GW data center'!B28*Inputs!$B$44-D2</f>
-        <v>720.5424540000002</v>
+        <f>'1 GW data center'!B28*Inputs!$B$45-D2</f>
+        <v/>
       </c>
       <c r="I2" s="4">
-        <f>'1 GW data center'!C28*Inputs!$C$44-E2</f>
-        <v>7310.184598</v>
+        <f>'1 GW data center'!C28*Inputs!$C$45-E2</f>
+        <v/>
       </c>
       <c r="J2" s="4">
-        <f>'1 GW data center'!B29*Inputs!$B$46</f>
-        <v>1604.2102596</v>
+        <f>'1 GW data center'!B29*Inputs!$B$47</f>
+        <v/>
       </c>
       <c r="K2" s="4">
-        <f>'1 GW data center'!C29*Inputs!$C$46</f>
-        <v>3491.0314452</v>
+        <f>'1 GW data center'!C29*Inputs!$C$47</f>
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -4441,44 +4470,44 @@
         </is>
       </c>
       <c r="B3" s="4">
-        <f>'1 GW data center'!B33*Inputs!$B$43</f>
-        <v>20700.0</v>
+        <f>'1 GW data center'!B33*Inputs!$B$44</f>
+        <v/>
       </c>
       <c r="C3" s="4">
-        <f>'1 GW data center'!C33*Inputs!$C$43</f>
-        <v>54000.0</v>
+        <f>'1 GW data center'!C33*Inputs!$C$44</f>
+        <v/>
       </c>
       <c r="D3" s="4">
-        <f>'1 GW data center'!B34*Inputs!$B$45</f>
-        <v>1725.0</v>
+        <f>'1 GW data center'!B34*Inputs!$B$46</f>
+        <v/>
       </c>
       <c r="E3" s="4">
-        <f>'1 GW data center'!C34*Inputs!$C$45</f>
-        <v>9000.0</v>
+        <f>'1 GW data center'!C34*Inputs!$C$46</f>
+        <v/>
       </c>
       <c r="F3" s="4">
         <f>B3-D3</f>
-        <v>18975.0</v>
+        <v/>
       </c>
       <c r="G3" s="4">
         <f>C3-E3</f>
-        <v>45000.0</v>
+        <v/>
       </c>
       <c r="H3" s="4">
-        <f>'1 GW data center'!B33*Inputs!$B$44-D3</f>
-        <v>2875.0</v>
+        <f>'1 GW data center'!B33*Inputs!$B$45-D3</f>
+        <v/>
       </c>
       <c r="I3" s="4">
-        <f>'1 GW data center'!C33*Inputs!$C$44-E3</f>
-        <v>12000.0</v>
+        <f>'1 GW data center'!C33*Inputs!$C$45-E3</f>
+        <v/>
       </c>
       <c r="J3" s="4">
-        <f>'1 GW data center'!B34*Inputs!$B$46</f>
-        <v>4485.0</v>
+        <f>'1 GW data center'!B34*Inputs!$B$47</f>
+        <v/>
       </c>
       <c r="K3" s="4">
-        <f>'1 GW data center'!C34*Inputs!$C$46</f>
-        <v>23400.0</v>
+        <f>'1 GW data center'!C34*Inputs!$C$47</f>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -4488,44 +4517,44 @@
         </is>
       </c>
       <c r="B4" s="4">
-        <f>'1 GW data center'!B37*Inputs!$B$43</f>
-        <v>95400.0</v>
+        <f>'1 GW data center'!B37*Inputs!$B$44</f>
+        <v/>
       </c>
       <c r="C4" s="4">
-        <f>'1 GW data center'!C37*Inputs!$C$43</f>
-        <v>194400.0</v>
+        <f>'1 GW data center'!C37*Inputs!$C$44</f>
+        <v/>
       </c>
       <c r="D4" s="4">
-        <f>'1 GW data center'!B38*Inputs!$B$45</f>
-        <v>7950.0</v>
+        <f>'1 GW data center'!B38*Inputs!$B$46</f>
+        <v/>
       </c>
       <c r="E4" s="4">
-        <f>'1 GW data center'!C38*Inputs!$C$45</f>
-        <v>32400.0</v>
+        <f>'1 GW data center'!C38*Inputs!$C$46</f>
+        <v/>
       </c>
       <c r="F4" s="4">
         <f>B4-D4</f>
-        <v>87450.0</v>
+        <v/>
       </c>
       <c r="G4" s="4">
         <f>C4-E4</f>
-        <v>162000.0</v>
+        <v/>
       </c>
       <c r="H4" s="4">
-        <f>'1 GW data center'!B37*Inputs!$B$44-D4</f>
-        <v>13250.0</v>
+        <f>'1 GW data center'!B37*Inputs!$B$45-D4</f>
+        <v/>
       </c>
       <c r="I4" s="4">
-        <f>'1 GW data center'!C37*Inputs!$C$44-E4</f>
-        <v>43200.0</v>
+        <f>'1 GW data center'!C37*Inputs!$C$45-E4</f>
+        <v/>
       </c>
       <c r="J4" s="4">
-        <f>'1 GW data center'!B38*Inputs!$B$46</f>
-        <v>20670.0</v>
+        <f>'1 GW data center'!B38*Inputs!$B$47</f>
+        <v/>
       </c>
       <c r="K4" s="4">
-        <f>'1 GW data center'!C38*Inputs!$C$46</f>
-        <v>84240.0</v>
+        <f>'1 GW data center'!C38*Inputs!$C$47</f>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -4535,44 +4564,44 @@
         </is>
       </c>
       <c r="B5" s="4">
-        <f>'1 GW data center'!B41*Inputs!$B$34</f>
-        <v>119556.0</v>
+        <f>'1 GW data center'!B41*Inputs!$B$35</f>
+        <v/>
       </c>
       <c r="C5" s="4">
-        <f>'1 GW data center'!C41*Inputs!$C$34</f>
-        <v>247320.0</v>
+        <f>'1 GW data center'!C41*Inputs!$C$35</f>
+        <v/>
       </c>
       <c r="D5" s="4">
-        <f>'1 GW data center'!B42*Inputs!$B$45</f>
-        <v>27945.0</v>
+        <f>'1 GW data center'!B42*Inputs!$B$46</f>
+        <v/>
       </c>
       <c r="E5" s="4">
-        <f>'1 GW data center'!C42*Inputs!$C$45</f>
-        <v>172800.0</v>
+        <f>'1 GW data center'!C42*Inputs!$C$46</f>
+        <v/>
       </c>
       <c r="F5" s="4">
         <f>B5-D5</f>
-        <v>91611.0</v>
+        <v/>
       </c>
       <c r="G5" s="4">
         <f>C5-E5</f>
-        <v>74520.0</v>
-      </c>
-      <c r="H5" s="4" t="str">
+        <v/>
+      </c>
+      <c r="H5" s="4">
         <f>"n/a"</f>
-        <v>n/a</v>
-      </c>
-      <c r="I5" s="4" t="str">
+        <v/>
+      </c>
+      <c r="I5" s="4">
         <f>"n/a"</f>
-        <v>n/a</v>
+        <v/>
       </c>
       <c r="J5" s="4">
-        <f>'1 GW data center'!B42*Inputs!$B$46</f>
-        <v>72657.0</v>
+        <f>'1 GW data center'!B42*Inputs!$B$47</f>
+        <v/>
       </c>
       <c r="K5" s="4">
-        <f>'1 GW data center'!C42*Inputs!$C$46</f>
-        <v>449280.0</v>
+        <f>'1 GW data center'!C42*Inputs!$C$47</f>
+        <v/>
       </c>
     </row>
     <row r="7">

--- a/superwood-datacenter-investor/analyses/materials-mass-and-replacement.xlsx
+++ b/superwood-datacenter-investor/analyses/materials-mass-and-replacement.xlsx
@@ -186,7 +186,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>High case, tonnes per campus — replaced by SUPERWOOD vs not (slab concrete row excluded)</a:t>
+              <a:t>High case, tons per data center — replaced by SUPERWOOD vs not (slab concrete row excluded)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -278,7 +278,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>t per campus</a:t>
+                  <a:t>tons per data center</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -633,7 +633,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Reference unit: 1 GW IT-load campus. Change any yellow cell on Inputs (and the four addressable-share columns on 1 GW data center — immediate, soon, medium term, long term; a row may split across them); everything recalculates.</t>
+          <t>Reference unit: 1 GW IT-load data center. Change any yellow cell on Inputs (and the four addressable-share columns on 1 GW data center — immediate, soon, medium term, long term; a row may split across them); everything recalculates.</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IT load of reference campus</t>
+          <t>IT load of reference data center</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -847,7 +847,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Yard / mechanical screens and louvers (per campus)</t>
+          <t>Yard / mechanical screens and louvers (per data center)</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -892,7 +892,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Campus perimeter plus transformer / generator yards</t>
+          <t>Data center perimeter plus transformer / generator yards</t>
         </is>
       </c>
     </row>
@@ -1987,12 +1987,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Low  t per campus</t>
+          <t>Low  tons per data center</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>High  t per campus</t>
+          <t>High  tons per data center</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -3808,14 +3808,14 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>SUMMARY — per campus</t>
+          <t>SUMMARY — per data center</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Total mass, building and contents (t)</t>
+          <t>Total mass, building and contents (tons)</t>
         </is>
       </c>
       <c r="B24" s="8">
@@ -3830,7 +3830,7 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>Total excluding concrete (t)</t>
+          <t>Total excluding concrete (tons)</t>
         </is>
       </c>
       <c r="B25" s="8">
@@ -3852,7 +3852,7 @@
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Immediate — incumbent mass replaced (t)</t>
+          <t>Immediate — incumbent mass replaced (tons)</t>
         </is>
       </c>
       <c r="B28" s="10">
@@ -3867,7 +3867,7 @@
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>Immediate — SUPERWOOD required (t)</t>
+          <t>Immediate — SUPERWOOD required (tons)</t>
         </is>
       </c>
       <c r="B29" s="10">
@@ -3912,7 +3912,7 @@
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>Soon — incumbent mass replaced (t)</t>
+          <t>Soon — incumbent mass replaced (tons)</t>
         </is>
       </c>
       <c r="B33" s="10">
@@ -3927,7 +3927,7 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>Soon — SUPERWOOD required (t)</t>
+          <t>Soon — SUPERWOOD required (tons)</t>
         </is>
       </c>
       <c r="B34" s="10">
@@ -3957,7 +3957,7 @@
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>Medium term — incumbent mass replaced (t)</t>
+          <t>Medium term — incumbent mass replaced (tons)</t>
         </is>
       </c>
       <c r="B37" s="10">
@@ -3972,7 +3972,7 @@
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>Medium term — SUPERWOOD required (t)</t>
+          <t>Medium term — SUPERWOOD required (tons)</t>
         </is>
       </c>
       <c r="B38" s="10">
@@ -4002,7 +4002,7 @@
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>Long term — incumbent mass replaced (t)</t>
+          <t>Long term — incumbent mass replaced (tons)</t>
         </is>
       </c>
       <c r="B41" s="10">
@@ -4017,7 +4017,7 @@
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>Long term — SUPERWOOD required (t)</t>
+          <t>Long term — SUPERWOOD required (tons)</t>
         </is>
       </c>
       <c r="B42" s="10">
@@ -4047,7 +4047,7 @@
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>Cumulative incumbent mass replaced (t)</t>
+          <t>Cumulative incumbent mass replaced (tons)</t>
         </is>
       </c>
       <c r="B45" s="8">
@@ -4062,7 +4062,7 @@
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>Cumulative SUPERWOOD required (t)</t>
+          <t>Cumulative SUPERWOOD required (tons)</t>
         </is>
       </c>
       <c r="B46" s="8">
@@ -4122,7 +4122,7 @@
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>Not replaced by SUPERWOOD (t)</t>
+          <t>Not replaced by SUPERWOOD (tons)</t>
         </is>
       </c>
       <c r="B50" s="8">

--- a/superwood-datacenter-investor/analyses/materials-mass-and-replacement.xlsx
+++ b/superwood-datacenter-investor/analyses/materials-mass-and-replacement.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1 GW data center" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Derived" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carbon" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Steel share" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -81,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -91,6 +92,8 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -98,6 +101,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -304,7 +308,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>53</row>
+      <row>62</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="4320000"/>
@@ -614,7 +618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -623,7 +627,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>SUPERWOOD × Data Centers — material mass build-up and replacement model (2026-09-01, v2)</t>
+          <t>SUPERWOOD × Data Centers — material mass, embodied carbon and replacement model (2026-09-04, v3)</t>
         </is>
       </c>
     </row>
@@ -673,6 +677,13 @@
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
+        <is>
+          <t>Embodied carbon: columns X–AB on the main sheet value each row at its own factor (concrete, steel, mixed; equipment not estimated), with totals and steel/concrete shares in the summary; the Carbon sheet rolls avoided emissions up by horizon at those factors and at the recycled-steel (EAF) factor. Steel share: the Steel share sheet estimates what fraction of above-ground mass, contents included, is steel (per-component steel fractions are yellow inputs).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Companion narrative: materials-mass-and-replacement.md in the same folder.</t>
         </is>
@@ -689,7 +700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -1940,6 +1951,34 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Interior finishes emissions (gypsum, wood, steel studs — mixed)</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>kg CO₂e/kg</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>estimated [L]</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Used only for the interior finishes row</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1951,7 +1990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W51"/>
+  <dimension ref="A1:AB60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -1977,6 +2016,11 @@
     <col hidden="1" outlineLevel="1" width="11" customWidth="1" min="21" max="21"/>
     <col hidden="1" outlineLevel="1" width="11" customWidth="1" min="22" max="22"/>
     <col hidden="1" outlineLevel="1" width="11" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="18" customWidth="1" min="25" max="25"/>
+    <col width="18" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2093,6 +2137,31 @@
       <c r="W1" s="1" t="inlineStr">
         <is>
           <t>High SW long</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Carbon factor (kg CO₂e/kg)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Low embodied carbon (t CO₂e)</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>High embodied carbon (t CO₂e)</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>EAF-basis factor (kg CO₂e/kg)</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Material class</t>
         </is>
       </c>
     </row>
@@ -2212,6 +2281,27 @@
         <f>IF(SUM($F3:$I3)=0,0,M3*I3/SUM($F3:$I3))</f>
         <v/>
       </c>
+      <c r="X3" s="7">
+        <f>Inputs!$B$35</f>
+        <v/>
+      </c>
+      <c r="Y3" s="5">
+        <f>B3*X3</f>
+        <v/>
+      </c>
+      <c r="Z3" s="5">
+        <f>C3*X3</f>
+        <v/>
+      </c>
+      <c r="AA3" s="7">
+        <f>Inputs!$B$35</f>
+        <v/>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>concrete</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2305,6 +2395,27 @@
         <f>IF(SUM($F4:$I4)=0,0,M4*I4/SUM($F4:$I4))</f>
         <v/>
       </c>
+      <c r="X4" s="7">
+        <f>Inputs!$B$35</f>
+        <v/>
+      </c>
+      <c r="Y4" s="5">
+        <f>B4*X4</f>
+        <v/>
+      </c>
+      <c r="Z4" s="5">
+        <f>C4*X4</f>
+        <v/>
+      </c>
+      <c r="AA4" s="7">
+        <f>Inputs!$B$35</f>
+        <v/>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>concrete</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2397,6 +2508,27 @@
         <f>IF(SUM($F5:$I5)=0,0,M5*I5/SUM($F5:$I5))</f>
         <v/>
       </c>
+      <c r="X5" s="7">
+        <f>Inputs!$B$35</f>
+        <v/>
+      </c>
+      <c r="Y5" s="5">
+        <f>B5*X5</f>
+        <v/>
+      </c>
+      <c r="Z5" s="5">
+        <f>C5*X5</f>
+        <v/>
+      </c>
+      <c r="AA5" s="7">
+        <f>Inputs!$B$35</f>
+        <v/>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>concrete</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2490,6 +2622,27 @@
         <f>IF(SUM($F6:$I6)=0,0,M6*I6/SUM($F6:$I6))</f>
         <v/>
       </c>
+      <c r="X6" s="7">
+        <f>Inputs!$B$44</f>
+        <v/>
+      </c>
+      <c r="Y6" s="5">
+        <f>B6*X6</f>
+        <v/>
+      </c>
+      <c r="Z6" s="5">
+        <f>C6*X6</f>
+        <v/>
+      </c>
+      <c r="AA6" s="7">
+        <f>Inputs!$C$45</f>
+        <v/>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>steel</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2582,6 +2735,27 @@
         <f>IF(SUM($F7:$I7)=0,0,M7*I7/SUM($F7:$I7))</f>
         <v/>
       </c>
+      <c r="X7" s="7">
+        <f>Inputs!$B$44</f>
+        <v/>
+      </c>
+      <c r="Y7" s="5">
+        <f>B7*X7</f>
+        <v/>
+      </c>
+      <c r="Z7" s="5">
+        <f>C7*X7</f>
+        <v/>
+      </c>
+      <c r="AA7" s="7">
+        <f>Inputs!$C$45</f>
+        <v/>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>steel</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2674,6 +2848,27 @@
         <f>IF(SUM($F8:$I8)=0,0,M8*I8/SUM($F8:$I8))</f>
         <v/>
       </c>
+      <c r="X8" s="7">
+        <f>Inputs!$B$44</f>
+        <v/>
+      </c>
+      <c r="Y8" s="5">
+        <f>B8*X8</f>
+        <v/>
+      </c>
+      <c r="Z8" s="5">
+        <f>C8*X8</f>
+        <v/>
+      </c>
+      <c r="AA8" s="7">
+        <f>Inputs!$C$45</f>
+        <v/>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>steel</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2766,6 +2961,27 @@
         <f>IF(SUM($F9:$I9)=0,0,M9*I9/SUM($F9:$I9))</f>
         <v/>
       </c>
+      <c r="X9" s="7">
+        <f>Inputs!$B$44</f>
+        <v/>
+      </c>
+      <c r="Y9" s="5">
+        <f>B9*X9</f>
+        <v/>
+      </c>
+      <c r="Z9" s="5">
+        <f>C9*X9</f>
+        <v/>
+      </c>
+      <c r="AA9" s="7">
+        <f>Inputs!$C$45</f>
+        <v/>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>steel</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2858,6 +3074,27 @@
         <f>IF(SUM($F10:$I10)=0,0,M10*I10/SUM($F10:$I10))</f>
         <v/>
       </c>
+      <c r="X10" s="7">
+        <f>Inputs!$B$44</f>
+        <v/>
+      </c>
+      <c r="Y10" s="5">
+        <f>B10*X10</f>
+        <v/>
+      </c>
+      <c r="Z10" s="5">
+        <f>C10*X10</f>
+        <v/>
+      </c>
+      <c r="AA10" s="7">
+        <f>Inputs!$C$45</f>
+        <v/>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>steel</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2949,6 +3186,27 @@
       <c r="W11" s="5">
         <f>IF(SUM($F11:$I11)=0,0,M11*I11/SUM($F11:$I11))</f>
         <v/>
+      </c>
+      <c r="X11" s="7">
+        <f>Inputs!$B$44</f>
+        <v/>
+      </c>
+      <c r="Y11" s="5">
+        <f>B11*X11</f>
+        <v/>
+      </c>
+      <c r="Z11" s="5">
+        <f>C11*X11</f>
+        <v/>
+      </c>
+      <c r="AA11" s="7">
+        <f>Inputs!$C$45</f>
+        <v/>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>steel</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -2974,6 +3232,10 @@
       <c r="U12" s="4" t="n"/>
       <c r="V12" s="4" t="n"/>
       <c r="W12" s="4" t="n"/>
+      <c r="X12" s="8" t="n"/>
+      <c r="Y12" s="4" t="n"/>
+      <c r="Z12" s="4" t="n"/>
+      <c r="AA12" s="8" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3066,6 +3328,27 @@
         <f>IF(SUM($F13:$I13)=0,0,M13*I13/SUM($F13:$I13))</f>
         <v/>
       </c>
+      <c r="X13" s="7">
+        <f>Inputs!$B$44</f>
+        <v/>
+      </c>
+      <c r="Y13" s="5">
+        <f>B13*X13</f>
+        <v/>
+      </c>
+      <c r="Z13" s="5">
+        <f>C13*X13</f>
+        <v/>
+      </c>
+      <c r="AA13" s="7">
+        <f>Inputs!$C$45</f>
+        <v/>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>steel</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3158,6 +3441,27 @@
         <f>IF(SUM($F14:$I14)=0,0,M14*I14/SUM($F14:$I14))</f>
         <v/>
       </c>
+      <c r="X14" s="7">
+        <f>Inputs!$B$44</f>
+        <v/>
+      </c>
+      <c r="Y14" s="5">
+        <f>B14*X14</f>
+        <v/>
+      </c>
+      <c r="Z14" s="5">
+        <f>C14*X14</f>
+        <v/>
+      </c>
+      <c r="AA14" s="7">
+        <f>Inputs!$C$45</f>
+        <v/>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>steel</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3250,6 +3554,27 @@
         <f>IF(SUM($F15:$I15)=0,0,M15*I15/SUM($F15:$I15))</f>
         <v/>
       </c>
+      <c r="X15" s="7">
+        <f>Inputs!$B$44</f>
+        <v/>
+      </c>
+      <c r="Y15" s="5">
+        <f>B15*X15</f>
+        <v/>
+      </c>
+      <c r="Z15" s="5">
+        <f>C15*X15</f>
+        <v/>
+      </c>
+      <c r="AA15" s="7">
+        <f>Inputs!$C$45</f>
+        <v/>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>steel</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3343,6 +3668,27 @@
         <f>IF(SUM($F16:$I16)=0,0,M16*I16/SUM($F16:$I16))</f>
         <v/>
       </c>
+      <c r="X16" s="7">
+        <f>Inputs!$B$44</f>
+        <v/>
+      </c>
+      <c r="Y16" s="5">
+        <f>B16*X16</f>
+        <v/>
+      </c>
+      <c r="Z16" s="5">
+        <f>C16*X16</f>
+        <v/>
+      </c>
+      <c r="AA16" s="7">
+        <f>Inputs!$C$45</f>
+        <v/>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>steel</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3435,6 +3781,27 @@
         <f>IF(SUM($F17:$I17)=0,0,M17*I17/SUM($F17:$I17))</f>
         <v/>
       </c>
+      <c r="X17" s="7">
+        <f>Inputs!$B$44</f>
+        <v/>
+      </c>
+      <c r="Y17" s="5">
+        <f>B17*X17</f>
+        <v/>
+      </c>
+      <c r="Z17" s="5">
+        <f>C17*X17</f>
+        <v/>
+      </c>
+      <c r="AA17" s="7">
+        <f>Inputs!$C$45</f>
+        <v/>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>steel</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3527,6 +3894,27 @@
         <f>IF(SUM($F18:$I18)=0,0,M18*I18/SUM($F18:$I18))</f>
         <v/>
       </c>
+      <c r="X18" s="7">
+        <f>Inputs!$B$48</f>
+        <v/>
+      </c>
+      <c r="Y18" s="5">
+        <f>B18*X18</f>
+        <v/>
+      </c>
+      <c r="Z18" s="5">
+        <f>C18*X18</f>
+        <v/>
+      </c>
+      <c r="AA18" s="7">
+        <f>Inputs!$B$48</f>
+        <v/>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3619,6 +4007,25 @@
         <f>IF(SUM($F19:$I19)=0,0,M19*I19/SUM($F19:$I19))</f>
         <v/>
       </c>
+      <c r="X19" s="8" t="inlineStr">
+        <is>
+          <t>not estimated</t>
+        </is>
+      </c>
+      <c r="Y19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3711,6 +4118,25 @@
         <f>IF(SUM($F20:$I20)=0,0,M20*I20/SUM($F20:$I20))</f>
         <v/>
       </c>
+      <c r="X20" s="8" t="inlineStr">
+        <is>
+          <t>not estimated</t>
+        </is>
+      </c>
+      <c r="Y20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3804,6 +4230,25 @@
         <f>IF(SUM($F21:$I21)=0,0,M21*I21/SUM($F21:$I21))</f>
         <v/>
       </c>
+      <c r="X21" s="8" t="inlineStr">
+        <is>
+          <t>not estimated</t>
+        </is>
+      </c>
+      <c r="Y21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -3813,339 +4258,451 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>Total mass, building and contents (tons)</t>
         </is>
       </c>
-      <c r="B24" s="8">
+      <c r="B24" s="10">
         <f>SUM(B3:B21)</f>
         <v/>
       </c>
-      <c r="C24" s="8">
+      <c r="C24" s="10">
         <f>SUM(C3:C21)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>Total excluding concrete (tons)</t>
         </is>
       </c>
-      <c r="B25" s="8">
+      <c r="B25" s="10">
         <f>B24-B3-B4-B5</f>
         <v/>
       </c>
-      <c r="C25" s="8">
+      <c r="C25" s="10">
         <f>C24-C3-C4-C5</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>Replaced by SUPERWOOD, by horizon</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>Immediate — incumbent mass replaced (tons)</t>
         </is>
       </c>
-      <c r="B28" s="10">
+      <c r="B28" s="12">
         <f>SUMPRODUCT(B3:B21,F3:F21)</f>
         <v/>
       </c>
-      <c r="C28" s="10">
+      <c r="C28" s="12">
         <f>SUMPRODUCT(C3:C21,F3:F21)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>Immediate — SUPERWOOD required (tons)</t>
         </is>
       </c>
-      <c r="B29" s="10">
+      <c r="B29" s="12">
         <f>SUM(P3:P21)</f>
         <v/>
       </c>
-      <c r="C29" s="10">
+      <c r="C29" s="12">
         <f>SUM(T3:T21)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>Immediate — SUPERWOOD required (sf)</t>
         </is>
       </c>
-      <c r="B30" s="10">
+      <c r="B30" s="12">
         <f>B29*1000/Derived!B6</f>
         <v/>
       </c>
-      <c r="C30" s="10">
+      <c r="C30" s="12">
         <f>C29*1000/Derived!C6</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Immediate — years of SuperMill One output</t>
         </is>
       </c>
-      <c r="B31" s="11">
+      <c r="B31" s="13">
         <f>B29/Derived!B7</f>
         <v/>
       </c>
-      <c r="C31" s="11">
+      <c r="C31" s="13">
         <f>C29/Derived!C7</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>Soon — incumbent mass replaced (tons)</t>
         </is>
       </c>
-      <c r="B33" s="10">
+      <c r="B33" s="12">
         <f>SUMPRODUCT(B3:B21,G3:G21)</f>
         <v/>
       </c>
-      <c r="C33" s="10">
+      <c r="C33" s="12">
         <f>SUMPRODUCT(C3:C21,G3:G21)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>Soon — SUPERWOOD required (tons)</t>
         </is>
       </c>
-      <c r="B34" s="10">
+      <c r="B34" s="12">
         <f>SUM(Q3:Q21)</f>
         <v/>
       </c>
-      <c r="C34" s="10">
+      <c r="C34" s="12">
         <f>SUM(U3:U21)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>Soon — years of SuperMill Two output</t>
         </is>
       </c>
-      <c r="B35" s="11">
+      <c r="B35" s="13">
         <f>B34/Derived!B8</f>
         <v/>
       </c>
-      <c r="C35" s="11">
+      <c r="C35" s="13">
         <f>C34/Derived!C8</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>Medium term — incumbent mass replaced (tons)</t>
         </is>
       </c>
-      <c r="B37" s="10">
+      <c r="B37" s="12">
         <f>SUMPRODUCT(B3:B21,H3:H21)</f>
         <v/>
       </c>
-      <c r="C37" s="10">
+      <c r="C37" s="12">
         <f>SUMPRODUCT(C3:C21,H3:H21)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>Medium term — SUPERWOOD required (tons)</t>
         </is>
       </c>
-      <c r="B38" s="10">
+      <c r="B38" s="12">
         <f>SUM(R3:R21)</f>
         <v/>
       </c>
-      <c r="C38" s="10">
+      <c r="C38" s="12">
         <f>SUM(V3:V21)</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>Medium term — years of SuperMill Two output</t>
         </is>
       </c>
-      <c r="B39" s="11">
+      <c r="B39" s="13">
         <f>B38/Derived!B8</f>
         <v/>
       </c>
-      <c r="C39" s="11">
+      <c r="C39" s="13">
         <f>C38/Derived!C8</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>Long term — incumbent mass replaced (tons)</t>
         </is>
       </c>
-      <c r="B41" s="10">
+      <c r="B41" s="12">
         <f>SUMPRODUCT(B3:B21,I3:I21)</f>
         <v/>
       </c>
-      <c r="C41" s="10">
+      <c r="C41" s="12">
         <f>SUMPRODUCT(C3:C21,I3:I21)</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>Long term — SUPERWOOD required (tons)</t>
         </is>
       </c>
-      <c r="B42" s="10">
+      <c r="B42" s="12">
         <f>SUM(S3:S21)</f>
         <v/>
       </c>
-      <c r="C42" s="10">
+      <c r="C42" s="12">
         <f>SUM(W3:W21)</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="inlineStr">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t>Long term — years of SuperMill Two output</t>
         </is>
       </c>
-      <c r="B43" s="11">
+      <c r="B43" s="13">
         <f>B42/Derived!B8</f>
         <v/>
       </c>
-      <c r="C43" s="11">
+      <c r="C43" s="13">
         <f>C42/Derived!C8</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="7" t="inlineStr">
+      <c r="A45" s="9" t="inlineStr">
         <is>
           <t>Cumulative incumbent mass replaced (tons)</t>
         </is>
       </c>
-      <c r="B45" s="8">
+      <c r="B45" s="10">
         <f>SUM(J3:J21)</f>
         <v/>
       </c>
-      <c r="C45" s="8">
+      <c r="C45" s="10">
         <f>SUM(K3:K21)</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="7" t="inlineStr">
+      <c r="A46" s="9" t="inlineStr">
         <is>
           <t>Cumulative SUPERWOOD required (tons)</t>
         </is>
       </c>
-      <c r="B46" s="8">
+      <c r="B46" s="10">
         <f>SUM(L3:L21)</f>
         <v/>
       </c>
-      <c r="C46" s="8">
+      <c r="C46" s="10">
         <f>SUM(M3:M21)</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="9" t="inlineStr">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t>Cumulative years of SuperMill Two output</t>
         </is>
       </c>
-      <c r="B47" s="11">
+      <c r="B47" s="13">
         <f>B46/Derived!B8</f>
         <v/>
       </c>
-      <c r="C47" s="11">
+      <c r="C47" s="13">
         <f>C46/Derived!C8</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="9" t="inlineStr">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>Share of total mass replaced</t>
         </is>
       </c>
-      <c r="B48" s="12">
+      <c r="B48" s="14">
         <f>B45/B24</f>
         <v/>
       </c>
-      <c r="C48" s="12">
+      <c r="C48" s="14">
         <f>C45/C24</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="9" t="inlineStr">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>Share of ex-concrete mass replaced through the medium term (excludes foundations)</t>
         </is>
       </c>
-      <c r="B49" s="12">
+      <c r="B49" s="14">
         <f>(B45-B41)/B25</f>
         <v/>
       </c>
-      <c r="C49" s="12">
+      <c r="C49" s="14">
         <f>(C45-C41)/C25</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="7" t="inlineStr">
+      <c r="A50" s="9" t="inlineStr">
         <is>
           <t>Not replaced by SUPERWOOD (tons)</t>
         </is>
       </c>
-      <c r="B50" s="8">
+      <c r="B50" s="10">
         <f>B24-B45</f>
         <v/>
       </c>
-      <c r="C50" s="8">
+      <c r="C50" s="10">
         <f>C24-C45</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="9" t="inlineStr">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t>Not replaced, share of total</t>
         </is>
       </c>
-      <c r="B51" s="12">
+      <c r="B51" s="14">
         <f>B50/B24</f>
         <v/>
       </c>
-      <c r="C51" s="12">
+      <c r="C51" s="14">
         <f>C50/C24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>EMBODIED CARBON — building materials (equipment not estimated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>Embodied carbon, building materials (t CO₂e)</t>
+        </is>
+      </c>
+      <c r="B54" s="10">
+        <f>SUM(Y3:Y21)</f>
+        <v/>
+      </c>
+      <c r="C54" s="10">
+        <f>SUM(Z3:Z21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  of which steel (t CO₂e)</t>
+        </is>
+      </c>
+      <c r="B55" s="12">
+        <f>SUMIF(AB3:AB21,"steel",Y3:Y21)</f>
+        <v/>
+      </c>
+      <c r="C55" s="12">
+        <f>SUMIF(AB3:AB21,"steel",Z3:Z21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  of which concrete (t CO₂e)</t>
+        </is>
+      </c>
+      <c r="B56" s="12">
+        <f>SUMIF(AB3:AB21,"concrete",Y3:Y21)</f>
+        <v/>
+      </c>
+      <c r="C56" s="12">
+        <f>SUMIF(AB3:AB21,"concrete",Z3:Z21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>Steel share of building-materials carbon</t>
+        </is>
+      </c>
+      <c r="B57" s="14">
+        <f>B55/B54</f>
+        <v/>
+      </c>
+      <c r="C57" s="14">
+        <f>C55/C54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>Concrete share of building-materials carbon</t>
+        </is>
+      </c>
+      <c r="B58" s="14">
+        <f>B56/B54</f>
+        <v/>
+      </c>
+      <c r="C58" s="14">
+        <f>C56/C54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>Steel above the slab (steel excl. rebar), share of building-materials carbon</t>
+        </is>
+      </c>
+      <c r="B59" s="14">
+        <f>(B55-Y6)/B54</f>
+        <v/>
+      </c>
+      <c r="C59" s="14">
+        <f>(C55-Z6)/C54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>Steel share if steel is recycled (EAF factor, high end)</t>
+        </is>
+      </c>
+      <c r="B60" s="14">
+        <f>SUMPRODUCT(B3:B21,AA3:AA21,--(AB3:AB21="steel"))/SUMPRODUCT(B3:B21,AA3:AA21)</f>
+        <v/>
+      </c>
+      <c r="C60" s="14">
+        <f>SUMPRODUCT(C3:C21,AA3:AA21,--(AB3:AB21="steel"))/SUMPRODUCT(C3:C21,AA3:AA21)</f>
         <v/>
       </c>
     </row>
@@ -4198,11 +4755,11 @@
           <t>Number of buildings</t>
         </is>
       </c>
-      <c r="B2" s="13">
+      <c r="B2" s="15">
         <f>Inputs!$B$3*Inputs!$B$2/Inputs!$B$4</f>
         <v/>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="15">
         <f>Inputs!$C$3*Inputs!$C$2/Inputs!$C$4</f>
         <v/>
       </c>
@@ -4218,11 +4775,11 @@
           <t>Exterior wall area, sf</t>
         </is>
       </c>
-      <c r="B3" s="13">
+      <c r="B3" s="15">
         <f>B2*Inputs!$B$5</f>
         <v/>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="15">
         <f>C2*Inputs!$C$5</f>
         <v/>
       </c>
@@ -4238,11 +4795,11 @@
           <t>Exterior wall area, m²</t>
         </is>
       </c>
-      <c r="B4" s="13">
+      <c r="B4" s="15">
         <f>B3*0.092903</f>
         <v/>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="15">
         <f>C3*0.092903</f>
         <v/>
       </c>
@@ -4258,11 +4815,11 @@
           <t>Fence face area, sf</t>
         </is>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="15">
         <f>Inputs!$B$7*1000*Inputs!$B$8/0.092903</f>
         <v/>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="15">
         <f>Inputs!$C$7*1000*Inputs!$C$8/0.092903</f>
         <v/>
       </c>
@@ -4278,11 +4835,11 @@
           <t>SUPERWOOD board mass per sf</t>
         </is>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="15">
         <f>Inputs!$B$36/1000*Inputs!$B$37*0.092903</f>
         <v/>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="15">
         <f>Inputs!$C$36/1000*Inputs!$C$37*0.092903</f>
         <v/>
       </c>
@@ -4298,11 +4855,11 @@
           <t>SuperMill One output in tonnes</t>
         </is>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="15">
         <f>Inputs!$B$38*B6/1000</f>
         <v/>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="15">
         <f>Inputs!$C$38*C6/1000</f>
         <v/>
       </c>
@@ -4318,11 +4875,11 @@
           <t>SuperMill Two output in tonnes</t>
         </is>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="15">
         <f>Inputs!$B$39*B6/1000</f>
         <v/>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="15">
         <f>Inputs!$C$39*C6/1000</f>
         <v/>
       </c>
@@ -4423,11 +4980,11 @@
         </is>
       </c>
       <c r="B2" s="4">
-        <f>'1 GW data center'!B28*Inputs!$B$44</f>
+        <f>SUMPRODUCT('1 GW data center'!B3:B21,'1 GW data center'!F3:F21,'1 GW data center'!X3:X21)</f>
         <v/>
       </c>
       <c r="C2" s="4">
-        <f>'1 GW data center'!C28*Inputs!$C$44</f>
+        <f>SUMPRODUCT('1 GW data center'!C3:C21,'1 GW data center'!F3:F21,'1 GW data center'!X3:X21)</f>
         <v/>
       </c>
       <c r="D2" s="4">
@@ -4447,11 +5004,11 @@
         <v/>
       </c>
       <c r="H2" s="4">
-        <f>'1 GW data center'!B28*Inputs!$B$45-D2</f>
+        <f>SUMPRODUCT('1 GW data center'!B3:B21,'1 GW data center'!F3:F21,'1 GW data center'!AA3:AA21)-D2</f>
         <v/>
       </c>
       <c r="I2" s="4">
-        <f>'1 GW data center'!C28*Inputs!$C$45-E2</f>
+        <f>SUMPRODUCT('1 GW data center'!C3:C21,'1 GW data center'!F3:F21,'1 GW data center'!AA3:AA21)-E2</f>
         <v/>
       </c>
       <c r="J2" s="4">
@@ -4470,11 +5027,11 @@
         </is>
       </c>
       <c r="B3" s="4">
-        <f>'1 GW data center'!B33*Inputs!$B$44</f>
+        <f>SUMPRODUCT('1 GW data center'!B3:B21,'1 GW data center'!G3:G21,'1 GW data center'!X3:X21)</f>
         <v/>
       </c>
       <c r="C3" s="4">
-        <f>'1 GW data center'!C33*Inputs!$C$44</f>
+        <f>SUMPRODUCT('1 GW data center'!C3:C21,'1 GW data center'!G3:G21,'1 GW data center'!X3:X21)</f>
         <v/>
       </c>
       <c r="D3" s="4">
@@ -4494,11 +5051,11 @@
         <v/>
       </c>
       <c r="H3" s="4">
-        <f>'1 GW data center'!B33*Inputs!$B$45-D3</f>
+        <f>SUMPRODUCT('1 GW data center'!B3:B21,'1 GW data center'!G3:G21,'1 GW data center'!AA3:AA21)-D3</f>
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>'1 GW data center'!C33*Inputs!$C$45-E3</f>
+        <f>SUMPRODUCT('1 GW data center'!C3:C21,'1 GW data center'!G3:G21,'1 GW data center'!AA3:AA21)-E3</f>
         <v/>
       </c>
       <c r="J3" s="4">
@@ -4517,11 +5074,11 @@
         </is>
       </c>
       <c r="B4" s="4">
-        <f>'1 GW data center'!B37*Inputs!$B$44</f>
+        <f>SUMPRODUCT('1 GW data center'!B3:B21,'1 GW data center'!H3:H21,'1 GW data center'!X3:X21)</f>
         <v/>
       </c>
       <c r="C4" s="4">
-        <f>'1 GW data center'!C37*Inputs!$C$44</f>
+        <f>SUMPRODUCT('1 GW data center'!C3:C21,'1 GW data center'!H3:H21,'1 GW data center'!X3:X21)</f>
         <v/>
       </c>
       <c r="D4" s="4">
@@ -4541,11 +5098,11 @@
         <v/>
       </c>
       <c r="H4" s="4">
-        <f>'1 GW data center'!B37*Inputs!$B$45-D4</f>
+        <f>SUMPRODUCT('1 GW data center'!B3:B21,'1 GW data center'!H3:H21,'1 GW data center'!AA3:AA21)-D4</f>
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>'1 GW data center'!C37*Inputs!$C$45-E4</f>
+        <f>SUMPRODUCT('1 GW data center'!C3:C21,'1 GW data center'!H3:H21,'1 GW data center'!AA3:AA21)-E4</f>
         <v/>
       </c>
       <c r="J4" s="4">
@@ -4560,15 +5117,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Long term (foundation concrete)</t>
+          <t>Long term (concrete, rebar, server enclosures)</t>
         </is>
       </c>
       <c r="B5" s="4">
-        <f>'1 GW data center'!B41*Inputs!$B$35</f>
+        <f>SUMPRODUCT('1 GW data center'!B3:B21,'1 GW data center'!I3:I21,'1 GW data center'!X3:X21)</f>
         <v/>
       </c>
       <c r="C5" s="4">
-        <f>'1 GW data center'!C41*Inputs!$C$35</f>
+        <f>SUMPRODUCT('1 GW data center'!C3:C21,'1 GW data center'!I3:I21,'1 GW data center'!X3:X21)</f>
         <v/>
       </c>
       <c r="D5" s="4">
@@ -4588,11 +5145,11 @@
         <v/>
       </c>
       <c r="H5" s="4">
-        <f>"n/a"</f>
+        <f>SUMPRODUCT('1 GW data center'!B3:B21,'1 GW data center'!I3:I21,'1 GW data center'!AA3:AA21)-D5</f>
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>"n/a"</f>
+        <f>SUMPRODUCT('1 GW data center'!C3:C21,'1 GW data center'!I3:I21,'1 GW data center'!AA3:AA21)-E5</f>
         <v/>
       </c>
       <c r="J5" s="4">
@@ -4607,7 +5164,635 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pre-LCA projections (LCA under way with Prof. Ming Hu, University of Notre Dame). Long-term row uses a concrete factor (Inputs co2_conc) and treats the rebar in foundations at the concrete factor — conservative. Biogenic storage reported separately (EN 15804 module C).</t>
+          <t>Pre-LCA projections (LCA under way with Prof. Ming Hu, University of Notre Dame). Each row is valued at its own factor (column X on the main sheet): concrete rows at co2_conc, steel rows including rebar at co2_steel, interior finishes at co2_mixed; equipment rows (including the long-term server enclosures) carry no factor, so the long-term row counts concrete and rebar only. The EAF column revalues steel rows at the recycled-steel factor (high end). Equipment rows carry no factor. Biogenic storage reported separately (EN 15804 module C).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="64" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Above-ground component (contents included)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Low tons</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>High tons</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Steel fraction — low</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Steel fraction — high</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Low steel tons</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>High steel tons</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Basis for the fraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Structural steel — primary frame (columns, girders)</t>
+        </is>
+      </c>
+      <c r="B2" s="5">
+        <f>'1 GW data center'!B7</f>
+        <v/>
+      </c>
+      <c r="C2" s="5">
+        <f>'1 GW data center'!C7</f>
+        <v/>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="5">
+        <f>B2*D2</f>
+        <v/>
+      </c>
+      <c r="G2" s="5">
+        <f>C2*E2</f>
+        <v/>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>steel by definition</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Structural steel — roof trusses, joists, roof deck, girts</t>
+        </is>
+      </c>
+      <c r="B3" s="5">
+        <f>'1 GW data center'!B8</f>
+        <v/>
+      </c>
+      <c r="C3" s="5">
+        <f>'1 GW data center'!C8</f>
+        <v/>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5">
+        <f>B3*D3</f>
+        <v/>
+      </c>
+      <c r="G3" s="5">
+        <f>C3*E3</f>
+        <v/>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>steel by definition</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Exterior skins — metal panel / IMP (metal-panel case)</t>
+        </is>
+      </c>
+      <c r="B4" s="5">
+        <f>'1 GW data center'!B9</f>
+        <v/>
+      </c>
+      <c r="C4" s="5">
+        <f>'1 GW data center'!C9</f>
+        <v/>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F4" s="5">
+        <f>B4*D4</f>
+        <v/>
+      </c>
+      <c r="G4" s="5">
+        <f>C4*E4</f>
+        <v/>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>steel-faced IMP; some aluminum</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Louvers and yard / mechanical screens</t>
+        </is>
+      </c>
+      <c r="B5" s="5">
+        <f>'1 GW data center'!B10</f>
+        <v/>
+      </c>
+      <c r="C5" s="5">
+        <f>'1 GW data center'!C10</f>
+        <v/>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F5" s="5">
+        <f>B5*D5</f>
+        <v/>
+      </c>
+      <c r="G5" s="5">
+        <f>C5*E5</f>
+        <v/>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>aluminum common</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Security and staff-area fencing</t>
+        </is>
+      </c>
+      <c r="B6" s="5">
+        <f>'1 GW data center'!B11</f>
+        <v/>
+      </c>
+      <c r="C6" s="5">
+        <f>'1 GW data center'!C11</f>
+        <v/>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="5">
+        <f>B6*D6</f>
+        <v/>
+      </c>
+      <c r="G6" s="5">
+        <f>C6*E6</f>
+        <v/>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>chain-link, palisade, posts</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Platforms, walkways, mezzanines, railings, tray supports</t>
+        </is>
+      </c>
+      <c r="B7" s="5">
+        <f>'1 GW data center'!B13</f>
+        <v/>
+      </c>
+      <c r="C7" s="5">
+        <f>'1 GW data center'!C13</f>
+        <v/>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="5">
+        <f>B7*D7</f>
+        <v/>
+      </c>
+      <c r="G7" s="5">
+        <f>C7*E7</f>
+        <v/>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>structural and misc. steel</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Acoustic barriers, enclosures, HVAC separations</t>
+        </is>
+      </c>
+      <c r="B8" s="5">
+        <f>'1 GW data center'!B14</f>
+        <v/>
+      </c>
+      <c r="C8" s="5">
+        <f>'1 GW data center'!C14</f>
+        <v/>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F8" s="5">
+        <f>B8*D8</f>
+        <v/>
+      </c>
+      <c r="G8" s="5">
+        <f>C8*E8</f>
+        <v/>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>steel panels with absorptive fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Racking and equipment supports</t>
+        </is>
+      </c>
+      <c r="B9" s="5">
+        <f>'1 GW data center'!B15</f>
+        <v/>
+      </c>
+      <c r="C9" s="5">
+        <f>'1 GW data center'!C15</f>
+        <v/>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="5">
+        <f>B9*D9</f>
+        <v/>
+      </c>
+      <c r="G9" s="5">
+        <f>C9*E9</f>
+        <v/>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>steel</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Other tray, containment, doors, misc. metals</t>
+        </is>
+      </c>
+      <c r="B10" s="5">
+        <f>'1 GW data center'!B16</f>
+        <v/>
+      </c>
+      <c r="C10" s="5">
+        <f>'1 GW data center'!C16</f>
+        <v/>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F10" s="5">
+        <f>B10*D10</f>
+        <v/>
+      </c>
+      <c r="G10" s="5">
+        <f>C10*E10</f>
+        <v/>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>mostly steel, some aluminum</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ducting, plenums and air-distribution sheet metal</t>
+        </is>
+      </c>
+      <c r="B11" s="5">
+        <f>'1 GW data center'!B17</f>
+        <v/>
+      </c>
+      <c r="C11" s="5">
+        <f>'1 GW data center'!C17</f>
+        <v/>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="5">
+        <f>B11*D11</f>
+        <v/>
+      </c>
+      <c r="G11" s="5">
+        <f>C11*E11</f>
+        <v/>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>galvanized steel</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Interior finishes, backplanes, trim (admin / office)</t>
+        </is>
+      </c>
+      <c r="B12" s="5">
+        <f>'1 GW data center'!B18</f>
+        <v/>
+      </c>
+      <c r="C12" s="5">
+        <f>'1 GW data center'!C18</f>
+        <v/>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F12" s="5">
+        <f>B12*D12</f>
+        <v/>
+      </c>
+      <c r="G12" s="5">
+        <f>C12*E12</f>
+        <v/>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>gypsum, wood, steel studs</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Electrical equipment and conductors</t>
+        </is>
+      </c>
+      <c r="B13" s="5">
+        <f>'1 GW data center'!B19</f>
+        <v/>
+      </c>
+      <c r="C13" s="5">
+        <f>'1 GW data center'!C19</f>
+        <v/>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F13" s="5">
+        <f>B13*D13</f>
+        <v/>
+      </c>
+      <c r="G13" s="5">
+        <f>C13*E13</f>
+        <v/>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>enclosures, cores, gensets, switchgear; rest copper, oil, batteries</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Mechanical equipment, piping, loop water</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>'1 GW data center'!B20</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>'1 GW data center'!C20</f>
+        <v/>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F14" s="5">
+        <f>B14*D14</f>
+        <v/>
+      </c>
+      <c r="G14" s="5">
+        <f>C14*E14</f>
+        <v/>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>chillers, piping steel; water, copper, refrigerant not</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>IT — servers and racks</t>
+        </is>
+      </c>
+      <c r="B15" s="5">
+        <f>'1 GW data center'!B21</f>
+        <v/>
+      </c>
+      <c r="C15" s="5">
+        <f>'1 GW data center'!C21</f>
+        <v/>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F15" s="5">
+        <f>B15*D15</f>
+        <v/>
+      </c>
+      <c r="G15" s="5">
+        <f>C15*E15</f>
+        <v/>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>steel chassis and racks; aluminum, PCBs, copper</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Above-ground mass, contents included (tons)</t>
+        </is>
+      </c>
+      <c r="B17" s="4">
+        <f>SUM(B2:B15)</f>
+        <v/>
+      </c>
+      <c r="C17" s="4">
+        <f>SUM(C2:C15)</f>
+        <v/>
+      </c>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Steel in it (tons)</t>
+        </is>
+      </c>
+      <c r="B18" s="4">
+        <f>SUM(F2:F15)</f>
+        <v/>
+      </c>
+      <c r="C18" s="4">
+        <f>SUM(G2:G15)</f>
+        <v/>
+      </c>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Steel share of above-ground mass</t>
+        </is>
+      </c>
+      <c r="B19" s="16">
+        <f>B18/B17</f>
+        <v/>
+      </c>
+      <c r="C19" s="16">
+        <f>C18/C17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Steel share including slab rebar (at-grade steel)</t>
+        </is>
+      </c>
+      <c r="B20" s="16">
+        <f>(B18+'1 GW data center'!B6)/(B17+'1 GW data center'!B6)</f>
+        <v/>
+      </c>
+      <c r="C20" s="16">
+        <f>(C18+'1 GW data center'!C6)/(C17+'1 GW data center'!C6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>Structure and envelope only (first five rows)</t>
+        </is>
+      </c>
+      <c r="B21" s="16">
+        <f>SUM(F2:F6)/SUM(B2:B6)</f>
+        <v/>
+      </c>
+      <c r="C21" s="16">
+        <f>SUM(G2:G6)/SUM(C2:C6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Excludes slab on grade, paving, foundations and all concrete. Steel fractions per component are estimates [conf: L] (yellow cells). Printed band on the deck: 50–80% (Alex, 2026-09-04). Precast/tilt-up walls would add above-ground concrete and lower the share sharply.</t>
         </is>
       </c>
     </row>

--- a/superwood-datacenter-investor/analyses/materials-mass-and-replacement.xlsx
+++ b/superwood-datacenter-investor/analyses/materials-mass-and-replacement.xlsx
@@ -82,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -102,6 +102,7 @@
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5179,7 +5180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -5237,22 +5238,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Structural steel — primary frame (columns, girders)</t>
+          <t>Precast / tilt-up perimeter walls (precast case)</t>
         </is>
       </c>
       <c r="B2" s="5">
-        <f>'1 GW data center'!B7</f>
+        <f>'1 GW data center'!B5</f>
         <v/>
       </c>
       <c r="C2" s="5">
-        <f>'1 GW data center'!C7</f>
+        <f>'1 GW data center'!C5</f>
         <v/>
       </c>
       <c r="D2" s="6" t="n">
-        <v>1</v>
+        <v>0.03</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="F2" s="5">
         <f>B2*D2</f>
@@ -5264,22 +5265,22 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>steel by definition</t>
+          <t>rebar in precast/tilt-up panels; row is zero unless Inputs walls_precast = 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Structural steel — roof trusses, joists, roof deck, girts</t>
+          <t>Structural steel — primary frame (columns, girders)</t>
         </is>
       </c>
       <c r="B3" s="5">
-        <f>'1 GW data center'!B8</f>
+        <f>'1 GW data center'!B7</f>
         <v/>
       </c>
       <c r="C3" s="5">
-        <f>'1 GW data center'!C8</f>
+        <f>'1 GW data center'!C7</f>
         <v/>
       </c>
       <c r="D3" s="6" t="n">
@@ -5305,22 +5306,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Exterior skins — metal panel / IMP (metal-panel case)</t>
+          <t>Structural steel — roof trusses, joists, roof deck, girts</t>
         </is>
       </c>
       <c r="B4" s="5">
-        <f>'1 GW data center'!B9</f>
+        <f>'1 GW data center'!B8</f>
         <v/>
       </c>
       <c r="C4" s="5">
-        <f>'1 GW data center'!C9</f>
+        <f>'1 GW data center'!C8</f>
         <v/>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F4" s="5">
         <f>B4*D4</f>
@@ -5332,29 +5333,29 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>steel-faced IMP; some aluminum</t>
+          <t>steel by definition</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Louvers and yard / mechanical screens</t>
+          <t>Exterior skins — metal panel / IMP (metal-panel case)</t>
         </is>
       </c>
       <c r="B5" s="5">
-        <f>'1 GW data center'!B10</f>
+        <f>'1 GW data center'!B9</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>'1 GW data center'!C10</f>
+        <f>'1 GW data center'!C9</f>
         <v/>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.4</v>
+        <v>0.85</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>0.7</v>
+        <v>0.95</v>
       </c>
       <c r="F5" s="5">
         <f>B5*D5</f>
@@ -5366,29 +5367,29 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>aluminum common</t>
+          <t>steel-faced IMP; some aluminum</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Security and staff-area fencing</t>
+          <t>Louvers and yard / mechanical screens</t>
         </is>
       </c>
       <c r="B6" s="5">
-        <f>'1 GW data center'!B11</f>
+        <f>'1 GW data center'!B10</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>'1 GW data center'!C11</f>
+        <f>'1 GW data center'!C10</f>
         <v/>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="F6" s="5">
         <f>B6*D6</f>
@@ -5400,26 +5401,26 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>chain-link, palisade, posts</t>
+          <t>aluminum common</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Platforms, walkways, mezzanines, railings, tray supports</t>
+          <t>Security and staff-area fencing</t>
         </is>
       </c>
       <c r="B7" s="5">
-        <f>'1 GW data center'!B13</f>
+        <f>'1 GW data center'!B11</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>'1 GW data center'!C13</f>
+        <f>'1 GW data center'!C11</f>
         <v/>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>1</v>
@@ -5434,29 +5435,29 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>structural and misc. steel</t>
+          <t>chain-link, palisade, posts</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Acoustic barriers, enclosures, HVAC separations</t>
+          <t>Platforms, walkways, mezzanines, railings, tray supports</t>
         </is>
       </c>
       <c r="B8" s="5">
-        <f>'1 GW data center'!B14</f>
+        <f>'1 GW data center'!B13</f>
         <v/>
       </c>
       <c r="C8" s="5">
-        <f>'1 GW data center'!C14</f>
+        <f>'1 GW data center'!C13</f>
         <v/>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.7</v>
+        <v>0.95</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F8" s="5">
         <f>B8*D8</f>
@@ -5468,29 +5469,29 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>steel panels with absorptive fill</t>
+          <t>structural and misc. steel</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Racking and equipment supports</t>
+          <t>Acoustic barriers, enclosures, HVAC separations</t>
         </is>
       </c>
       <c r="B9" s="5">
-        <f>'1 GW data center'!B15</f>
+        <f>'1 GW data center'!B14</f>
         <v/>
       </c>
       <c r="C9" s="5">
-        <f>'1 GW data center'!C15</f>
+        <f>'1 GW data center'!C14</f>
         <v/>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.95</v>
+        <v>0.7</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F9" s="5">
         <f>B9*D9</f>
@@ -5502,29 +5503,29 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>steel panels with absorptive fill</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Other tray, containment, doors, misc. metals</t>
+          <t>Racking and equipment supports</t>
         </is>
       </c>
       <c r="B10" s="5">
-        <f>'1 GW data center'!B16</f>
+        <f>'1 GW data center'!B15</f>
         <v/>
       </c>
       <c r="C10" s="5">
-        <f>'1 GW data center'!C16</f>
+        <f>'1 GW data center'!C15</f>
         <v/>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F10" s="5">
         <f>B10*D10</f>
@@ -5536,29 +5537,29 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>mostly steel, some aluminum</t>
+          <t>steel</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ducting, plenums and air-distribution sheet metal</t>
+          <t>Other tray, containment, doors, misc. metals</t>
         </is>
       </c>
       <c r="B11" s="5">
-        <f>'1 GW data center'!B17</f>
+        <f>'1 GW data center'!B16</f>
         <v/>
       </c>
       <c r="C11" s="5">
-        <f>'1 GW data center'!C17</f>
+        <f>'1 GW data center'!C16</f>
         <v/>
       </c>
       <c r="D11" s="6" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E11" s="6" t="n">
         <v>0.95</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>1</v>
       </c>
       <c r="F11" s="5">
         <f>B11*D11</f>
@@ -5570,29 +5571,29 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>galvanized steel</t>
+          <t>mostly steel, some aluminum</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Interior finishes, backplanes, trim (admin / office)</t>
+          <t>Ducting, plenums and air-distribution sheet metal</t>
         </is>
       </c>
       <c r="B12" s="5">
-        <f>'1 GW data center'!B18</f>
+        <f>'1 GW data center'!B17</f>
         <v/>
       </c>
       <c r="C12" s="5">
-        <f>'1 GW data center'!C18</f>
+        <f>'1 GW data center'!C17</f>
         <v/>
       </c>
       <c r="D12" s="6" t="n">
-        <v>0.2</v>
+        <v>0.95</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="F12" s="5">
         <f>B12*D12</f>
@@ -5604,29 +5605,29 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>gypsum, wood, steel studs</t>
+          <t>galvanized steel</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Electrical equipment and conductors</t>
+          <t>Interior finishes, backplanes, trim (admin / office)</t>
         </is>
       </c>
       <c r="B13" s="5">
-        <f>'1 GW data center'!B19</f>
+        <f>'1 GW data center'!B18</f>
         <v/>
       </c>
       <c r="C13" s="5">
-        <f>'1 GW data center'!C19</f>
+        <f>'1 GW data center'!C18</f>
         <v/>
       </c>
       <c r="D13" s="6" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>0.65</v>
+        <v>0.4</v>
       </c>
       <c r="F13" s="5">
         <f>B13*D13</f>
@@ -5638,26 +5639,26 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>enclosures, cores, gensets, switchgear; rest copper, oil, batteries</t>
+          <t>gypsum, wood, steel studs</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mechanical equipment, piping, loop water</t>
+          <t>Electrical equipment and conductors</t>
         </is>
       </c>
       <c r="B14" s="5">
-        <f>'1 GW data center'!B20</f>
+        <f>'1 GW data center'!B19</f>
         <v/>
       </c>
       <c r="C14" s="5">
-        <f>'1 GW data center'!C20</f>
+        <f>'1 GW data center'!C19</f>
         <v/>
       </c>
       <c r="D14" s="6" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>0.65</v>
@@ -5672,29 +5673,29 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>chillers, piping steel; water, copper, refrigerant not</t>
+          <t>enclosures, cores, gensets, switchgear; rest copper, oil, batteries</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IT — servers and racks</t>
+          <t>Mechanical equipment, piping, loop water</t>
         </is>
       </c>
       <c r="B15" s="5">
-        <f>'1 GW data center'!B21</f>
+        <f>'1 GW data center'!B20</f>
         <v/>
       </c>
       <c r="C15" s="5">
-        <f>'1 GW data center'!C21</f>
+        <f>'1 GW data center'!C20</f>
         <v/>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="F15" s="5">
         <f>B15*D15</f>
@@ -5706,39 +5707,56 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
+          <t>chillers, piping steel; water, copper, refrigerant not</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>IT — servers and racks</t>
+        </is>
+      </c>
+      <c r="B16" s="5">
+        <f>'1 GW data center'!B21</f>
+        <v/>
+      </c>
+      <c r="C16" s="5">
+        <f>'1 GW data center'!C21</f>
+        <v/>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F16" s="5">
+        <f>B16*D16</f>
+        <v/>
+      </c>
+      <c r="G16" s="5">
+        <f>C16*E16</f>
+        <v/>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>steel chassis and racks; aluminum, PCBs, copper</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>Above-ground mass, contents included (tons)</t>
-        </is>
-      </c>
-      <c r="B17" s="4">
-        <f>SUM(B2:B15)</f>
-        <v/>
-      </c>
-      <c r="C17" s="4">
-        <f>SUM(C2:C15)</f>
-        <v/>
-      </c>
-      <c r="F17" s="4" t="n"/>
-      <c r="G17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>Steel in it (tons)</t>
+          <t>Above-ground mass, contents included (tons)</t>
         </is>
       </c>
       <c r="B18" s="4">
-        <f>SUM(F2:F15)</f>
+        <f>SUM(B2:B16)</f>
         <v/>
       </c>
       <c r="C18" s="4">
-        <f>SUM(G2:G15)</f>
+        <f>SUM(C2:C16)</f>
         <v/>
       </c>
       <c r="F18" s="4" t="n"/>
@@ -5747,52 +5765,136 @@
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>Steel share of above-ground mass</t>
-        </is>
-      </c>
-      <c r="B19" s="16">
-        <f>B18/B17</f>
-        <v/>
-      </c>
-      <c r="C19" s="16">
-        <f>C18/C17</f>
-        <v/>
-      </c>
+          <t>Steel in it (tons)</t>
+        </is>
+      </c>
+      <c r="B19" s="4">
+        <f>SUM(F2:F16)</f>
+        <v/>
+      </c>
+      <c r="C19" s="4">
+        <f>SUM(G2:G16)</f>
+        <v/>
+      </c>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>Steel share including slab rebar (at-grade steel)</t>
+          <t>Steel share of above-ground mass</t>
         </is>
       </c>
       <c r="B20" s="16">
-        <f>(B18+'1 GW data center'!B6)/(B17+'1 GW data center'!B6)</f>
+        <f>B19/B18</f>
         <v/>
       </c>
       <c r="C20" s="16">
-        <f>(C18+'1 GW data center'!C6)/(C17+'1 GW data center'!C6)</f>
+        <f>C19/C18</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
+          <t>Steel share including slab rebar (at-grade steel)</t>
+        </is>
+      </c>
+      <c r="B21" s="16">
+        <f>(B19+'1 GW data center'!B6)/(B18+'1 GW data center'!B6)</f>
+        <v/>
+      </c>
+      <c r="C21" s="16">
+        <f>(C19+'1 GW data center'!C6)/(C18+'1 GW data center'!C6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
           <t>Structure and envelope only (first five rows)</t>
         </is>
       </c>
-      <c r="B21" s="16">
-        <f>SUM(F2:F6)/SUM(B2:B6)</f>
-        <v/>
-      </c>
-      <c r="C21" s="16">
-        <f>SUM(G2:G6)/SUM(C2:C6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Excludes slab on grade, paving, foundations and all concrete. Steel fractions per component are estimates [conf: L] (yellow cells). Printed band on the deck: 50–80% (Alex, 2026-09-04). Precast/tilt-up walls would add above-ground concrete and lower the share sharply.</t>
+      <c r="B22" s="16">
+        <f>SUM(F2:F7)/SUM(B2:B7)</f>
+        <v/>
+      </c>
+      <c r="C22" s="16">
+        <f>SUM(G2:G7)/SUM(C2:C7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>WALL SYSTEM CASES (independent of the Inputs toggle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Tilt-up / precast wall mass if chosen (tons)</t>
+        </is>
+      </c>
+      <c r="B25" s="17">
+        <f>Derived!B4*Inputs!$B$14*Inputs!$B$12</f>
+        <v/>
+      </c>
+      <c r="C25" s="17">
+        <f>Derived!C4*Inputs!$C$14*Inputs!$C$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Metal-panel skin mass if chosen (tons)</t>
+        </is>
+      </c>
+      <c r="B26" s="17">
+        <f>Derived!B4*Inputs!$B$19/1000</f>
+        <v/>
+      </c>
+      <c r="C26" s="17">
+        <f>Derived!C4*Inputs!$C$19/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>Steel share — metal-panel walls</t>
+        </is>
+      </c>
+      <c r="B27" s="16">
+        <f>(B19-F2-F5+B26*D5)/(B18-B2-B5+B26)</f>
+        <v/>
+      </c>
+      <c r="C27" s="16">
+        <f>(C19-F2-F5+C26*E5)/(C18-C2-C5+C26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>Steel share — tilt-up / precast concrete walls</t>
+        </is>
+      </c>
+      <c r="B28" s="16">
+        <f>(B19-F2-F5+B25*D2)/(B18-B2-B5+B25)</f>
+        <v/>
+      </c>
+      <c r="C28" s="16">
+        <f>(C19-G2-G5+C25*E2)/(C18-C2-C5+C25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Excludes slab on grade, paving and foundations. The wall system matters: the main block follows Inputs walls_precast (0 = metal panel, 1 = tilt-up/precast); the two case rows above force each wall system regardless of the toggle. Steel fractions per component are estimates [conf: L] (yellow cells). Printed band on the deck: 50–80% (Alex, 2026-09-04), covering both wall systems.</t>
         </is>
       </c>
     </row>

--- a/superwood-datacenter-investor/analyses/materials-mass-and-replacement.xlsx
+++ b/superwood-datacenter-investor/analyses/materials-mass-and-replacement.xlsx
@@ -701,7 +701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -1451,14 +1451,14 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Share of IT mass that is server and equipment enclosures (boxes), replaceable long term</t>
+          <t>Share of all concrete that is foundations, footings, piers and equipment pads</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
         <v>0.4</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1467,26 +1467,26 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>estimated [L]; Alex 2026-09-04</t>
+          <t>estimated [L]</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Server boxes eventually; the electronics never</t>
+          <t>Remainder is slab on grade, paving and yard</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Share of all concrete that is foundations, footings, piers and equipment pads</t>
+          <t>Long-term technical potential: share of slab-on-grade and paving concrete replaceable</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>0.4</v>
+        <v>0.75</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1495,26 +1495,26 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>estimated [L]</t>
+          <t>asserted-internal (Alex, 2026-09-01) [L]</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Remainder is slab on grade, paving and yard</t>
+          <t>Technical potential, not a plan; no design or code pathway yet</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Long-term technical potential: share of slab-on-grade and paving concrete replaceable</t>
+          <t>Long-term technical potential: share of foundations, footings, piers and pads replaceable</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1528,53 +1528,53 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Technical potential, not a plan; no design or code pathway yet</t>
+          <t>Technical potential, not a plan</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Long-term technical potential: share of foundations, footings, piers and pads replaceable</t>
+          <t>kg SUPERWOOD per kg of concrete replaced</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>0.9</v>
+        <v>0.05</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>0.9</v>
+        <v>0.15</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>share</t>
+          <t>kg/kg</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>asserted-internal (Alex, 2026-09-01) [L]</t>
+          <t>estimated [L]</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Technical potential, not a plan</t>
+          <t>Lightweight insulated wood-foundation concept; no design exists yet</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>kg SUPERWOOD per kg of concrete replaced</t>
+          <t>Ducting, plenums and air-distribution sheet metal</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>0.05</v>
+        <v>3</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>0.15</v>
+        <v>8</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>kg/kg</t>
+          <t>t/MW</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1584,86 +1584,82 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lightweight insulated wood-foundation concept; no design exists yet</t>
+          <t>Separate from the mechanical-equipment row</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ducting, plenums and air-distribution sheet metal</t>
+          <t>Concrete emissions</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>3</v>
+        <v>0.12</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>8</v>
+        <v>0.12</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>t/MW</t>
+          <t>kg CO₂e/kg</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>estimated [L]</t>
+          <t>industry range [M]</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Separate from the mechanical-equipment row</t>
+          <t>Ready-mix, cradle to gate; typical 0.10–0.15</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Concrete emissions</t>
+          <t>SUPERWOOD average board thickness</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>0.12</v>
+        <v>7.2</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>0.12</v>
+        <v>7.2</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>kg CO₂e/kg</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>industry range [M]</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Ready-mix, cradle to gate; typical 0.10–0.15</t>
-        </is>
-      </c>
+          <t>internal TEM basis [H]</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SUPERWOOD average board thickness</t>
+          <t>SUPERWOOD density</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>7.2</v>
+        <v>1300</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>7.2</v>
+        <v>1300</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>kg/m³</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>internal TEM basis [H]</t>
+          <t>internal TEM [H]</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -1671,23 +1667,23 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SUPERWOOD density</t>
+          <t>SuperMill One output</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>1300</v>
+        <v>1000000</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>1300</v>
+        <v>1000000</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>kg/m³</t>
+          <t>sf/yr</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>internal TEM [H]</t>
+          <t>internal [H]</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -1695,14 +1691,14 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SuperMill One output</t>
+          <t>SuperMill Two output</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>1000000</v>
+        <v>36000000</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>1000000</v>
+        <v>36000000</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1719,42 +1715,46 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SuperMill Two output</t>
+          <t>Structural substitution: kg SUPERWOOD per kg steel replaced</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>36000000</v>
+        <v>0.3</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>36000000</v>
+        <v>0.6</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>sf/yr</t>
+          <t>kg/kg</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>internal [H]</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
+          <t>estimated [L]</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Engineering-stamped per element (Fast + Epp) before external use</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Structural substitution: kg SUPERWOOD per kg steel replaced</t>
+          <t>SUPERWOOD in a hybrid wall panel replacing precast</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>0.3</v>
+        <v>20</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>0.6</v>
+        <v>40</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>kg/kg</t>
+          <t>kg/m²</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1764,25 +1764,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Engineering-stamped per element (Fast + Epp) before external use</t>
+          <t>Panel design unsettled</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SUPERWOOD in a hybrid wall panel replacing precast</t>
+          <t>Addressable share of other tray / containment / doors (medium term)</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>20</v>
+        <v>0.5</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>40</v>
+        <v>0.5</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>kg/m²</t>
+          <t>share</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1790,75 +1790,71 @@
           <t>estimated [L]</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Panel design unsettled</t>
-        </is>
-      </c>
+      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Addressable share of other tray / containment / doors (medium term)</t>
+          <t>Count rebar as addressable in the long term? (0/1)</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>share</t>
+          <t>flag</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>estimated [L]</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
+          <t>choice</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Rebar is a frontier market with no pathway; off by default</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Count rebar as addressable in the long term? (0/1)</t>
+          <t>Steel emissions, global average (BF-BOF)</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>flag</t>
+          <t>kg CO₂e/kg</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>choice</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Rebar is a frontier market with no pathway; off by default</t>
-        </is>
-      </c>
+          <t>published-class [M]</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Steel emissions, global average (BF-BOF)</t>
+          <t>Steel emissions, recycled (EAF)</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1867,7 +1863,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>published-class [M]</t>
+          <t>industry range [M]</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -1875,14 +1871,14 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Steel emissions, recycled (EAF)</t>
+          <t>SUPERWOOD manufacturing emissions</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1891,22 +1887,26 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>industry range [M]</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
+          <t>internal, pre-LCA [L]</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Canva DCII deck; LCA under way, Prof. Ming Hu, Notre Dame</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SUPERWOOD manufacturing emissions</t>
+          <t>SUPERWOOD biogenic carbon stored</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1920,21 +1920,21 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Canva DCII deck; LCA under way, Prof. Ming Hu, Notre Dame</t>
+          <t>Report separately; module C release under EN 15804</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SUPERWOOD biogenic carbon stored</t>
+          <t>Interior finishes emissions (gypsum, wood, steel studs — mixed)</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1943,38 +1943,10 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>internal, pre-LCA [L]</t>
+          <t>estimated [L]</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
-        <is>
-          <t>Report separately; module C release under EN 15804</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Interior finishes emissions (gypsum, wood, steel studs — mixed)</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>kg CO₂e/kg</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>estimated [L]</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
         <is>
           <t>Used only for the interior finishes row</t>
         </is>
@@ -2197,11 +2169,11 @@
         </is>
       </c>
       <c r="B3" s="5">
-        <f>Inputs!$B$11*(1-Inputs!$B$30)*Inputs!$B$12*Inputs!$B$2-B5</f>
+        <f>Inputs!$B$11*(1-Inputs!$B$29)*Inputs!$B$12*Inputs!$B$2-B5</f>
         <v/>
       </c>
       <c r="C3" s="5">
-        <f>Inputs!$C$11*(1-Inputs!$C$30)*Inputs!$C$12*Inputs!$C$2-C5</f>
+        <f>Inputs!$C$11*(1-Inputs!$C$29)*Inputs!$C$12*Inputs!$C$2-C5</f>
         <v/>
       </c>
       <c r="D3" s="5">
@@ -2222,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="6">
-        <f>Inputs!$B$31</f>
+        <f>Inputs!$B$30</f>
         <v/>
       </c>
       <c r="J3" s="5">
@@ -2234,11 +2206,11 @@
         <v/>
       </c>
       <c r="L3" s="5">
-        <f>J3*Inputs!$B$33</f>
+        <f>J3*Inputs!$B$32</f>
         <v/>
       </c>
       <c r="M3" s="5">
-        <f>K3*Inputs!$C$33</f>
+        <f>K3*Inputs!$C$32</f>
         <v/>
       </c>
       <c r="N3" t="inlineStr">
@@ -2283,7 +2255,7 @@
         <v/>
       </c>
       <c r="X3" s="7">
-        <f>Inputs!$B$35</f>
+        <f>Inputs!$B$34</f>
         <v/>
       </c>
       <c r="Y3" s="5">
@@ -2295,7 +2267,7 @@
         <v/>
       </c>
       <c r="AA3" s="7">
-        <f>Inputs!$B$35</f>
+        <f>Inputs!$B$34</f>
         <v/>
       </c>
       <c r="AB3" t="inlineStr">
@@ -2311,11 +2283,11 @@
         </is>
       </c>
       <c r="B4" s="5">
-        <f>Inputs!$B$11*Inputs!$B$30*Inputs!$B$12*Inputs!$B$2</f>
+        <f>Inputs!$B$11*Inputs!$B$29*Inputs!$B$12*Inputs!$B$2</f>
         <v/>
       </c>
       <c r="C4" s="5">
-        <f>Inputs!$C$11*Inputs!$C$30*Inputs!$C$12*Inputs!$C$2</f>
+        <f>Inputs!$C$11*Inputs!$C$29*Inputs!$C$12*Inputs!$C$2</f>
         <v/>
       </c>
       <c r="D4" s="5">
@@ -2336,7 +2308,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="6">
-        <f>Inputs!$B$32</f>
+        <f>Inputs!$B$31</f>
         <v/>
       </c>
       <c r="J4" s="5">
@@ -2348,11 +2320,11 @@
         <v/>
       </c>
       <c r="L4" s="5">
-        <f>J4*Inputs!$B$33</f>
+        <f>J4*Inputs!$B$32</f>
         <v/>
       </c>
       <c r="M4" s="5">
-        <f>K4*Inputs!$C$33</f>
+        <f>K4*Inputs!$C$32</f>
         <v/>
       </c>
       <c r="N4" t="inlineStr">
@@ -2397,7 +2369,7 @@
         <v/>
       </c>
       <c r="X4" s="7">
-        <f>Inputs!$B$35</f>
+        <f>Inputs!$B$34</f>
         <v/>
       </c>
       <c r="Y4" s="5">
@@ -2409,7 +2381,7 @@
         <v/>
       </c>
       <c r="AA4" s="7">
-        <f>Inputs!$B$35</f>
+        <f>Inputs!$B$34</f>
         <v/>
       </c>
       <c r="AB4" t="inlineStr">
@@ -2461,11 +2433,11 @@
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>SUM($F5:$I5)*Inputs!$B$13*Derived!B4*Inputs!$B$41/1000</f>
+        <f>SUM($F5:$I5)*Inputs!$B$13*Derived!B4*Inputs!$B$40/1000</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>SUM($F5:$I5)*Inputs!$C$13*Derived!C4*Inputs!$C$41/1000</f>
+        <f>SUM($F5:$I5)*Inputs!$C$13*Derived!C4*Inputs!$C$40/1000</f>
         <v/>
       </c>
       <c r="N5" t="inlineStr">
@@ -2510,7 +2482,7 @@
         <v/>
       </c>
       <c r="X5" s="7">
-        <f>Inputs!$B$35</f>
+        <f>Inputs!$B$34</f>
         <v/>
       </c>
       <c r="Y5" s="5">
@@ -2522,7 +2494,7 @@
         <v/>
       </c>
       <c r="AA5" s="7">
-        <f>Inputs!$B$35</f>
+        <f>Inputs!$B$34</f>
         <v/>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2563,7 +2535,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="6">
-        <f>Inputs!$B$30*Inputs!$B$32+(1-Inputs!$B$30)*Inputs!$B$31</f>
+        <f>Inputs!$B$29*Inputs!$B$31+(1-Inputs!$B$29)*Inputs!$B$30</f>
         <v/>
       </c>
       <c r="J6" s="5">
@@ -2575,11 +2547,11 @@
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>J6*Inputs!$B$40</f>
+        <f>J6*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>K6*Inputs!$C$40</f>
+        <f>K6*Inputs!$C$39</f>
         <v/>
       </c>
       <c r="N6" t="inlineStr">
@@ -2624,7 +2596,7 @@
         <v/>
       </c>
       <c r="X6" s="7">
-        <f>Inputs!$B$44</f>
+        <f>Inputs!$B$43</f>
         <v/>
       </c>
       <c r="Y6" s="5">
@@ -2636,7 +2608,7 @@
         <v/>
       </c>
       <c r="AA6" s="7">
-        <f>Inputs!$C$45</f>
+        <f>Inputs!$C$44</f>
         <v/>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2688,11 +2660,11 @@
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>J7*Inputs!$B$40</f>
+        <f>J7*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>K7*Inputs!$C$40</f>
+        <f>K7*Inputs!$C$39</f>
         <v/>
       </c>
       <c r="N7" t="inlineStr">
@@ -2737,7 +2709,7 @@
         <v/>
       </c>
       <c r="X7" s="7">
-        <f>Inputs!$B$44</f>
+        <f>Inputs!$B$43</f>
         <v/>
       </c>
       <c r="Y7" s="5">
@@ -2749,7 +2721,7 @@
         <v/>
       </c>
       <c r="AA7" s="7">
-        <f>Inputs!$C$45</f>
+        <f>Inputs!$C$44</f>
         <v/>
       </c>
       <c r="AB7" t="inlineStr">
@@ -2801,11 +2773,11 @@
         <v/>
       </c>
       <c r="L8" s="5">
-        <f>J8*Inputs!$B$40</f>
+        <f>J8*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="M8" s="5">
-        <f>K8*Inputs!$C$40</f>
+        <f>K8*Inputs!$C$39</f>
         <v/>
       </c>
       <c r="N8" t="inlineStr">
@@ -2850,7 +2822,7 @@
         <v/>
       </c>
       <c r="X8" s="7">
-        <f>Inputs!$B$44</f>
+        <f>Inputs!$B$43</f>
         <v/>
       </c>
       <c r="Y8" s="5">
@@ -2862,7 +2834,7 @@
         <v/>
       </c>
       <c r="AA8" s="7">
-        <f>Inputs!$C$45</f>
+        <f>Inputs!$C$44</f>
         <v/>
       </c>
       <c r="AB8" t="inlineStr">
@@ -2963,7 +2935,7 @@
         <v/>
       </c>
       <c r="X9" s="7">
-        <f>Inputs!$B$44</f>
+        <f>Inputs!$B$43</f>
         <v/>
       </c>
       <c r="Y9" s="5">
@@ -2975,7 +2947,7 @@
         <v/>
       </c>
       <c r="AA9" s="7">
-        <f>Inputs!$C$45</f>
+        <f>Inputs!$C$44</f>
         <v/>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3076,7 +3048,7 @@
         <v/>
       </c>
       <c r="X10" s="7">
-        <f>Inputs!$B$44</f>
+        <f>Inputs!$B$43</f>
         <v/>
       </c>
       <c r="Y10" s="5">
@@ -3088,7 +3060,7 @@
         <v/>
       </c>
       <c r="AA10" s="7">
-        <f>Inputs!$C$45</f>
+        <f>Inputs!$C$44</f>
         <v/>
       </c>
       <c r="AB10" t="inlineStr">
@@ -3189,7 +3161,7 @@
         <v/>
       </c>
       <c r="X11" s="7">
-        <f>Inputs!$B$44</f>
+        <f>Inputs!$B$43</f>
         <v/>
       </c>
       <c r="Y11" s="5">
@@ -3201,7 +3173,7 @@
         <v/>
       </c>
       <c r="AA11" s="7">
-        <f>Inputs!$C$45</f>
+        <f>Inputs!$C$44</f>
         <v/>
       </c>
       <c r="AB11" t="inlineStr">
@@ -3281,11 +3253,11 @@
         <v/>
       </c>
       <c r="L13" s="5">
-        <f>J13*Inputs!$B$40</f>
+        <f>J13*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="M13" s="5">
-        <f>K13*Inputs!$C$40</f>
+        <f>K13*Inputs!$C$39</f>
         <v/>
       </c>
       <c r="N13" t="inlineStr">
@@ -3330,7 +3302,7 @@
         <v/>
       </c>
       <c r="X13" s="7">
-        <f>Inputs!$B$44</f>
+        <f>Inputs!$B$43</f>
         <v/>
       </c>
       <c r="Y13" s="5">
@@ -3342,7 +3314,7 @@
         <v/>
       </c>
       <c r="AA13" s="7">
-        <f>Inputs!$C$45</f>
+        <f>Inputs!$C$44</f>
         <v/>
       </c>
       <c r="AB13" t="inlineStr">
@@ -3394,11 +3366,11 @@
         <v/>
       </c>
       <c r="L14" s="5">
-        <f>J14*Inputs!$B$40</f>
+        <f>J14*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="M14" s="5">
-        <f>K14*Inputs!$C$40</f>
+        <f>K14*Inputs!$C$39</f>
         <v/>
       </c>
       <c r="N14" t="inlineStr">
@@ -3443,7 +3415,7 @@
         <v/>
       </c>
       <c r="X14" s="7">
-        <f>Inputs!$B$44</f>
+        <f>Inputs!$B$43</f>
         <v/>
       </c>
       <c r="Y14" s="5">
@@ -3455,7 +3427,7 @@
         <v/>
       </c>
       <c r="AA14" s="7">
-        <f>Inputs!$C$45</f>
+        <f>Inputs!$C$44</f>
         <v/>
       </c>
       <c r="AB14" t="inlineStr">
@@ -3507,11 +3479,11 @@
         <v/>
       </c>
       <c r="L15" s="5">
-        <f>J15*Inputs!$B$40</f>
+        <f>J15*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="M15" s="5">
-        <f>K15*Inputs!$C$40</f>
+        <f>K15*Inputs!$C$39</f>
         <v/>
       </c>
       <c r="N15" t="inlineStr">
@@ -3556,7 +3528,7 @@
         <v/>
       </c>
       <c r="X15" s="7">
-        <f>Inputs!$B$44</f>
+        <f>Inputs!$B$43</f>
         <v/>
       </c>
       <c r="Y15" s="5">
@@ -3568,7 +3540,7 @@
         <v/>
       </c>
       <c r="AA15" s="7">
-        <f>Inputs!$C$45</f>
+        <f>Inputs!$C$44</f>
         <v/>
       </c>
       <c r="AB15" t="inlineStr">
@@ -3603,7 +3575,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="6">
-        <f>Inputs!$B$42</f>
+        <f>Inputs!$B$41</f>
         <v/>
       </c>
       <c r="H16" s="6" t="n">
@@ -3621,11 +3593,11 @@
         <v/>
       </c>
       <c r="L16" s="5">
-        <f>J16*Inputs!$B$40</f>
+        <f>J16*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="M16" s="5">
-        <f>K16*Inputs!$C$40</f>
+        <f>K16*Inputs!$C$39</f>
         <v/>
       </c>
       <c r="N16" t="inlineStr">
@@ -3670,7 +3642,7 @@
         <v/>
       </c>
       <c r="X16" s="7">
-        <f>Inputs!$B$44</f>
+        <f>Inputs!$B$43</f>
         <v/>
       </c>
       <c r="Y16" s="5">
@@ -3682,7 +3654,7 @@
         <v/>
       </c>
       <c r="AA16" s="7">
-        <f>Inputs!$C$45</f>
+        <f>Inputs!$C$44</f>
         <v/>
       </c>
       <c r="AB16" t="inlineStr">
@@ -3698,11 +3670,11 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>Inputs!$B$34*Inputs!$B$2</f>
+        <f>Inputs!$B$33*Inputs!$B$2</f>
         <v/>
       </c>
       <c r="C17" s="5">
-        <f>Inputs!$C$34*Inputs!$C$2</f>
+        <f>Inputs!$C$33*Inputs!$C$2</f>
         <v/>
       </c>
       <c r="D17" s="5">
@@ -3734,11 +3706,11 @@
         <v/>
       </c>
       <c r="L17" s="5">
-        <f>J17*Inputs!$B$40</f>
+        <f>J17*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="M17" s="5">
-        <f>K17*Inputs!$C$40</f>
+        <f>K17*Inputs!$C$39</f>
         <v/>
       </c>
       <c r="N17" t="inlineStr">
@@ -3783,7 +3755,7 @@
         <v/>
       </c>
       <c r="X17" s="7">
-        <f>Inputs!$B$44</f>
+        <f>Inputs!$B$43</f>
         <v/>
       </c>
       <c r="Y17" s="5">
@@ -3795,7 +3767,7 @@
         <v/>
       </c>
       <c r="AA17" s="7">
-        <f>Inputs!$C$45</f>
+        <f>Inputs!$C$44</f>
         <v/>
       </c>
       <c r="AB17" t="inlineStr">
@@ -3896,7 +3868,7 @@
         <v/>
       </c>
       <c r="X18" s="7">
-        <f>Inputs!$B$48</f>
+        <f>Inputs!$B$47</f>
         <v/>
       </c>
       <c r="Y18" s="5">
@@ -3908,7 +3880,7 @@
         <v/>
       </c>
       <c r="AA18" s="7">
-        <f>Inputs!$B$48</f>
+        <f>Inputs!$B$47</f>
         <v/>
       </c>
       <c r="AB18" t="inlineStr">
@@ -4170,9 +4142,8 @@
       <c r="H21" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I21" s="6">
-        <f>Inputs!$B$29</f>
-        <v/>
+      <c r="I21" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="J21" s="5">
         <f>B21*SUM($F21:$I21)</f>
@@ -4183,16 +4154,16 @@
         <v/>
       </c>
       <c r="L21" s="5">
-        <f>J21*Inputs!$B$40</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="M21" s="5">
-        <f>K21*Inputs!$C$40</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Server and equipment enclosures only (40% of IT mass, estimate); electronics never. Rack masses [H]; aggregate [L]</t>
+          <t>Servers, racks as shipped, and their enclosures are not replaced (Alex 2026-09-05; server boxes removed from the long-term horizon). Rack masses [H]; aggregate per MW [L]</t>
         </is>
       </c>
       <c r="O21" s="5">
@@ -4837,11 +4808,11 @@
         </is>
       </c>
       <c r="B6" s="15">
-        <f>Inputs!$B$36/1000*Inputs!$B$37*0.092903</f>
+        <f>Inputs!$B$35/1000*Inputs!$B$36*0.092903</f>
         <v/>
       </c>
       <c r="C6" s="15">
-        <f>Inputs!$C$36/1000*Inputs!$C$37*0.092903</f>
+        <f>Inputs!$C$35/1000*Inputs!$C$36*0.092903</f>
         <v/>
       </c>
       <c r="D6" t="inlineStr">
@@ -4857,11 +4828,11 @@
         </is>
       </c>
       <c r="B7" s="15">
-        <f>Inputs!$B$38*B6/1000</f>
+        <f>Inputs!$B$37*B6/1000</f>
         <v/>
       </c>
       <c r="C7" s="15">
-        <f>Inputs!$C$38*C6/1000</f>
+        <f>Inputs!$C$37*C6/1000</f>
         <v/>
       </c>
       <c r="D7" t="inlineStr">
@@ -4877,11 +4848,11 @@
         </is>
       </c>
       <c r="B8" s="15">
-        <f>Inputs!$B$39*B6/1000</f>
+        <f>Inputs!$B$38*B6/1000</f>
         <v/>
       </c>
       <c r="C8" s="15">
-        <f>Inputs!$C$39*C6/1000</f>
+        <f>Inputs!$C$38*C6/1000</f>
         <v/>
       </c>
       <c r="D8" t="inlineStr">
@@ -4989,11 +4960,11 @@
         <v/>
       </c>
       <c r="D2" s="4">
-        <f>'1 GW data center'!B29*Inputs!$B$46</f>
+        <f>'1 GW data center'!B29*Inputs!$B$45</f>
         <v/>
       </c>
       <c r="E2" s="4">
-        <f>'1 GW data center'!C29*Inputs!$C$46</f>
+        <f>'1 GW data center'!C29*Inputs!$C$45</f>
         <v/>
       </c>
       <c r="F2" s="4">
@@ -5013,11 +4984,11 @@
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>'1 GW data center'!B29*Inputs!$B$47</f>
+        <f>'1 GW data center'!B29*Inputs!$B$46</f>
         <v/>
       </c>
       <c r="K2" s="4">
-        <f>'1 GW data center'!C29*Inputs!$C$47</f>
+        <f>'1 GW data center'!C29*Inputs!$C$46</f>
         <v/>
       </c>
     </row>
@@ -5036,11 +5007,11 @@
         <v/>
       </c>
       <c r="D3" s="4">
-        <f>'1 GW data center'!B34*Inputs!$B$46</f>
+        <f>'1 GW data center'!B34*Inputs!$B$45</f>
         <v/>
       </c>
       <c r="E3" s="4">
-        <f>'1 GW data center'!C34*Inputs!$C$46</f>
+        <f>'1 GW data center'!C34*Inputs!$C$45</f>
         <v/>
       </c>
       <c r="F3" s="4">
@@ -5060,11 +5031,11 @@
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>'1 GW data center'!B34*Inputs!$B$47</f>
+        <f>'1 GW data center'!B34*Inputs!$B$46</f>
         <v/>
       </c>
       <c r="K3" s="4">
-        <f>'1 GW data center'!C34*Inputs!$C$47</f>
+        <f>'1 GW data center'!C34*Inputs!$C$46</f>
         <v/>
       </c>
     </row>
@@ -5083,11 +5054,11 @@
         <v/>
       </c>
       <c r="D4" s="4">
-        <f>'1 GW data center'!B38*Inputs!$B$46</f>
+        <f>'1 GW data center'!B38*Inputs!$B$45</f>
         <v/>
       </c>
       <c r="E4" s="4">
-        <f>'1 GW data center'!C38*Inputs!$C$46</f>
+        <f>'1 GW data center'!C38*Inputs!$C$45</f>
         <v/>
       </c>
       <c r="F4" s="4">
@@ -5107,18 +5078,18 @@
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>'1 GW data center'!B38*Inputs!$B$47</f>
+        <f>'1 GW data center'!B38*Inputs!$B$46</f>
         <v/>
       </c>
       <c r="K4" s="4">
-        <f>'1 GW data center'!C38*Inputs!$C$47</f>
+        <f>'1 GW data center'!C38*Inputs!$C$46</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Long term (concrete, rebar, server enclosures)</t>
+          <t>Long term (concrete, rebar)</t>
         </is>
       </c>
       <c r="B5" s="4">
@@ -5130,11 +5101,11 @@
         <v/>
       </c>
       <c r="D5" s="4">
-        <f>'1 GW data center'!B42*Inputs!$B$46</f>
+        <f>'1 GW data center'!B42*Inputs!$B$45</f>
         <v/>
       </c>
       <c r="E5" s="4">
-        <f>'1 GW data center'!C42*Inputs!$C$46</f>
+        <f>'1 GW data center'!C42*Inputs!$C$45</f>
         <v/>
       </c>
       <c r="F5" s="4">
@@ -5154,11 +5125,11 @@
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>'1 GW data center'!B42*Inputs!$B$47</f>
+        <f>'1 GW data center'!B42*Inputs!$B$46</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>'1 GW data center'!C42*Inputs!$C$47</f>
+        <f>'1 GW data center'!C42*Inputs!$C$46</f>
         <v/>
       </c>
     </row>

--- a/superwood-datacenter-investor/analyses/materials-mass-and-replacement.xlsx
+++ b/superwood-datacenter-investor/analyses/materials-mass-and-replacement.xlsx
@@ -701,7 +701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -1451,14 +1451,14 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Share of all concrete that is foundations, footings, piers and equipment pads</t>
+          <t>Share of IT mass that is server and equipment enclosures (boxes), replaceable long term</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
         <v>0.4</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1467,26 +1467,26 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>estimated [L]</t>
+          <t>estimated [L]; Alex 2026-09-04</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Remainder is slab on grade, paving and yard</t>
+          <t>Server boxes eventually; the electronics never</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Long-term technical potential: share of slab-on-grade and paving concrete replaceable</t>
+          <t>Share of all concrete that is foundations, footings, piers and equipment pads</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1495,26 +1495,26 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>asserted-internal (Alex, 2026-09-01) [L]</t>
+          <t>estimated [L]</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Technical potential, not a plan; no design or code pathway yet</t>
+          <t>Remainder is slab on grade, paving and yard</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Long-term technical potential: share of foundations, footings, piers and pads replaceable</t>
+          <t>Long-term technical potential: share of slab-on-grade and paving concrete replaceable</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1528,53 +1528,53 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Technical potential, not a plan</t>
+          <t>Technical potential, not a plan; no design or code pathway yet</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>kg SUPERWOOD per kg of concrete replaced</t>
+          <t>Long-term technical potential: share of foundations, footings, piers and pads replaceable</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>0.05</v>
+        <v>0.9</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>0.15</v>
+        <v>0.9</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>kg/kg</t>
+          <t>share</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>estimated [L]</t>
+          <t>asserted-internal (Alex, 2026-09-01) [L]</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lightweight insulated wood-foundation concept; no design exists yet</t>
+          <t>Technical potential, not a plan</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Ducting, plenums and air-distribution sheet metal</t>
+          <t>kg SUPERWOOD per kg of concrete replaced</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>3</v>
+        <v>0.05</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>8</v>
+        <v>0.15</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>t/MW</t>
+          <t>kg/kg</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1584,82 +1584,86 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Separate from the mechanical-equipment row</t>
+          <t>Lightweight insulated wood-foundation concept; no design exists yet</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Concrete emissions</t>
+          <t>Ducting, plenums and air-distribution sheet metal</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>0.12</v>
+        <v>3</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>0.12</v>
+        <v>8</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>kg CO₂e/kg</t>
+          <t>t/MW</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>industry range [M]</t>
+          <t>estimated [L]</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ready-mix, cradle to gate; typical 0.10–0.15</t>
+          <t>Separate from the mechanical-equipment row</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SUPERWOOD average board thickness</t>
+          <t>Concrete emissions</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>7.2</v>
+        <v>0.12</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>7.2</v>
+        <v>0.12</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>kg CO₂e/kg</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>internal TEM basis [H]</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
+          <t>industry range [M]</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Ready-mix, cradle to gate; typical 0.10–0.15</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SUPERWOOD density</t>
+          <t>SUPERWOOD average board thickness</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>1300</v>
+        <v>7.2</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>1300</v>
+        <v>7.2</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>kg/m³</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>internal TEM [H]</t>
+          <t>internal TEM basis [H]</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -1667,23 +1671,23 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SuperMill One output</t>
+          <t>SUPERWOOD density</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>1000000</v>
+        <v>1300</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>1000000</v>
+        <v>1300</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>sf/yr</t>
+          <t>kg/m³</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>internal [H]</t>
+          <t>internal TEM [H]</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -1691,14 +1695,14 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SuperMill Two output</t>
+          <t>SuperMill One output</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>36000000</v>
+        <v>1000000</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>36000000</v>
+        <v>1000000</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1715,46 +1719,42 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Structural substitution: kg SUPERWOOD per kg steel replaced</t>
+          <t>SuperMill Two output</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>0.3</v>
+        <v>36000000</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>0.6</v>
+        <v>36000000</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>kg/kg</t>
+          <t>sf/yr</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>estimated [L]</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Engineering-stamped per element (Fast + Epp) before external use</t>
-        </is>
-      </c>
+          <t>internal [H]</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SUPERWOOD in a hybrid wall panel replacing precast</t>
+          <t>Structural substitution: kg SUPERWOOD per kg steel replaced</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>20</v>
+        <v>0.3</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>40</v>
+        <v>0.6</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>kg/m²</t>
+          <t>kg/kg</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1764,25 +1764,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Panel design unsettled</t>
+          <t>Engineering-stamped per element (Fast + Epp) before external use</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Addressable share of other tray / containment / doors (medium term)</t>
+          <t>SUPERWOOD in a hybrid wall panel replacing precast</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>0.5</v>
+        <v>20</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>0.5</v>
+        <v>40</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>share</t>
+          <t>kg/m²</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1790,71 +1790,75 @@
           <t>estimated [L]</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Panel design unsettled</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Count rebar as addressable in the long term? (0/1)</t>
+          <t>Addressable share of other tray / containment / doors (medium term)</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>flag</t>
+          <t>share</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>choice</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Rebar is a frontier market with no pathway; off by default</t>
-        </is>
-      </c>
+          <t>estimated [L]</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Steel emissions, global average (BF-BOF)</t>
+          <t>Count rebar as addressable in the long term? (0/1)</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>kg CO₂e/kg</t>
+          <t>flag</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>published-class [M]</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
+          <t>choice</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Rebar is a frontier market with no pathway; off by default</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Steel emissions, recycled (EAF)</t>
+          <t>Steel emissions, global average (BF-BOF)</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1863,7 +1867,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>industry range [M]</t>
+          <t>published-class [M]</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -1871,14 +1875,14 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SUPERWOOD manufacturing emissions</t>
+          <t>Steel emissions, recycled (EAF)</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1887,26 +1891,22 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>internal, pre-LCA [L]</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Canva DCII deck; LCA under way, Prof. Ming Hu, Notre Dame</t>
-        </is>
-      </c>
+          <t>industry range [M]</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SUPERWOOD biogenic carbon stored</t>
+          <t>SUPERWOOD manufacturing emissions</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1920,33 +1920,61 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Report separately; module C release under EN 15804</t>
+          <t>Canva DCII deck; LCA under way, Prof. Ming Hu, Notre Dame</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>SUPERWOOD biogenic carbon stored</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>kg CO₂e/kg</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>internal, pre-LCA [L]</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Report separately; module C release under EN 15804</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>Interior finishes emissions (gypsum, wood, steel studs — mixed)</t>
         </is>
       </c>
-      <c r="B47" s="2" t="n">
+      <c r="B48" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C47" s="2" t="n">
+      <c r="C48" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>kg CO₂e/kg</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>estimated [L]</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Used only for the interior finishes row</t>
         </is>
@@ -2169,11 +2197,11 @@
         </is>
       </c>
       <c r="B3" s="5">
-        <f>Inputs!$B$11*(1-Inputs!$B$29)*Inputs!$B$12*Inputs!$B$2-B5</f>
+        <f>Inputs!$B$11*(1-Inputs!$B$30)*Inputs!$B$12*Inputs!$B$2-B5</f>
         <v/>
       </c>
       <c r="C3" s="5">
-        <f>Inputs!$C$11*(1-Inputs!$C$29)*Inputs!$C$12*Inputs!$C$2-C5</f>
+        <f>Inputs!$C$11*(1-Inputs!$C$30)*Inputs!$C$12*Inputs!$C$2-C5</f>
         <v/>
       </c>
       <c r="D3" s="5">
@@ -2194,7 +2222,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="6">
-        <f>Inputs!$B$30</f>
+        <f>Inputs!$B$31</f>
         <v/>
       </c>
       <c r="J3" s="5">
@@ -2206,11 +2234,11 @@
         <v/>
       </c>
       <c r="L3" s="5">
-        <f>J3*Inputs!$B$32</f>
+        <f>J3*Inputs!$B$33</f>
         <v/>
       </c>
       <c r="M3" s="5">
-        <f>K3*Inputs!$C$32</f>
+        <f>K3*Inputs!$C$33</f>
         <v/>
       </c>
       <c r="N3" t="inlineStr">
@@ -2255,7 +2283,7 @@
         <v/>
       </c>
       <c r="X3" s="7">
-        <f>Inputs!$B$34</f>
+        <f>Inputs!$B$35</f>
         <v/>
       </c>
       <c r="Y3" s="5">
@@ -2267,7 +2295,7 @@
         <v/>
       </c>
       <c r="AA3" s="7">
-        <f>Inputs!$B$34</f>
+        <f>Inputs!$B$35</f>
         <v/>
       </c>
       <c r="AB3" t="inlineStr">
@@ -2283,11 +2311,11 @@
         </is>
       </c>
       <c r="B4" s="5">
-        <f>Inputs!$B$11*Inputs!$B$29*Inputs!$B$12*Inputs!$B$2</f>
+        <f>Inputs!$B$11*Inputs!$B$30*Inputs!$B$12*Inputs!$B$2</f>
         <v/>
       </c>
       <c r="C4" s="5">
-        <f>Inputs!$C$11*Inputs!$C$29*Inputs!$C$12*Inputs!$C$2</f>
+        <f>Inputs!$C$11*Inputs!$C$30*Inputs!$C$12*Inputs!$C$2</f>
         <v/>
       </c>
       <c r="D4" s="5">
@@ -2308,7 +2336,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="6">
-        <f>Inputs!$B$31</f>
+        <f>Inputs!$B$32</f>
         <v/>
       </c>
       <c r="J4" s="5">
@@ -2320,11 +2348,11 @@
         <v/>
       </c>
       <c r="L4" s="5">
-        <f>J4*Inputs!$B$32</f>
+        <f>J4*Inputs!$B$33</f>
         <v/>
       </c>
       <c r="M4" s="5">
-        <f>K4*Inputs!$C$32</f>
+        <f>K4*Inputs!$C$33</f>
         <v/>
       </c>
       <c r="N4" t="inlineStr">
@@ -2369,7 +2397,7 @@
         <v/>
       </c>
       <c r="X4" s="7">
-        <f>Inputs!$B$34</f>
+        <f>Inputs!$B$35</f>
         <v/>
       </c>
       <c r="Y4" s="5">
@@ -2381,7 +2409,7 @@
         <v/>
       </c>
       <c r="AA4" s="7">
-        <f>Inputs!$B$34</f>
+        <f>Inputs!$B$35</f>
         <v/>
       </c>
       <c r="AB4" t="inlineStr">
@@ -2433,11 +2461,11 @@
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>SUM($F5:$I5)*Inputs!$B$13*Derived!B4*Inputs!$B$40/1000</f>
+        <f>SUM($F5:$I5)*Inputs!$B$13*Derived!B4*Inputs!$B$41/1000</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>SUM($F5:$I5)*Inputs!$C$13*Derived!C4*Inputs!$C$40/1000</f>
+        <f>SUM($F5:$I5)*Inputs!$C$13*Derived!C4*Inputs!$C$41/1000</f>
         <v/>
       </c>
       <c r="N5" t="inlineStr">
@@ -2482,7 +2510,7 @@
         <v/>
       </c>
       <c r="X5" s="7">
-        <f>Inputs!$B$34</f>
+        <f>Inputs!$B$35</f>
         <v/>
       </c>
       <c r="Y5" s="5">
@@ -2494,7 +2522,7 @@
         <v/>
       </c>
       <c r="AA5" s="7">
-        <f>Inputs!$B$34</f>
+        <f>Inputs!$B$35</f>
         <v/>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2535,7 +2563,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="6">
-        <f>Inputs!$B$29*Inputs!$B$31+(1-Inputs!$B$29)*Inputs!$B$30</f>
+        <f>Inputs!$B$30*Inputs!$B$32+(1-Inputs!$B$30)*Inputs!$B$31</f>
         <v/>
       </c>
       <c r="J6" s="5">
@@ -2547,11 +2575,11 @@
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>J6*Inputs!$B$39</f>
+        <f>J6*Inputs!$B$40</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>K6*Inputs!$C$39</f>
+        <f>K6*Inputs!$C$40</f>
         <v/>
       </c>
       <c r="N6" t="inlineStr">
@@ -2596,7 +2624,7 @@
         <v/>
       </c>
       <c r="X6" s="7">
-        <f>Inputs!$B$43</f>
+        <f>Inputs!$B$44</f>
         <v/>
       </c>
       <c r="Y6" s="5">
@@ -2608,7 +2636,7 @@
         <v/>
       </c>
       <c r="AA6" s="7">
-        <f>Inputs!$C$44</f>
+        <f>Inputs!$C$45</f>
         <v/>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2660,11 +2688,11 @@
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>J7*Inputs!$B$39</f>
+        <f>J7*Inputs!$B$40</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>K7*Inputs!$C$39</f>
+        <f>K7*Inputs!$C$40</f>
         <v/>
       </c>
       <c r="N7" t="inlineStr">
@@ -2709,7 +2737,7 @@
         <v/>
       </c>
       <c r="X7" s="7">
-        <f>Inputs!$B$43</f>
+        <f>Inputs!$B$44</f>
         <v/>
       </c>
       <c r="Y7" s="5">
@@ -2721,7 +2749,7 @@
         <v/>
       </c>
       <c r="AA7" s="7">
-        <f>Inputs!$C$44</f>
+        <f>Inputs!$C$45</f>
         <v/>
       </c>
       <c r="AB7" t="inlineStr">
@@ -2773,11 +2801,11 @@
         <v/>
       </c>
       <c r="L8" s="5">
-        <f>J8*Inputs!$B$39</f>
+        <f>J8*Inputs!$B$40</f>
         <v/>
       </c>
       <c r="M8" s="5">
-        <f>K8*Inputs!$C$39</f>
+        <f>K8*Inputs!$C$40</f>
         <v/>
       </c>
       <c r="N8" t="inlineStr">
@@ -2822,7 +2850,7 @@
         <v/>
       </c>
       <c r="X8" s="7">
-        <f>Inputs!$B$43</f>
+        <f>Inputs!$B$44</f>
         <v/>
       </c>
       <c r="Y8" s="5">
@@ -2834,7 +2862,7 @@
         <v/>
       </c>
       <c r="AA8" s="7">
-        <f>Inputs!$C$44</f>
+        <f>Inputs!$C$45</f>
         <v/>
       </c>
       <c r="AB8" t="inlineStr">
@@ -2935,7 +2963,7 @@
         <v/>
       </c>
       <c r="X9" s="7">
-        <f>Inputs!$B$43</f>
+        <f>Inputs!$B$44</f>
         <v/>
       </c>
       <c r="Y9" s="5">
@@ -2947,7 +2975,7 @@
         <v/>
       </c>
       <c r="AA9" s="7">
-        <f>Inputs!$C$44</f>
+        <f>Inputs!$C$45</f>
         <v/>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3048,7 +3076,7 @@
         <v/>
       </c>
       <c r="X10" s="7">
-        <f>Inputs!$B$43</f>
+        <f>Inputs!$B$44</f>
         <v/>
       </c>
       <c r="Y10" s="5">
@@ -3060,7 +3088,7 @@
         <v/>
       </c>
       <c r="AA10" s="7">
-        <f>Inputs!$C$44</f>
+        <f>Inputs!$C$45</f>
         <v/>
       </c>
       <c r="AB10" t="inlineStr">
@@ -3161,7 +3189,7 @@
         <v/>
       </c>
       <c r="X11" s="7">
-        <f>Inputs!$B$43</f>
+        <f>Inputs!$B$44</f>
         <v/>
       </c>
       <c r="Y11" s="5">
@@ -3173,7 +3201,7 @@
         <v/>
       </c>
       <c r="AA11" s="7">
-        <f>Inputs!$C$44</f>
+        <f>Inputs!$C$45</f>
         <v/>
       </c>
       <c r="AB11" t="inlineStr">
@@ -3253,11 +3281,11 @@
         <v/>
       </c>
       <c r="L13" s="5">
-        <f>J13*Inputs!$B$39</f>
+        <f>J13*Inputs!$B$40</f>
         <v/>
       </c>
       <c r="M13" s="5">
-        <f>K13*Inputs!$C$39</f>
+        <f>K13*Inputs!$C$40</f>
         <v/>
       </c>
       <c r="N13" t="inlineStr">
@@ -3302,7 +3330,7 @@
         <v/>
       </c>
       <c r="X13" s="7">
-        <f>Inputs!$B$43</f>
+        <f>Inputs!$B$44</f>
         <v/>
       </c>
       <c r="Y13" s="5">
@@ -3314,7 +3342,7 @@
         <v/>
       </c>
       <c r="AA13" s="7">
-        <f>Inputs!$C$44</f>
+        <f>Inputs!$C$45</f>
         <v/>
       </c>
       <c r="AB13" t="inlineStr">
@@ -3366,11 +3394,11 @@
         <v/>
       </c>
       <c r="L14" s="5">
-        <f>J14*Inputs!$B$39</f>
+        <f>J14*Inputs!$B$40</f>
         <v/>
       </c>
       <c r="M14" s="5">
-        <f>K14*Inputs!$C$39</f>
+        <f>K14*Inputs!$C$40</f>
         <v/>
       </c>
       <c r="N14" t="inlineStr">
@@ -3415,7 +3443,7 @@
         <v/>
       </c>
       <c r="X14" s="7">
-        <f>Inputs!$B$43</f>
+        <f>Inputs!$B$44</f>
         <v/>
       </c>
       <c r="Y14" s="5">
@@ -3427,7 +3455,7 @@
         <v/>
       </c>
       <c r="AA14" s="7">
-        <f>Inputs!$C$44</f>
+        <f>Inputs!$C$45</f>
         <v/>
       </c>
       <c r="AB14" t="inlineStr">
@@ -3479,11 +3507,11 @@
         <v/>
       </c>
       <c r="L15" s="5">
-        <f>J15*Inputs!$B$39</f>
+        <f>J15*Inputs!$B$40</f>
         <v/>
       </c>
       <c r="M15" s="5">
-        <f>K15*Inputs!$C$39</f>
+        <f>K15*Inputs!$C$40</f>
         <v/>
       </c>
       <c r="N15" t="inlineStr">
@@ -3528,7 +3556,7 @@
         <v/>
       </c>
       <c r="X15" s="7">
-        <f>Inputs!$B$43</f>
+        <f>Inputs!$B$44</f>
         <v/>
       </c>
       <c r="Y15" s="5">
@@ -3540,7 +3568,7 @@
         <v/>
       </c>
       <c r="AA15" s="7">
-        <f>Inputs!$C$44</f>
+        <f>Inputs!$C$45</f>
         <v/>
       </c>
       <c r="AB15" t="inlineStr">
@@ -3575,7 +3603,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="6">
-        <f>Inputs!$B$41</f>
+        <f>Inputs!$B$42</f>
         <v/>
       </c>
       <c r="H16" s="6" t="n">
@@ -3593,11 +3621,11 @@
         <v/>
       </c>
       <c r="L16" s="5">
-        <f>J16*Inputs!$B$39</f>
+        <f>J16*Inputs!$B$40</f>
         <v/>
       </c>
       <c r="M16" s="5">
-        <f>K16*Inputs!$C$39</f>
+        <f>K16*Inputs!$C$40</f>
         <v/>
       </c>
       <c r="N16" t="inlineStr">
@@ -3642,7 +3670,7 @@
         <v/>
       </c>
       <c r="X16" s="7">
-        <f>Inputs!$B$43</f>
+        <f>Inputs!$B$44</f>
         <v/>
       </c>
       <c r="Y16" s="5">
@@ -3654,7 +3682,7 @@
         <v/>
       </c>
       <c r="AA16" s="7">
-        <f>Inputs!$C$44</f>
+        <f>Inputs!$C$45</f>
         <v/>
       </c>
       <c r="AB16" t="inlineStr">
@@ -3670,11 +3698,11 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>Inputs!$B$33*Inputs!$B$2</f>
+        <f>Inputs!$B$34*Inputs!$B$2</f>
         <v/>
       </c>
       <c r="C17" s="5">
-        <f>Inputs!$C$33*Inputs!$C$2</f>
+        <f>Inputs!$C$34*Inputs!$C$2</f>
         <v/>
       </c>
       <c r="D17" s="5">
@@ -3706,11 +3734,11 @@
         <v/>
       </c>
       <c r="L17" s="5">
-        <f>J17*Inputs!$B$39</f>
+        <f>J17*Inputs!$B$40</f>
         <v/>
       </c>
       <c r="M17" s="5">
-        <f>K17*Inputs!$C$39</f>
+        <f>K17*Inputs!$C$40</f>
         <v/>
       </c>
       <c r="N17" t="inlineStr">
@@ -3755,7 +3783,7 @@
         <v/>
       </c>
       <c r="X17" s="7">
-        <f>Inputs!$B$43</f>
+        <f>Inputs!$B$44</f>
         <v/>
       </c>
       <c r="Y17" s="5">
@@ -3767,7 +3795,7 @@
         <v/>
       </c>
       <c r="AA17" s="7">
-        <f>Inputs!$C$44</f>
+        <f>Inputs!$C$45</f>
         <v/>
       </c>
       <c r="AB17" t="inlineStr">
@@ -3868,7 +3896,7 @@
         <v/>
       </c>
       <c r="X18" s="7">
-        <f>Inputs!$B$47</f>
+        <f>Inputs!$B$48</f>
         <v/>
       </c>
       <c r="Y18" s="5">
@@ -3880,7 +3908,7 @@
         <v/>
       </c>
       <c r="AA18" s="7">
-        <f>Inputs!$B$47</f>
+        <f>Inputs!$B$48</f>
         <v/>
       </c>
       <c r="AB18" t="inlineStr">
@@ -4142,8 +4170,9 @@
       <c r="H21" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I21" s="6" t="n">
-        <v>0</v>
+      <c r="I21" s="6">
+        <f>Inputs!$B$29</f>
+        <v/>
       </c>
       <c r="J21" s="5">
         <f>B21*SUM($F21:$I21)</f>
@@ -4154,16 +4183,16 @@
         <v/>
       </c>
       <c r="L21" s="5">
-        <f>0</f>
+        <f>J21*Inputs!$B$40</f>
         <v/>
       </c>
       <c r="M21" s="5">
-        <f>0</f>
+        <f>K21*Inputs!$C$40</f>
         <v/>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Servers, racks as shipped, and their enclosures are not replaced (Alex 2026-09-05; server boxes removed from the long-term horizon). Rack masses [H]; aggregate per MW [L]</t>
+          <t>Server and equipment enclosures only (40% of IT mass, estimate); electronics never. Rack masses [H]; aggregate [L]</t>
         </is>
       </c>
       <c r="O21" s="5">
@@ -4808,11 +4837,11 @@
         </is>
       </c>
       <c r="B6" s="15">
-        <f>Inputs!$B$35/1000*Inputs!$B$36*0.092903</f>
+        <f>Inputs!$B$36/1000*Inputs!$B$37*0.092903</f>
         <v/>
       </c>
       <c r="C6" s="15">
-        <f>Inputs!$C$35/1000*Inputs!$C$36*0.092903</f>
+        <f>Inputs!$C$36/1000*Inputs!$C$37*0.092903</f>
         <v/>
       </c>
       <c r="D6" t="inlineStr">
@@ -4828,11 +4857,11 @@
         </is>
       </c>
       <c r="B7" s="15">
-        <f>Inputs!$B$37*B6/1000</f>
+        <f>Inputs!$B$38*B6/1000</f>
         <v/>
       </c>
       <c r="C7" s="15">
-        <f>Inputs!$C$37*C6/1000</f>
+        <f>Inputs!$C$38*C6/1000</f>
         <v/>
       </c>
       <c r="D7" t="inlineStr">
@@ -4848,11 +4877,11 @@
         </is>
       </c>
       <c r="B8" s="15">
-        <f>Inputs!$B$38*B6/1000</f>
+        <f>Inputs!$B$39*B6/1000</f>
         <v/>
       </c>
       <c r="C8" s="15">
-        <f>Inputs!$C$38*C6/1000</f>
+        <f>Inputs!$C$39*C6/1000</f>
         <v/>
       </c>
       <c r="D8" t="inlineStr">
@@ -4960,11 +4989,11 @@
         <v/>
       </c>
       <c r="D2" s="4">
-        <f>'1 GW data center'!B29*Inputs!$B$45</f>
+        <f>'1 GW data center'!B29*Inputs!$B$46</f>
         <v/>
       </c>
       <c r="E2" s="4">
-        <f>'1 GW data center'!C29*Inputs!$C$45</f>
+        <f>'1 GW data center'!C29*Inputs!$C$46</f>
         <v/>
       </c>
       <c r="F2" s="4">
@@ -4984,11 +5013,11 @@
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>'1 GW data center'!B29*Inputs!$B$46</f>
+        <f>'1 GW data center'!B29*Inputs!$B$47</f>
         <v/>
       </c>
       <c r="K2" s="4">
-        <f>'1 GW data center'!C29*Inputs!$C$46</f>
+        <f>'1 GW data center'!C29*Inputs!$C$47</f>
         <v/>
       </c>
     </row>
@@ -5007,11 +5036,11 @@
         <v/>
       </c>
       <c r="D3" s="4">
-        <f>'1 GW data center'!B34*Inputs!$B$45</f>
+        <f>'1 GW data center'!B34*Inputs!$B$46</f>
         <v/>
       </c>
       <c r="E3" s="4">
-        <f>'1 GW data center'!C34*Inputs!$C$45</f>
+        <f>'1 GW data center'!C34*Inputs!$C$46</f>
         <v/>
       </c>
       <c r="F3" s="4">
@@ -5031,11 +5060,11 @@
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>'1 GW data center'!B34*Inputs!$B$46</f>
+        <f>'1 GW data center'!B34*Inputs!$B$47</f>
         <v/>
       </c>
       <c r="K3" s="4">
-        <f>'1 GW data center'!C34*Inputs!$C$46</f>
+        <f>'1 GW data center'!C34*Inputs!$C$47</f>
         <v/>
       </c>
     </row>
@@ -5054,11 +5083,11 @@
         <v/>
       </c>
       <c r="D4" s="4">
-        <f>'1 GW data center'!B38*Inputs!$B$45</f>
+        <f>'1 GW data center'!B38*Inputs!$B$46</f>
         <v/>
       </c>
       <c r="E4" s="4">
-        <f>'1 GW data center'!C38*Inputs!$C$45</f>
+        <f>'1 GW data center'!C38*Inputs!$C$46</f>
         <v/>
       </c>
       <c r="F4" s="4">
@@ -5078,18 +5107,18 @@
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>'1 GW data center'!B38*Inputs!$B$46</f>
+        <f>'1 GW data center'!B38*Inputs!$B$47</f>
         <v/>
       </c>
       <c r="K4" s="4">
-        <f>'1 GW data center'!C38*Inputs!$C$46</f>
+        <f>'1 GW data center'!C38*Inputs!$C$47</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Long term (concrete, rebar)</t>
+          <t>Long term (concrete, rebar, server enclosures)</t>
         </is>
       </c>
       <c r="B5" s="4">
@@ -5101,11 +5130,11 @@
         <v/>
       </c>
       <c r="D5" s="4">
-        <f>'1 GW data center'!B42*Inputs!$B$45</f>
+        <f>'1 GW data center'!B42*Inputs!$B$46</f>
         <v/>
       </c>
       <c r="E5" s="4">
-        <f>'1 GW data center'!C42*Inputs!$C$45</f>
+        <f>'1 GW data center'!C42*Inputs!$C$46</f>
         <v/>
       </c>
       <c r="F5" s="4">
@@ -5125,11 +5154,11 @@
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>'1 GW data center'!B42*Inputs!$B$46</f>
+        <f>'1 GW data center'!B42*Inputs!$B$47</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>'1 GW data center'!C42*Inputs!$C$46</f>
+        <f>'1 GW data center'!C42*Inputs!$C$47</f>
         <v/>
       </c>
     </row>

--- a/superwood-datacenter-investor/analyses/materials-mass-and-replacement.xlsx
+++ b/superwood-datacenter-investor/analyses/materials-mass-and-replacement.xlsx
@@ -701,7 +701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -1977,6 +1977,90 @@
       <c r="F48" t="inlineStr">
         <is>
           <t>Used only for the interior finishes row</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Steel share of electrical equipment mass (gensets, transformers, switchgear, UPS cabinets)</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>estimated [L]; Alex asked for the estimate 2026-09-05</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Cast iron and steel in engines, transformer cores and tanks, switchgear and UPS enclosures; copper, aluminum, oil and cells excluded</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Steel share of mechanical equipment mass (chillers, fan walls, coolers, piping)</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>estimated [L]</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Shells, frames, casings and steel piping; copper tubes, aluminum coils and loop water excluded</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Steel share of IT mass (rack frames, server chassis)</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>estimated [L]</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Same 40% enclosure share used for the long-term replacement row</t>
         </is>
       </c>
     </row>
@@ -4008,19 +4092,21 @@
         <f>IF(SUM($F19:$I19)=0,0,M19*I19/SUM($F19:$I19))</f>
         <v/>
       </c>
-      <c r="X19" s="8" t="inlineStr">
-        <is>
-          <t>not estimated</t>
-        </is>
-      </c>
-      <c r="Y19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" s="8" t="n">
-        <v>0</v>
+      <c r="X19" s="7">
+        <f>Inputs!$B$49*Inputs!$B$44</f>
+        <v/>
+      </c>
+      <c r="Y19" s="5">
+        <f>B19*X19</f>
+        <v/>
+      </c>
+      <c r="Z19" s="5">
+        <f>C19*X19</f>
+        <v/>
+      </c>
+      <c r="AA19" s="7">
+        <f>Inputs!$B$49*Inputs!$C$45</f>
+        <v/>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
@@ -4119,19 +4205,21 @@
         <f>IF(SUM($F20:$I20)=0,0,M20*I20/SUM($F20:$I20))</f>
         <v/>
       </c>
-      <c r="X20" s="8" t="inlineStr">
-        <is>
-          <t>not estimated</t>
-        </is>
-      </c>
-      <c r="Y20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="8" t="n">
-        <v>0</v>
+      <c r="X20" s="7">
+        <f>Inputs!$B$50*Inputs!$B$44</f>
+        <v/>
+      </c>
+      <c r="Y20" s="5">
+        <f>B20*X20</f>
+        <v/>
+      </c>
+      <c r="Z20" s="5">
+        <f>C20*X20</f>
+        <v/>
+      </c>
+      <c r="AA20" s="7">
+        <f>Inputs!$B$50*Inputs!$C$45</f>
+        <v/>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
@@ -4231,19 +4319,21 @@
         <f>IF(SUM($F21:$I21)=0,0,M21*I21/SUM($F21:$I21))</f>
         <v/>
       </c>
-      <c r="X21" s="8" t="inlineStr">
-        <is>
-          <t>not estimated</t>
-        </is>
-      </c>
-      <c r="Y21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="8" t="n">
-        <v>0</v>
+      <c r="X21" s="7">
+        <f>Inputs!$B$51*Inputs!$B$44</f>
+        <v/>
+      </c>
+      <c r="Y21" s="5">
+        <f>B21*X21</f>
+        <v/>
+      </c>
+      <c r="Z21" s="5">
+        <f>C21*X21</f>
+        <v/>
+      </c>
+      <c r="AA21" s="7">
+        <f>Inputs!$B$51*Inputs!$C$45</f>
+        <v/>
       </c>
       <c r="AB21" t="inlineStr">
         <is>

--- a/superwood-datacenter-investor/analyses/materials-mass-and-replacement.xlsx
+++ b/superwood-datacenter-investor/analyses/materials-mass-and-replacement.xlsx
@@ -701,7 +701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -1647,47 +1647,51 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SUPERWOOD average board thickness</t>
+          <t>Polymers in paints, foam cores and plastic trim (average)</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>7.2</v>
+        <v>3</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>7.2</v>
+        <v>3</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>kg CO₂e/kg</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>internal TEM basis [H]</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
+          <t>industry range [M]; Alex 2026-09-05</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Cradle to gate; polyolefins and PVC about 2–2.5, polyurethane foam 3–4, coatings higher</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SUPERWOOD density</t>
+          <t>SUPERWOOD average board thickness</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>1300</v>
+        <v>7.2</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>1300</v>
+        <v>7.2</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>kg/m³</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>internal TEM [H]</t>
+          <t>internal TEM basis [H]</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -1695,23 +1699,23 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SuperMill One output</t>
+          <t>SUPERWOOD density</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>1000000</v>
+        <v>1300</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>1000000</v>
+        <v>1300</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>sf/yr</t>
+          <t>kg/m³</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>internal [H]</t>
+          <t>internal TEM [H]</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -1719,14 +1723,14 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SuperMill Two output</t>
+          <t>SuperMill One output</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>36000000</v>
+        <v>1000000</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>36000000</v>
+        <v>1000000</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1743,46 +1747,42 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Structural substitution: kg SUPERWOOD per kg steel replaced</t>
+          <t>SuperMill Two output</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>0.3</v>
+        <v>36000000</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>0.6</v>
+        <v>36000000</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>kg/kg</t>
+          <t>sf/yr</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>estimated [L]</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Engineering-stamped per element (Fast + Epp) before external use</t>
-        </is>
-      </c>
+          <t>internal [H]</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SUPERWOOD in a hybrid wall panel replacing precast</t>
+          <t>Structural substitution: kg SUPERWOOD per kg steel replaced</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>20</v>
+        <v>0.3</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>40</v>
+        <v>0.6</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>kg/m²</t>
+          <t>kg/kg</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1792,25 +1792,25 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Panel design unsettled</t>
+          <t>Engineering-stamped per element (Fast + Epp) before external use</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Addressable share of other tray / containment / doors (medium term)</t>
+          <t>SUPERWOOD in a hybrid wall panel replacing precast</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>0.5</v>
+        <v>20</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>0.5</v>
+        <v>40</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>share</t>
+          <t>kg/m²</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1818,71 +1818,75 @@
           <t>estimated [L]</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Panel design unsettled</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Count rebar as addressable in the long term? (0/1)</t>
+          <t>Addressable share of other tray / containment / doors (medium term)</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>flag</t>
+          <t>share</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>choice</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Rebar is a frontier market with no pathway; off by default</t>
-        </is>
-      </c>
+          <t>estimated [L]</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Steel emissions, global average (BF-BOF)</t>
+          <t>Count rebar as addressable in the long term? (0/1)</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>kg CO₂e/kg</t>
+          <t>flag</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>published-class [M]</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
+          <t>choice</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Rebar is a frontier market with no pathway; off by default</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Steel emissions, recycled (EAF)</t>
+          <t>Steel emissions, global average (BF-BOF)</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1891,7 +1895,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>industry range [M]</t>
+          <t>published-class [M]</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -1899,14 +1903,14 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SUPERWOOD manufacturing emissions</t>
+          <t>Steel emissions, recycled (EAF)</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1915,26 +1919,22 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>internal, pre-LCA [L]</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Canva DCII deck; LCA under way, Prof. Ming Hu, Notre Dame</t>
-        </is>
-      </c>
+          <t>industry range [M]</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SUPERWOOD biogenic carbon stored</t>
+          <t>SUPERWOOD manufacturing emissions</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1948,21 +1948,21 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Report separately; module C release under EN 15804</t>
+          <t>Canva DCII deck; LCA under way, Prof. Ming Hu, Notre Dame</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Interior finishes emissions (gypsum, wood, steel studs — mixed)</t>
+          <t>SUPERWOOD biogenic carbon stored</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1971,96 +1971,40 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>estimated [L]</t>
+          <t>internal, pre-LCA [L]</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Used only for the interior finishes row</t>
+          <t>Report separately; module C release under EN 15804</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Steel share of electrical equipment mass (gensets, transformers, switchgear, UPS cabinets)</t>
+          <t>Interior finishes emissions (gypsum, wood, steel studs — mixed)</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>share</t>
+          <t>kg CO₂e/kg</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>estimated [L]; Alex asked for the estimate 2026-09-05</t>
+          <t>estimated [L]</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cast iron and steel in engines, transformer cores and tanks, switchgear and UPS enclosures; copper, aluminum, oil and cells excluded</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Steel share of mechanical equipment mass (chillers, fan walls, coolers, piping)</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C50" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>share</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>estimated [L]</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Shells, frames, casings and steel piping; copper tubes, aluminum coils and loop water excluded</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Steel share of IT mass (rack frames, server chassis)</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C51" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>share</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>estimated [L]</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Same 40% enclosure share used for the long-term replacement row</t>
+          <t>Used only for the interior finishes row</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB60"/>
+  <dimension ref="A1:AF60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -2106,6 +2050,10 @@
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="14" customWidth="1" min="27" max="27"/>
     <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="10" customWidth="1" min="31" max="31"/>
+    <col width="10" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2247,6 +2195,26 @@
       <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Material class</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Steel share</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Concrete share</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Plastic share</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Other share</t>
         </is>
       </c>
     </row>
@@ -2367,7 +2335,7 @@
         <v/>
       </c>
       <c r="X3" s="7">
-        <f>Inputs!$B$35</f>
+        <f>AC3*Inputs!$B$45+AD3*Inputs!$B$35+AE3*Inputs!$B$36</f>
         <v/>
       </c>
       <c r="Y3" s="5">
@@ -2379,13 +2347,25 @@
         <v/>
       </c>
       <c r="AA3" s="7">
-        <f>Inputs!$B$35</f>
+        <f>AC3*Inputs!$C$46+AD3*Inputs!$B$35+AE3*Inputs!$B$36</f>
         <v/>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
           <t>concrete</t>
         </is>
+      </c>
+      <c r="AC3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2481,7 +2461,7 @@
         <v/>
       </c>
       <c r="X4" s="7">
-        <f>Inputs!$B$35</f>
+        <f>AC4*Inputs!$B$45+AD4*Inputs!$B$35+AE4*Inputs!$B$36</f>
         <v/>
       </c>
       <c r="Y4" s="5">
@@ -2493,13 +2473,25 @@
         <v/>
       </c>
       <c r="AA4" s="7">
-        <f>Inputs!$B$35</f>
+        <f>AC4*Inputs!$C$46+AD4*Inputs!$B$35+AE4*Inputs!$B$36</f>
         <v/>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
           <t>concrete</t>
         </is>
+      </c>
+      <c r="AC4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2545,11 +2537,11 @@
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>SUM($F5:$I5)*Inputs!$B$13*Derived!B4*Inputs!$B$41/1000</f>
+        <f>SUM($F5:$I5)*Inputs!$B$13*Derived!B4*Inputs!$B$42/1000</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>SUM($F5:$I5)*Inputs!$C$13*Derived!C4*Inputs!$C$41/1000</f>
+        <f>SUM($F5:$I5)*Inputs!$C$13*Derived!C4*Inputs!$C$42/1000</f>
         <v/>
       </c>
       <c r="N5" t="inlineStr">
@@ -2594,7 +2586,7 @@
         <v/>
       </c>
       <c r="X5" s="7">
-        <f>Inputs!$B$35</f>
+        <f>AC5*Inputs!$B$45+AD5*Inputs!$B$35+AE5*Inputs!$B$36</f>
         <v/>
       </c>
       <c r="Y5" s="5">
@@ -2606,13 +2598,25 @@
         <v/>
       </c>
       <c r="AA5" s="7">
-        <f>Inputs!$B$35</f>
+        <f>AC5*Inputs!$C$46+AD5*Inputs!$B$35+AE5*Inputs!$B$36</f>
         <v/>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
           <t>concrete</t>
         </is>
+      </c>
+      <c r="AC5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -2659,11 +2663,11 @@
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>J6*Inputs!$B$40</f>
+        <f>J6*Inputs!$B$41</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>K6*Inputs!$C$40</f>
+        <f>K6*Inputs!$C$41</f>
         <v/>
       </c>
       <c r="N6" t="inlineStr">
@@ -2708,7 +2712,7 @@
         <v/>
       </c>
       <c r="X6" s="7">
-        <f>Inputs!$B$44</f>
+        <f>AC6*Inputs!$B$45+AD6*Inputs!$B$35+AE6*Inputs!$B$36</f>
         <v/>
       </c>
       <c r="Y6" s="5">
@@ -2720,13 +2724,25 @@
         <v/>
       </c>
       <c r="AA6" s="7">
-        <f>Inputs!$C$45</f>
+        <f>AC6*Inputs!$C$46+AD6*Inputs!$B$35+AE6*Inputs!$B$36</f>
         <v/>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
           <t>steel</t>
         </is>
+      </c>
+      <c r="AC6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -2772,11 +2788,11 @@
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>J7*Inputs!$B$40</f>
+        <f>J7*Inputs!$B$41</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>K7*Inputs!$C$40</f>
+        <f>K7*Inputs!$C$41</f>
         <v/>
       </c>
       <c r="N7" t="inlineStr">
@@ -2821,7 +2837,7 @@
         <v/>
       </c>
       <c r="X7" s="7">
-        <f>Inputs!$B$44</f>
+        <f>AC7*Inputs!$B$45+AD7*Inputs!$B$35+AE7*Inputs!$B$36</f>
         <v/>
       </c>
       <c r="Y7" s="5">
@@ -2833,13 +2849,25 @@
         <v/>
       </c>
       <c r="AA7" s="7">
-        <f>Inputs!$C$45</f>
+        <f>AC7*Inputs!$C$46+AD7*Inputs!$B$35+AE7*Inputs!$B$36</f>
         <v/>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
           <t>steel</t>
         </is>
+      </c>
+      <c r="AC7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -2885,11 +2913,11 @@
         <v/>
       </c>
       <c r="L8" s="5">
-        <f>J8*Inputs!$B$40</f>
+        <f>J8*Inputs!$B$41</f>
         <v/>
       </c>
       <c r="M8" s="5">
-        <f>K8*Inputs!$C$40</f>
+        <f>K8*Inputs!$C$41</f>
         <v/>
       </c>
       <c r="N8" t="inlineStr">
@@ -2934,7 +2962,7 @@
         <v/>
       </c>
       <c r="X8" s="7">
-        <f>Inputs!$B$44</f>
+        <f>AC8*Inputs!$B$45+AD8*Inputs!$B$35+AE8*Inputs!$B$36</f>
         <v/>
       </c>
       <c r="Y8" s="5">
@@ -2946,13 +2974,25 @@
         <v/>
       </c>
       <c r="AA8" s="7">
-        <f>Inputs!$C$45</f>
+        <f>AC8*Inputs!$C$46+AD8*Inputs!$B$35+AE8*Inputs!$B$36</f>
         <v/>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
           <t>steel</t>
         </is>
+      </c>
+      <c r="AC8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -3047,7 +3087,7 @@
         <v/>
       </c>
       <c r="X9" s="7">
-        <f>Inputs!$B$44</f>
+        <f>AC9*Inputs!$B$45+AD9*Inputs!$B$35+AE9*Inputs!$B$36</f>
         <v/>
       </c>
       <c r="Y9" s="5">
@@ -3059,13 +3099,25 @@
         <v/>
       </c>
       <c r="AA9" s="7">
-        <f>Inputs!$C$45</f>
+        <f>AC9*Inputs!$C$46+AD9*Inputs!$B$35+AE9*Inputs!$B$36</f>
         <v/>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
           <t>steel</t>
         </is>
+      </c>
+      <c r="AC9" s="2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AD9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AF9" s="2" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="10">
@@ -3160,7 +3212,7 @@
         <v/>
       </c>
       <c r="X10" s="7">
-        <f>Inputs!$B$44</f>
+        <f>AC10*Inputs!$B$45+AD10*Inputs!$B$35+AE10*Inputs!$B$36</f>
         <v/>
       </c>
       <c r="Y10" s="5">
@@ -3172,13 +3224,25 @@
         <v/>
       </c>
       <c r="AA10" s="7">
-        <f>Inputs!$C$45</f>
+        <f>AC10*Inputs!$C$46+AD10*Inputs!$B$35+AE10*Inputs!$B$36</f>
         <v/>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
           <t>steel</t>
         </is>
+      </c>
+      <c r="AC10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -3273,7 +3337,7 @@
         <v/>
       </c>
       <c r="X11" s="7">
-        <f>Inputs!$B$44</f>
+        <f>AC11*Inputs!$B$45+AD11*Inputs!$B$35+AE11*Inputs!$B$36</f>
         <v/>
       </c>
       <c r="Y11" s="5">
@@ -3285,13 +3349,25 @@
         <v/>
       </c>
       <c r="AA11" s="7">
-        <f>Inputs!$C$45</f>
+        <f>AC11*Inputs!$C$46+AD11*Inputs!$B$35+AE11*Inputs!$B$36</f>
         <v/>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
           <t>steel</t>
         </is>
+      </c>
+      <c r="AC11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -3365,11 +3441,11 @@
         <v/>
       </c>
       <c r="L13" s="5">
-        <f>J13*Inputs!$B$40</f>
+        <f>J13*Inputs!$B$41</f>
         <v/>
       </c>
       <c r="M13" s="5">
-        <f>K13*Inputs!$C$40</f>
+        <f>K13*Inputs!$C$41</f>
         <v/>
       </c>
       <c r="N13" t="inlineStr">
@@ -3414,7 +3490,7 @@
         <v/>
       </c>
       <c r="X13" s="7">
-        <f>Inputs!$B$44</f>
+        <f>AC13*Inputs!$B$45+AD13*Inputs!$B$35+AE13*Inputs!$B$36</f>
         <v/>
       </c>
       <c r="Y13" s="5">
@@ -3426,13 +3502,25 @@
         <v/>
       </c>
       <c r="AA13" s="7">
-        <f>Inputs!$C$45</f>
+        <f>AC13*Inputs!$C$46+AD13*Inputs!$B$35+AE13*Inputs!$B$36</f>
         <v/>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
           <t>steel</t>
         </is>
+      </c>
+      <c r="AC13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -3478,11 +3566,11 @@
         <v/>
       </c>
       <c r="L14" s="5">
-        <f>J14*Inputs!$B$40</f>
+        <f>J14*Inputs!$B$41</f>
         <v/>
       </c>
       <c r="M14" s="5">
-        <f>K14*Inputs!$C$40</f>
+        <f>K14*Inputs!$C$41</f>
         <v/>
       </c>
       <c r="N14" t="inlineStr">
@@ -3527,7 +3615,7 @@
         <v/>
       </c>
       <c r="X14" s="7">
-        <f>Inputs!$B$44</f>
+        <f>AC14*Inputs!$B$45+AD14*Inputs!$B$35+AE14*Inputs!$B$36</f>
         <v/>
       </c>
       <c r="Y14" s="5">
@@ -3539,13 +3627,25 @@
         <v/>
       </c>
       <c r="AA14" s="7">
-        <f>Inputs!$C$45</f>
+        <f>AC14*Inputs!$C$46+AD14*Inputs!$B$35+AE14*Inputs!$B$36</f>
         <v/>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
           <t>steel</t>
         </is>
+      </c>
+      <c r="AC14" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AD14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AF14" s="2" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="15">
@@ -3591,11 +3691,11 @@
         <v/>
       </c>
       <c r="L15" s="5">
-        <f>J15*Inputs!$B$40</f>
+        <f>J15*Inputs!$B$41</f>
         <v/>
       </c>
       <c r="M15" s="5">
-        <f>K15*Inputs!$C$40</f>
+        <f>K15*Inputs!$C$41</f>
         <v/>
       </c>
       <c r="N15" t="inlineStr">
@@ -3640,7 +3740,7 @@
         <v/>
       </c>
       <c r="X15" s="7">
-        <f>Inputs!$B$44</f>
+        <f>AC15*Inputs!$B$45+AD15*Inputs!$B$35+AE15*Inputs!$B$36</f>
         <v/>
       </c>
       <c r="Y15" s="5">
@@ -3652,13 +3752,25 @@
         <v/>
       </c>
       <c r="AA15" s="7">
-        <f>Inputs!$C$45</f>
+        <f>AC15*Inputs!$C$46+AD15*Inputs!$B$35+AE15*Inputs!$B$36</f>
         <v/>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
           <t>steel</t>
         </is>
+      </c>
+      <c r="AC15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3687,7 +3799,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="6">
-        <f>Inputs!$B$42</f>
+        <f>Inputs!$B$43</f>
         <v/>
       </c>
       <c r="H16" s="6" t="n">
@@ -3705,11 +3817,11 @@
         <v/>
       </c>
       <c r="L16" s="5">
-        <f>J16*Inputs!$B$40</f>
+        <f>J16*Inputs!$B$41</f>
         <v/>
       </c>
       <c r="M16" s="5">
-        <f>K16*Inputs!$C$40</f>
+        <f>K16*Inputs!$C$41</f>
         <v/>
       </c>
       <c r="N16" t="inlineStr">
@@ -3754,7 +3866,7 @@
         <v/>
       </c>
       <c r="X16" s="7">
-        <f>Inputs!$B$44</f>
+        <f>AC16*Inputs!$B$45+AD16*Inputs!$B$35+AE16*Inputs!$B$36</f>
         <v/>
       </c>
       <c r="Y16" s="5">
@@ -3766,13 +3878,25 @@
         <v/>
       </c>
       <c r="AA16" s="7">
-        <f>Inputs!$C$45</f>
+        <f>AC16*Inputs!$C$46+AD16*Inputs!$B$35+AE16*Inputs!$B$36</f>
         <v/>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
           <t>steel</t>
         </is>
+      </c>
+      <c r="AC16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3818,11 +3942,11 @@
         <v/>
       </c>
       <c r="L17" s="5">
-        <f>J17*Inputs!$B$40</f>
+        <f>J17*Inputs!$B$41</f>
         <v/>
       </c>
       <c r="M17" s="5">
-        <f>K17*Inputs!$C$40</f>
+        <f>K17*Inputs!$C$41</f>
         <v/>
       </c>
       <c r="N17" t="inlineStr">
@@ -3867,7 +3991,7 @@
         <v/>
       </c>
       <c r="X17" s="7">
-        <f>Inputs!$B$44</f>
+        <f>AC17*Inputs!$B$45+AD17*Inputs!$B$35+AE17*Inputs!$B$36</f>
         <v/>
       </c>
       <c r="Y17" s="5">
@@ -3879,13 +4003,25 @@
         <v/>
       </c>
       <c r="AA17" s="7">
-        <f>Inputs!$C$45</f>
+        <f>AC17*Inputs!$C$46+AD17*Inputs!$B$35+AE17*Inputs!$B$36</f>
         <v/>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
           <t>steel</t>
         </is>
+      </c>
+      <c r="AC17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3980,7 +4116,7 @@
         <v/>
       </c>
       <c r="X18" s="7">
-        <f>Inputs!$B$48</f>
+        <f>AC18*Inputs!$B$45+AD18*Inputs!$B$35+AE18*Inputs!$B$36</f>
         <v/>
       </c>
       <c r="Y18" s="5">
@@ -3992,13 +4128,25 @@
         <v/>
       </c>
       <c r="AA18" s="7">
-        <f>Inputs!$B$48</f>
+        <f>AC18*Inputs!$C$46+AD18*Inputs!$B$35+AE18*Inputs!$B$36</f>
         <v/>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
           <t>mixed</t>
         </is>
+      </c>
+      <c r="AC18" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AD18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AF18" s="2" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="19">
@@ -4093,7 +4241,7 @@
         <v/>
       </c>
       <c r="X19" s="7">
-        <f>Inputs!$B$49*Inputs!$B$44</f>
+        <f>AC19*Inputs!$B$45+AD19*Inputs!$B$35+AE19*Inputs!$B$36</f>
         <v/>
       </c>
       <c r="Y19" s="5">
@@ -4105,13 +4253,25 @@
         <v/>
       </c>
       <c r="AA19" s="7">
-        <f>Inputs!$B$49*Inputs!$C$45</f>
+        <f>AC19*Inputs!$C$46+AD19*Inputs!$B$35+AE19*Inputs!$B$36</f>
         <v/>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
           <t>equipment</t>
         </is>
+      </c>
+      <c r="AC19" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AD19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AF19" s="2" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="20">
@@ -4206,7 +4366,7 @@
         <v/>
       </c>
       <c r="X20" s="7">
-        <f>Inputs!$B$50*Inputs!$B$44</f>
+        <f>AC20*Inputs!$B$45+AD20*Inputs!$B$35+AE20*Inputs!$B$36</f>
         <v/>
       </c>
       <c r="Y20" s="5">
@@ -4218,13 +4378,25 @@
         <v/>
       </c>
       <c r="AA20" s="7">
-        <f>Inputs!$B$50*Inputs!$C$45</f>
+        <f>AC20*Inputs!$C$46+AD20*Inputs!$B$35+AE20*Inputs!$B$36</f>
         <v/>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
           <t>equipment</t>
         </is>
+      </c>
+      <c r="AC20" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AF20" s="2" t="n">
+        <v>0.45</v>
       </c>
     </row>
     <row r="21">
@@ -4271,11 +4443,11 @@
         <v/>
       </c>
       <c r="L21" s="5">
-        <f>J21*Inputs!$B$40</f>
+        <f>J21*Inputs!$B$41</f>
         <v/>
       </c>
       <c r="M21" s="5">
-        <f>K21*Inputs!$C$40</f>
+        <f>K21*Inputs!$C$41</f>
         <v/>
       </c>
       <c r="N21" t="inlineStr">
@@ -4320,7 +4492,7 @@
         <v/>
       </c>
       <c r="X21" s="7">
-        <f>Inputs!$B$51*Inputs!$B$44</f>
+        <f>AC21*Inputs!$B$45+AD21*Inputs!$B$35+AE21*Inputs!$B$36</f>
         <v/>
       </c>
       <c r="Y21" s="5">
@@ -4332,13 +4504,25 @@
         <v/>
       </c>
       <c r="AA21" s="7">
-        <f>Inputs!$B$51*Inputs!$C$45</f>
+        <f>AC21*Inputs!$C$46+AD21*Inputs!$B$35+AE21*Inputs!$B$36</f>
         <v/>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
           <t>equipment</t>
         </is>
+      </c>
+      <c r="AC21" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AD21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AF21" s="2" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="23">
@@ -4927,11 +5111,11 @@
         </is>
       </c>
       <c r="B6" s="15">
-        <f>Inputs!$B$36/1000*Inputs!$B$37*0.092903</f>
+        <f>Inputs!$B$37/1000*Inputs!$B$38*0.092903</f>
         <v/>
       </c>
       <c r="C6" s="15">
-        <f>Inputs!$C$36/1000*Inputs!$C$37*0.092903</f>
+        <f>Inputs!$C$37/1000*Inputs!$C$38*0.092903</f>
         <v/>
       </c>
       <c r="D6" t="inlineStr">
@@ -4947,11 +5131,11 @@
         </is>
       </c>
       <c r="B7" s="15">
-        <f>Inputs!$B$38*B6/1000</f>
+        <f>Inputs!$B$39*B6/1000</f>
         <v/>
       </c>
       <c r="C7" s="15">
-        <f>Inputs!$C$38*C6/1000</f>
+        <f>Inputs!$C$39*C6/1000</f>
         <v/>
       </c>
       <c r="D7" t="inlineStr">
@@ -4967,11 +5151,11 @@
         </is>
       </c>
       <c r="B8" s="15">
-        <f>Inputs!$B$39*B6/1000</f>
+        <f>Inputs!$B$40*B6/1000</f>
         <v/>
       </c>
       <c r="C8" s="15">
-        <f>Inputs!$C$39*C6/1000</f>
+        <f>Inputs!$C$40*C6/1000</f>
         <v/>
       </c>
       <c r="D8" t="inlineStr">
@@ -5079,11 +5263,11 @@
         <v/>
       </c>
       <c r="D2" s="4">
-        <f>'1 GW data center'!B29*Inputs!$B$46</f>
+        <f>'1 GW data center'!B29*Inputs!$B$47</f>
         <v/>
       </c>
       <c r="E2" s="4">
-        <f>'1 GW data center'!C29*Inputs!$C$46</f>
+        <f>'1 GW data center'!C29*Inputs!$C$47</f>
         <v/>
       </c>
       <c r="F2" s="4">
@@ -5103,11 +5287,11 @@
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>'1 GW data center'!B29*Inputs!$B$47</f>
+        <f>'1 GW data center'!B29*Inputs!$B$48</f>
         <v/>
       </c>
       <c r="K2" s="4">
-        <f>'1 GW data center'!C29*Inputs!$C$47</f>
+        <f>'1 GW data center'!C29*Inputs!$C$48</f>
         <v/>
       </c>
     </row>
@@ -5126,11 +5310,11 @@
         <v/>
       </c>
       <c r="D3" s="4">
-        <f>'1 GW data center'!B34*Inputs!$B$46</f>
+        <f>'1 GW data center'!B34*Inputs!$B$47</f>
         <v/>
       </c>
       <c r="E3" s="4">
-        <f>'1 GW data center'!C34*Inputs!$C$46</f>
+        <f>'1 GW data center'!C34*Inputs!$C$47</f>
         <v/>
       </c>
       <c r="F3" s="4">
@@ -5150,11 +5334,11 @@
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>'1 GW data center'!B34*Inputs!$B$47</f>
+        <f>'1 GW data center'!B34*Inputs!$B$48</f>
         <v/>
       </c>
       <c r="K3" s="4">
-        <f>'1 GW data center'!C34*Inputs!$C$47</f>
+        <f>'1 GW data center'!C34*Inputs!$C$48</f>
         <v/>
       </c>
     </row>
@@ -5173,11 +5357,11 @@
         <v/>
       </c>
       <c r="D4" s="4">
-        <f>'1 GW data center'!B38*Inputs!$B$46</f>
+        <f>'1 GW data center'!B38*Inputs!$B$47</f>
         <v/>
       </c>
       <c r="E4" s="4">
-        <f>'1 GW data center'!C38*Inputs!$C$46</f>
+        <f>'1 GW data center'!C38*Inputs!$C$47</f>
         <v/>
       </c>
       <c r="F4" s="4">
@@ -5197,11 +5381,11 @@
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>'1 GW data center'!B38*Inputs!$B$47</f>
+        <f>'1 GW data center'!B38*Inputs!$B$48</f>
         <v/>
       </c>
       <c r="K4" s="4">
-        <f>'1 GW data center'!C38*Inputs!$C$47</f>
+        <f>'1 GW data center'!C38*Inputs!$C$48</f>
         <v/>
       </c>
     </row>
@@ -5220,11 +5404,11 @@
         <v/>
       </c>
       <c r="D5" s="4">
-        <f>'1 GW data center'!B42*Inputs!$B$46</f>
+        <f>'1 GW data center'!B42*Inputs!$B$47</f>
         <v/>
       </c>
       <c r="E5" s="4">
-        <f>'1 GW data center'!C42*Inputs!$C$46</f>
+        <f>'1 GW data center'!C42*Inputs!$C$47</f>
         <v/>
       </c>
       <c r="F5" s="4">
@@ -5244,11 +5428,11 @@
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>'1 GW data center'!B42*Inputs!$B$47</f>
+        <f>'1 GW data center'!B42*Inputs!$B$48</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>'1 GW data center'!C42*Inputs!$C$47</f>
+        <f>'1 GW data center'!C42*Inputs!$C$48</f>
         <v/>
       </c>
     </row>

--- a/superwood-datacenter-investor/analyses/materials-mass-and-replacement.xlsx
+++ b/superwood-datacenter-investor/analyses/materials-mass-and-replacement.xlsx
@@ -701,7 +701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -1451,14 +1451,14 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Share of IT mass that is server and equipment enclosures (boxes), replaceable long term</t>
+          <t>Share of IT mass that is server rack cabinets (frames, panels, doors) — substitutable soon</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1467,26 +1467,26 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>estimated [L]; Alex 2026-09-04</t>
+          <t>estimated [L]; Alex 2026-09-06</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Server boxes eventually; the electronics never</t>
+          <t>A loaded rack of 1–1.4 t carries a 150–250 kg steel cabinet</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Share of all concrete that is foundations, footings, piers and equipment pads</t>
+          <t>Share of IT mass that is server enclosures (chassis) — long term</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>0.4</v>
+        <v>0.22</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>0.5</v>
+        <v>0.22</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1495,26 +1495,26 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>estimated [L]</t>
+          <t>estimated [L]; Alex 2026-09-04/06</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Remainder is slab on grade, paving and yard</t>
+          <t>Server boxes eventually; the electronics never</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Long-term technical potential: share of slab-on-grade and paving concrete replaceable</t>
+          <t>Share of all concrete that is foundations, footings, piers and equipment pads</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1523,26 +1523,26 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>asserted-internal (Alex, 2026-09-01) [L]</t>
+          <t>estimated [L]</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Technical potential, not a plan; no design or code pathway yet</t>
+          <t>Remainder is slab on grade, paving and yard</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Long-term technical potential: share of foundations, footings, piers and pads replaceable</t>
+          <t>Long-term technical potential: share of slab-on-grade and paving concrete replaceable</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1556,53 +1556,53 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Technical potential, not a plan</t>
+          <t>Technical potential, not a plan; no design or code pathway yet</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>kg SUPERWOOD per kg of concrete replaced</t>
+          <t>Long-term technical potential: share of foundations, footings, piers and pads replaceable</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>0.05</v>
+        <v>0.9</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>0.15</v>
+        <v>0.9</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>kg/kg</t>
+          <t>share</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>estimated [L]</t>
+          <t>asserted-internal (Alex, 2026-09-01) [L]</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lightweight insulated wood-foundation concept; no design exists yet</t>
+          <t>Technical potential, not a plan</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ducting, plenums and air-distribution sheet metal</t>
+          <t>kg SUPERWOOD per kg of concrete replaced</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>3</v>
+        <v>0.05</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>8</v>
+        <v>0.15</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>t/MW</t>
+          <t>kg/kg</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1612,49 +1612,49 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Separate from the mechanical-equipment row</t>
+          <t>Lightweight insulated wood-foundation concept; no design exists yet</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Concrete emissions</t>
+          <t>Ducting, plenums and air-distribution sheet metal</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>0.12</v>
+        <v>3</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>0.12</v>
+        <v>8</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>kg CO₂e/kg</t>
+          <t>t/MW</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>industry range [M]</t>
+          <t>estimated [L]</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ready-mix, cradle to gate; typical 0.10–0.15</t>
+          <t>Separate from the mechanical-equipment row</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Polymers in paints, foam cores and plastic trim (average)</t>
+          <t>Concrete emissions</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>3</v>
+        <v>0.12</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>3</v>
+        <v>0.12</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1663,59 +1663,63 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>industry range [M]; Alex 2026-09-05</t>
+          <t>industry range [M]</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cradle to gate; polyolefins and PVC about 2–2.5, polyurethane foam 3–4, coatings higher</t>
+          <t>Ready-mix, cradle to gate; typical 0.10–0.15</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SUPERWOOD average board thickness</t>
+          <t>Polymers in paints, foam cores and plastic trim (average)</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>7.2</v>
+        <v>3</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>7.2</v>
+        <v>3</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>kg CO₂e/kg</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>internal TEM basis [H]</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
+          <t>industry range [M]; Alex 2026-09-05</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Cradle to gate; polyolefins and PVC about 2–2.5, polyurethane foam 3–4, coatings higher</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SUPERWOOD density</t>
+          <t>SUPERWOOD average board thickness</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>1300</v>
+        <v>7.2</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>1300</v>
+        <v>7.2</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>kg/m³</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>internal TEM [H]</t>
+          <t>internal TEM basis [H]</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -1723,23 +1727,23 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SuperMill One output</t>
+          <t>SUPERWOOD density</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>1000000</v>
+        <v>1300</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>1000000</v>
+        <v>1300</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>sf/yr</t>
+          <t>kg/m³</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>internal [H]</t>
+          <t>internal TEM [H]</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -1747,14 +1751,14 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SuperMill Two output</t>
+          <t>SuperMill One output</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>36000000</v>
+        <v>1000000</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>36000000</v>
+        <v>1000000</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1771,46 +1775,42 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Structural substitution: kg SUPERWOOD per kg steel replaced</t>
+          <t>SuperMill Two output</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>0.3</v>
+        <v>36000000</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>0.6</v>
+        <v>36000000</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>kg/kg</t>
+          <t>sf/yr</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>estimated [L]</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Engineering-stamped per element (Fast + Epp) before external use</t>
-        </is>
-      </c>
+          <t>internal [H]</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SUPERWOOD in a hybrid wall panel replacing precast</t>
+          <t>Structural substitution: kg SUPERWOOD per kg steel replaced</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>20</v>
+        <v>0.3</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>40</v>
+        <v>0.6</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>kg/m²</t>
+          <t>kg/kg</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1820,25 +1820,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Panel design unsettled</t>
+          <t>Engineering-stamped per element (Fast + Epp) before external use</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Addressable share of other tray / containment / doors (medium term)</t>
+          <t>SUPERWOOD in a hybrid wall panel replacing precast</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>0.5</v>
+        <v>20</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>0.5</v>
+        <v>40</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>share</t>
+          <t>kg/m²</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1846,71 +1846,75 @@
           <t>estimated [L]</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Panel design unsettled</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Count rebar as addressable in the long term? (0/1)</t>
+          <t>Addressable share of other tray / containment / doors (medium term)</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>flag</t>
+          <t>share</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>choice</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Rebar is a frontier market with no pathway; off by default</t>
-        </is>
-      </c>
+          <t>estimated [L]</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Steel emissions, global average (BF-BOF)</t>
+          <t>Count rebar as addressable in the long term? (0/1)</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>kg CO₂e/kg</t>
+          <t>flag</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>published-class [M]</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
+          <t>choice</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Rebar is a frontier market with no pathway; off by default</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Steel emissions, recycled (EAF)</t>
+          <t>Steel emissions, global average (BF-BOF)</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1919,7 +1923,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>industry range [M]</t>
+          <t>published-class [M]</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -1927,14 +1931,14 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SUPERWOOD manufacturing emissions</t>
+          <t>Steel emissions, recycled (EAF)</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1943,26 +1947,22 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>internal, pre-LCA [L]</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Canva DCII deck; LCA under way, Prof. Ming Hu, Notre Dame</t>
-        </is>
-      </c>
+          <t>industry range [M]</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SUPERWOOD biogenic carbon stored</t>
+          <t>SUPERWOOD manufacturing emissions</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1976,33 +1976,61 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Report separately; module C release under EN 15804</t>
+          <t>Canva DCII deck; LCA under way, Prof. Ming Hu, Notre Dame</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>SUPERWOOD biogenic carbon stored</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>kg CO₂e/kg</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>internal, pre-LCA [L]</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Report separately; module C release under EN 15804</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>Interior finishes emissions (gypsum, wood, steel studs — mixed)</t>
         </is>
       </c>
-      <c r="B49" s="2" t="n">
+      <c r="B50" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C49" s="2" t="n">
+      <c r="C50" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>kg CO₂e/kg</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>estimated [L]</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Used only for the interior finishes row</t>
         </is>
@@ -2249,11 +2277,11 @@
         </is>
       </c>
       <c r="B3" s="5">
-        <f>Inputs!$B$11*(1-Inputs!$B$30)*Inputs!$B$12*Inputs!$B$2-B5</f>
+        <f>Inputs!$B$11*(1-Inputs!$B$31)*Inputs!$B$12*Inputs!$B$2-B5</f>
         <v/>
       </c>
       <c r="C3" s="5">
-        <f>Inputs!$C$11*(1-Inputs!$C$30)*Inputs!$C$12*Inputs!$C$2-C5</f>
+        <f>Inputs!$C$11*(1-Inputs!$C$31)*Inputs!$C$12*Inputs!$C$2-C5</f>
         <v/>
       </c>
       <c r="D3" s="5">
@@ -2274,7 +2302,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="6">
-        <f>Inputs!$B$31</f>
+        <f>Inputs!$B$32</f>
         <v/>
       </c>
       <c r="J3" s="5">
@@ -2286,11 +2314,11 @@
         <v/>
       </c>
       <c r="L3" s="5">
-        <f>J3*Inputs!$B$33</f>
+        <f>J3*Inputs!$B$34</f>
         <v/>
       </c>
       <c r="M3" s="5">
-        <f>K3*Inputs!$C$33</f>
+        <f>K3*Inputs!$C$34</f>
         <v/>
       </c>
       <c r="N3" t="inlineStr">
@@ -2335,7 +2363,7 @@
         <v/>
       </c>
       <c r="X3" s="7">
-        <f>AC3*Inputs!$B$45+AD3*Inputs!$B$35+AE3*Inputs!$B$36</f>
+        <f>AC3*Inputs!$B$46+AD3*Inputs!$B$36+AE3*Inputs!$B$37</f>
         <v/>
       </c>
       <c r="Y3" s="5">
@@ -2347,7 +2375,7 @@
         <v/>
       </c>
       <c r="AA3" s="7">
-        <f>AC3*Inputs!$C$46+AD3*Inputs!$B$35+AE3*Inputs!$B$36</f>
+        <f>AC3*Inputs!$C$47+AD3*Inputs!$B$36+AE3*Inputs!$B$37</f>
         <v/>
       </c>
       <c r="AB3" t="inlineStr">
@@ -2375,11 +2403,11 @@
         </is>
       </c>
       <c r="B4" s="5">
-        <f>Inputs!$B$11*Inputs!$B$30*Inputs!$B$12*Inputs!$B$2</f>
+        <f>Inputs!$B$11*Inputs!$B$31*Inputs!$B$12*Inputs!$B$2</f>
         <v/>
       </c>
       <c r="C4" s="5">
-        <f>Inputs!$C$11*Inputs!$C$30*Inputs!$C$12*Inputs!$C$2</f>
+        <f>Inputs!$C$11*Inputs!$C$31*Inputs!$C$12*Inputs!$C$2</f>
         <v/>
       </c>
       <c r="D4" s="5">
@@ -2400,7 +2428,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="6">
-        <f>Inputs!$B$32</f>
+        <f>Inputs!$B$33</f>
         <v/>
       </c>
       <c r="J4" s="5">
@@ -2412,11 +2440,11 @@
         <v/>
       </c>
       <c r="L4" s="5">
-        <f>J4*Inputs!$B$33</f>
+        <f>J4*Inputs!$B$34</f>
         <v/>
       </c>
       <c r="M4" s="5">
-        <f>K4*Inputs!$C$33</f>
+        <f>K4*Inputs!$C$34</f>
         <v/>
       </c>
       <c r="N4" t="inlineStr">
@@ -2461,7 +2489,7 @@
         <v/>
       </c>
       <c r="X4" s="7">
-        <f>AC4*Inputs!$B$45+AD4*Inputs!$B$35+AE4*Inputs!$B$36</f>
+        <f>AC4*Inputs!$B$46+AD4*Inputs!$B$36+AE4*Inputs!$B$37</f>
         <v/>
       </c>
       <c r="Y4" s="5">
@@ -2473,7 +2501,7 @@
         <v/>
       </c>
       <c r="AA4" s="7">
-        <f>AC4*Inputs!$C$46+AD4*Inputs!$B$35+AE4*Inputs!$B$36</f>
+        <f>AC4*Inputs!$C$47+AD4*Inputs!$B$36+AE4*Inputs!$B$37</f>
         <v/>
       </c>
       <c r="AB4" t="inlineStr">
@@ -2537,11 +2565,11 @@
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>SUM($F5:$I5)*Inputs!$B$13*Derived!B4*Inputs!$B$42/1000</f>
+        <f>SUM($F5:$I5)*Inputs!$B$13*Derived!B4*Inputs!$B$43/1000</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>SUM($F5:$I5)*Inputs!$C$13*Derived!C4*Inputs!$C$42/1000</f>
+        <f>SUM($F5:$I5)*Inputs!$C$13*Derived!C4*Inputs!$C$43/1000</f>
         <v/>
       </c>
       <c r="N5" t="inlineStr">
@@ -2586,7 +2614,7 @@
         <v/>
       </c>
       <c r="X5" s="7">
-        <f>AC5*Inputs!$B$45+AD5*Inputs!$B$35+AE5*Inputs!$B$36</f>
+        <f>AC5*Inputs!$B$46+AD5*Inputs!$B$36+AE5*Inputs!$B$37</f>
         <v/>
       </c>
       <c r="Y5" s="5">
@@ -2598,7 +2626,7 @@
         <v/>
       </c>
       <c r="AA5" s="7">
-        <f>AC5*Inputs!$C$46+AD5*Inputs!$B$35+AE5*Inputs!$B$36</f>
+        <f>AC5*Inputs!$C$47+AD5*Inputs!$B$36+AE5*Inputs!$B$37</f>
         <v/>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2651,7 +2679,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="6">
-        <f>Inputs!$B$30*Inputs!$B$32+(1-Inputs!$B$30)*Inputs!$B$31</f>
+        <f>Inputs!$B$31*Inputs!$B$33+(1-Inputs!$B$31)*Inputs!$B$32</f>
         <v/>
       </c>
       <c r="J6" s="5">
@@ -2663,11 +2691,11 @@
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>J6*Inputs!$B$41</f>
+        <f>J6*Inputs!$B$42</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>K6*Inputs!$C$41</f>
+        <f>K6*Inputs!$C$42</f>
         <v/>
       </c>
       <c r="N6" t="inlineStr">
@@ -2712,7 +2740,7 @@
         <v/>
       </c>
       <c r="X6" s="7">
-        <f>AC6*Inputs!$B$45+AD6*Inputs!$B$35+AE6*Inputs!$B$36</f>
+        <f>AC6*Inputs!$B$46+AD6*Inputs!$B$36+AE6*Inputs!$B$37</f>
         <v/>
       </c>
       <c r="Y6" s="5">
@@ -2724,7 +2752,7 @@
         <v/>
       </c>
       <c r="AA6" s="7">
-        <f>AC6*Inputs!$C$46+AD6*Inputs!$B$35+AE6*Inputs!$B$36</f>
+        <f>AC6*Inputs!$C$47+AD6*Inputs!$B$36+AE6*Inputs!$B$37</f>
         <v/>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2788,11 +2816,11 @@
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>J7*Inputs!$B$41</f>
+        <f>J7*Inputs!$B$42</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>K7*Inputs!$C$41</f>
+        <f>K7*Inputs!$C$42</f>
         <v/>
       </c>
       <c r="N7" t="inlineStr">
@@ -2837,7 +2865,7 @@
         <v/>
       </c>
       <c r="X7" s="7">
-        <f>AC7*Inputs!$B$45+AD7*Inputs!$B$35+AE7*Inputs!$B$36</f>
+        <f>AC7*Inputs!$B$46+AD7*Inputs!$B$36+AE7*Inputs!$B$37</f>
         <v/>
       </c>
       <c r="Y7" s="5">
@@ -2849,7 +2877,7 @@
         <v/>
       </c>
       <c r="AA7" s="7">
-        <f>AC7*Inputs!$C$46+AD7*Inputs!$B$35+AE7*Inputs!$B$36</f>
+        <f>AC7*Inputs!$C$47+AD7*Inputs!$B$36+AE7*Inputs!$B$37</f>
         <v/>
       </c>
       <c r="AB7" t="inlineStr">
@@ -2913,11 +2941,11 @@
         <v/>
       </c>
       <c r="L8" s="5">
-        <f>J8*Inputs!$B$41</f>
+        <f>J8*Inputs!$B$42</f>
         <v/>
       </c>
       <c r="M8" s="5">
-        <f>K8*Inputs!$C$41</f>
+        <f>K8*Inputs!$C$42</f>
         <v/>
       </c>
       <c r="N8" t="inlineStr">
@@ -2962,7 +2990,7 @@
         <v/>
       </c>
       <c r="X8" s="7">
-        <f>AC8*Inputs!$B$45+AD8*Inputs!$B$35+AE8*Inputs!$B$36</f>
+        <f>AC8*Inputs!$B$46+AD8*Inputs!$B$36+AE8*Inputs!$B$37</f>
         <v/>
       </c>
       <c r="Y8" s="5">
@@ -2974,7 +3002,7 @@
         <v/>
       </c>
       <c r="AA8" s="7">
-        <f>AC8*Inputs!$C$46+AD8*Inputs!$B$35+AE8*Inputs!$B$36</f>
+        <f>AC8*Inputs!$C$47+AD8*Inputs!$B$36+AE8*Inputs!$B$37</f>
         <v/>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3087,7 +3115,7 @@
         <v/>
       </c>
       <c r="X9" s="7">
-        <f>AC9*Inputs!$B$45+AD9*Inputs!$B$35+AE9*Inputs!$B$36</f>
+        <f>AC9*Inputs!$B$46+AD9*Inputs!$B$36+AE9*Inputs!$B$37</f>
         <v/>
       </c>
       <c r="Y9" s="5">
@@ -3099,7 +3127,7 @@
         <v/>
       </c>
       <c r="AA9" s="7">
-        <f>AC9*Inputs!$C$46+AD9*Inputs!$B$35+AE9*Inputs!$B$36</f>
+        <f>AC9*Inputs!$C$47+AD9*Inputs!$B$36+AE9*Inputs!$B$37</f>
         <v/>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3212,7 +3240,7 @@
         <v/>
       </c>
       <c r="X10" s="7">
-        <f>AC10*Inputs!$B$45+AD10*Inputs!$B$35+AE10*Inputs!$B$36</f>
+        <f>AC10*Inputs!$B$46+AD10*Inputs!$B$36+AE10*Inputs!$B$37</f>
         <v/>
       </c>
       <c r="Y10" s="5">
@@ -3224,7 +3252,7 @@
         <v/>
       </c>
       <c r="AA10" s="7">
-        <f>AC10*Inputs!$C$46+AD10*Inputs!$B$35+AE10*Inputs!$B$36</f>
+        <f>AC10*Inputs!$C$47+AD10*Inputs!$B$36+AE10*Inputs!$B$37</f>
         <v/>
       </c>
       <c r="AB10" t="inlineStr">
@@ -3337,7 +3365,7 @@
         <v/>
       </c>
       <c r="X11" s="7">
-        <f>AC11*Inputs!$B$45+AD11*Inputs!$B$35+AE11*Inputs!$B$36</f>
+        <f>AC11*Inputs!$B$46+AD11*Inputs!$B$36+AE11*Inputs!$B$37</f>
         <v/>
       </c>
       <c r="Y11" s="5">
@@ -3349,7 +3377,7 @@
         <v/>
       </c>
       <c r="AA11" s="7">
-        <f>AC11*Inputs!$C$46+AD11*Inputs!$B$35+AE11*Inputs!$B$36</f>
+        <f>AC11*Inputs!$C$47+AD11*Inputs!$B$36+AE11*Inputs!$B$37</f>
         <v/>
       </c>
       <c r="AB11" t="inlineStr">
@@ -3441,11 +3469,11 @@
         <v/>
       </c>
       <c r="L13" s="5">
-        <f>J13*Inputs!$B$41</f>
+        <f>J13*Inputs!$B$42</f>
         <v/>
       </c>
       <c r="M13" s="5">
-        <f>K13*Inputs!$C$41</f>
+        <f>K13*Inputs!$C$42</f>
         <v/>
       </c>
       <c r="N13" t="inlineStr">
@@ -3490,7 +3518,7 @@
         <v/>
       </c>
       <c r="X13" s="7">
-        <f>AC13*Inputs!$B$45+AD13*Inputs!$B$35+AE13*Inputs!$B$36</f>
+        <f>AC13*Inputs!$B$46+AD13*Inputs!$B$36+AE13*Inputs!$B$37</f>
         <v/>
       </c>
       <c r="Y13" s="5">
@@ -3502,7 +3530,7 @@
         <v/>
       </c>
       <c r="AA13" s="7">
-        <f>AC13*Inputs!$C$46+AD13*Inputs!$B$35+AE13*Inputs!$B$36</f>
+        <f>AC13*Inputs!$C$47+AD13*Inputs!$B$36+AE13*Inputs!$B$37</f>
         <v/>
       </c>
       <c r="AB13" t="inlineStr">
@@ -3566,11 +3594,11 @@
         <v/>
       </c>
       <c r="L14" s="5">
-        <f>J14*Inputs!$B$41</f>
+        <f>J14*Inputs!$B$42</f>
         <v/>
       </c>
       <c r="M14" s="5">
-        <f>K14*Inputs!$C$41</f>
+        <f>K14*Inputs!$C$42</f>
         <v/>
       </c>
       <c r="N14" t="inlineStr">
@@ -3615,7 +3643,7 @@
         <v/>
       </c>
       <c r="X14" s="7">
-        <f>AC14*Inputs!$B$45+AD14*Inputs!$B$35+AE14*Inputs!$B$36</f>
+        <f>AC14*Inputs!$B$46+AD14*Inputs!$B$36+AE14*Inputs!$B$37</f>
         <v/>
       </c>
       <c r="Y14" s="5">
@@ -3627,7 +3655,7 @@
         <v/>
       </c>
       <c r="AA14" s="7">
-        <f>AC14*Inputs!$C$46+AD14*Inputs!$B$35+AE14*Inputs!$B$36</f>
+        <f>AC14*Inputs!$C$47+AD14*Inputs!$B$36+AE14*Inputs!$B$37</f>
         <v/>
       </c>
       <c r="AB14" t="inlineStr">
@@ -3691,11 +3719,11 @@
         <v/>
       </c>
       <c r="L15" s="5">
-        <f>J15*Inputs!$B$41</f>
+        <f>J15*Inputs!$B$42</f>
         <v/>
       </c>
       <c r="M15" s="5">
-        <f>K15*Inputs!$C$41</f>
+        <f>K15*Inputs!$C$42</f>
         <v/>
       </c>
       <c r="N15" t="inlineStr">
@@ -3740,7 +3768,7 @@
         <v/>
       </c>
       <c r="X15" s="7">
-        <f>AC15*Inputs!$B$45+AD15*Inputs!$B$35+AE15*Inputs!$B$36</f>
+        <f>AC15*Inputs!$B$46+AD15*Inputs!$B$36+AE15*Inputs!$B$37</f>
         <v/>
       </c>
       <c r="Y15" s="5">
@@ -3752,7 +3780,7 @@
         <v/>
       </c>
       <c r="AA15" s="7">
-        <f>AC15*Inputs!$C$46+AD15*Inputs!$B$35+AE15*Inputs!$B$36</f>
+        <f>AC15*Inputs!$C$47+AD15*Inputs!$B$36+AE15*Inputs!$B$37</f>
         <v/>
       </c>
       <c r="AB15" t="inlineStr">
@@ -3799,7 +3827,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="6">
-        <f>Inputs!$B$43</f>
+        <f>Inputs!$B$44</f>
         <v/>
       </c>
       <c r="H16" s="6" t="n">
@@ -3817,11 +3845,11 @@
         <v/>
       </c>
       <c r="L16" s="5">
-        <f>J16*Inputs!$B$41</f>
+        <f>J16*Inputs!$B$42</f>
         <v/>
       </c>
       <c r="M16" s="5">
-        <f>K16*Inputs!$C$41</f>
+        <f>K16*Inputs!$C$42</f>
         <v/>
       </c>
       <c r="N16" t="inlineStr">
@@ -3866,7 +3894,7 @@
         <v/>
       </c>
       <c r="X16" s="7">
-        <f>AC16*Inputs!$B$45+AD16*Inputs!$B$35+AE16*Inputs!$B$36</f>
+        <f>AC16*Inputs!$B$46+AD16*Inputs!$B$36+AE16*Inputs!$B$37</f>
         <v/>
       </c>
       <c r="Y16" s="5">
@@ -3878,7 +3906,7 @@
         <v/>
       </c>
       <c r="AA16" s="7">
-        <f>AC16*Inputs!$C$46+AD16*Inputs!$B$35+AE16*Inputs!$B$36</f>
+        <f>AC16*Inputs!$C$47+AD16*Inputs!$B$36+AE16*Inputs!$B$37</f>
         <v/>
       </c>
       <c r="AB16" t="inlineStr">
@@ -3906,11 +3934,11 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>Inputs!$B$34*Inputs!$B$2</f>
+        <f>Inputs!$B$35*Inputs!$B$2</f>
         <v/>
       </c>
       <c r="C17" s="5">
-        <f>Inputs!$C$34*Inputs!$C$2</f>
+        <f>Inputs!$C$35*Inputs!$C$2</f>
         <v/>
       </c>
       <c r="D17" s="5">
@@ -3942,11 +3970,11 @@
         <v/>
       </c>
       <c r="L17" s="5">
-        <f>J17*Inputs!$B$41</f>
+        <f>J17*Inputs!$B$42</f>
         <v/>
       </c>
       <c r="M17" s="5">
-        <f>K17*Inputs!$C$41</f>
+        <f>K17*Inputs!$C$42</f>
         <v/>
       </c>
       <c r="N17" t="inlineStr">
@@ -3991,7 +4019,7 @@
         <v/>
       </c>
       <c r="X17" s="7">
-        <f>AC17*Inputs!$B$45+AD17*Inputs!$B$35+AE17*Inputs!$B$36</f>
+        <f>AC17*Inputs!$B$46+AD17*Inputs!$B$36+AE17*Inputs!$B$37</f>
         <v/>
       </c>
       <c r="Y17" s="5">
@@ -4003,7 +4031,7 @@
         <v/>
       </c>
       <c r="AA17" s="7">
-        <f>AC17*Inputs!$C$46+AD17*Inputs!$B$35+AE17*Inputs!$B$36</f>
+        <f>AC17*Inputs!$C$47+AD17*Inputs!$B$36+AE17*Inputs!$B$37</f>
         <v/>
       </c>
       <c r="AB17" t="inlineStr">
@@ -4116,7 +4144,7 @@
         <v/>
       </c>
       <c r="X18" s="7">
-        <f>AC18*Inputs!$B$45+AD18*Inputs!$B$35+AE18*Inputs!$B$36</f>
+        <f>AC18*Inputs!$B$46+AD18*Inputs!$B$36+AE18*Inputs!$B$37</f>
         <v/>
       </c>
       <c r="Y18" s="5">
@@ -4128,7 +4156,7 @@
         <v/>
       </c>
       <c r="AA18" s="7">
-        <f>AC18*Inputs!$C$46+AD18*Inputs!$B$35+AE18*Inputs!$B$36</f>
+        <f>AC18*Inputs!$C$47+AD18*Inputs!$B$36+AE18*Inputs!$B$37</f>
         <v/>
       </c>
       <c r="AB18" t="inlineStr">
@@ -4241,7 +4269,7 @@
         <v/>
       </c>
       <c r="X19" s="7">
-        <f>AC19*Inputs!$B$45+AD19*Inputs!$B$35+AE19*Inputs!$B$36</f>
+        <f>AC19*Inputs!$B$46+AD19*Inputs!$B$36+AE19*Inputs!$B$37</f>
         <v/>
       </c>
       <c r="Y19" s="5">
@@ -4253,7 +4281,7 @@
         <v/>
       </c>
       <c r="AA19" s="7">
-        <f>AC19*Inputs!$C$46+AD19*Inputs!$B$35+AE19*Inputs!$B$36</f>
+        <f>AC19*Inputs!$C$47+AD19*Inputs!$B$36+AE19*Inputs!$B$37</f>
         <v/>
       </c>
       <c r="AB19" t="inlineStr">
@@ -4366,7 +4394,7 @@
         <v/>
       </c>
       <c r="X20" s="7">
-        <f>AC20*Inputs!$B$45+AD20*Inputs!$B$35+AE20*Inputs!$B$36</f>
+        <f>AC20*Inputs!$B$46+AD20*Inputs!$B$36+AE20*Inputs!$B$37</f>
         <v/>
       </c>
       <c r="Y20" s="5">
@@ -4378,7 +4406,7 @@
         <v/>
       </c>
       <c r="AA20" s="7">
-        <f>AC20*Inputs!$C$46+AD20*Inputs!$B$35+AE20*Inputs!$B$36</f>
+        <f>AC20*Inputs!$C$47+AD20*Inputs!$B$36+AE20*Inputs!$B$37</f>
         <v/>
       </c>
       <c r="AB20" t="inlineStr">
@@ -4424,14 +4452,15 @@
       <c r="F21" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G21" s="6" t="n">
-        <v>0</v>
+      <c r="G21" s="6">
+        <f>Inputs!$B$29</f>
+        <v/>
       </c>
       <c r="H21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="6">
-        <f>Inputs!$B$29</f>
+        <f>Inputs!$B$30</f>
         <v/>
       </c>
       <c r="J21" s="5">
@@ -4443,16 +4472,16 @@
         <v/>
       </c>
       <c r="L21" s="5">
-        <f>J21*Inputs!$B$41</f>
+        <f>J21*Inputs!$B$42</f>
         <v/>
       </c>
       <c r="M21" s="5">
-        <f>K21*Inputs!$C$41</f>
+        <f>K21*Inputs!$C$42</f>
         <v/>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Server and equipment enclosures only (40% of IT mass, estimate); electronics never. Rack masses [H]; aggregate [L]</t>
+          <t>Rack cabinets soon (18% of IT mass), server enclosures long term (22%), estimates; electronics never. Rack masses [H]; aggregate [L]</t>
         </is>
       </c>
       <c r="O21" s="5">
@@ -4492,7 +4521,7 @@
         <v/>
       </c>
       <c r="X21" s="7">
-        <f>AC21*Inputs!$B$45+AD21*Inputs!$B$35+AE21*Inputs!$B$36</f>
+        <f>AC21*Inputs!$B$46+AD21*Inputs!$B$36+AE21*Inputs!$B$37</f>
         <v/>
       </c>
       <c r="Y21" s="5">
@@ -4504,7 +4533,7 @@
         <v/>
       </c>
       <c r="AA21" s="7">
-        <f>AC21*Inputs!$C$46+AD21*Inputs!$B$35+AE21*Inputs!$B$36</f>
+        <f>AC21*Inputs!$C$47+AD21*Inputs!$B$36+AE21*Inputs!$B$37</f>
         <v/>
       </c>
       <c r="AB21" t="inlineStr">
@@ -5111,11 +5140,11 @@
         </is>
       </c>
       <c r="B6" s="15">
-        <f>Inputs!$B$37/1000*Inputs!$B$38*0.092903</f>
+        <f>Inputs!$B$38/1000*Inputs!$B$39*0.092903</f>
         <v/>
       </c>
       <c r="C6" s="15">
-        <f>Inputs!$C$37/1000*Inputs!$C$38*0.092903</f>
+        <f>Inputs!$C$38/1000*Inputs!$C$39*0.092903</f>
         <v/>
       </c>
       <c r="D6" t="inlineStr">
@@ -5131,11 +5160,11 @@
         </is>
       </c>
       <c r="B7" s="15">
-        <f>Inputs!$B$39*B6/1000</f>
+        <f>Inputs!$B$40*B6/1000</f>
         <v/>
       </c>
       <c r="C7" s="15">
-        <f>Inputs!$C$39*C6/1000</f>
+        <f>Inputs!$C$40*C6/1000</f>
         <v/>
       </c>
       <c r="D7" t="inlineStr">
@@ -5151,11 +5180,11 @@
         </is>
       </c>
       <c r="B8" s="15">
-        <f>Inputs!$B$40*B6/1000</f>
+        <f>Inputs!$B$41*B6/1000</f>
         <v/>
       </c>
       <c r="C8" s="15">
-        <f>Inputs!$C$40*C6/1000</f>
+        <f>Inputs!$C$41*C6/1000</f>
         <v/>
       </c>
       <c r="D8" t="inlineStr">
@@ -5263,11 +5292,11 @@
         <v/>
       </c>
       <c r="D2" s="4">
-        <f>'1 GW data center'!B29*Inputs!$B$47</f>
+        <f>'1 GW data center'!B29*Inputs!$B$48</f>
         <v/>
       </c>
       <c r="E2" s="4">
-        <f>'1 GW data center'!C29*Inputs!$C$47</f>
+        <f>'1 GW data center'!C29*Inputs!$C$48</f>
         <v/>
       </c>
       <c r="F2" s="4">
@@ -5287,11 +5316,11 @@
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>'1 GW data center'!B29*Inputs!$B$48</f>
+        <f>'1 GW data center'!B29*Inputs!$B$49</f>
         <v/>
       </c>
       <c r="K2" s="4">
-        <f>'1 GW data center'!C29*Inputs!$C$48</f>
+        <f>'1 GW data center'!C29*Inputs!$C$49</f>
         <v/>
       </c>
     </row>
@@ -5310,11 +5339,11 @@
         <v/>
       </c>
       <c r="D3" s="4">
-        <f>'1 GW data center'!B34*Inputs!$B$47</f>
+        <f>'1 GW data center'!B34*Inputs!$B$48</f>
         <v/>
       </c>
       <c r="E3" s="4">
-        <f>'1 GW data center'!C34*Inputs!$C$47</f>
+        <f>'1 GW data center'!C34*Inputs!$C$48</f>
         <v/>
       </c>
       <c r="F3" s="4">
@@ -5334,11 +5363,11 @@
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>'1 GW data center'!B34*Inputs!$B$48</f>
+        <f>'1 GW data center'!B34*Inputs!$B$49</f>
         <v/>
       </c>
       <c r="K3" s="4">
-        <f>'1 GW data center'!C34*Inputs!$C$48</f>
+        <f>'1 GW data center'!C34*Inputs!$C$49</f>
         <v/>
       </c>
     </row>
@@ -5357,11 +5386,11 @@
         <v/>
       </c>
       <c r="D4" s="4">
-        <f>'1 GW data center'!B38*Inputs!$B$47</f>
+        <f>'1 GW data center'!B38*Inputs!$B$48</f>
         <v/>
       </c>
       <c r="E4" s="4">
-        <f>'1 GW data center'!C38*Inputs!$C$47</f>
+        <f>'1 GW data center'!C38*Inputs!$C$48</f>
         <v/>
       </c>
       <c r="F4" s="4">
@@ -5381,11 +5410,11 @@
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>'1 GW data center'!B38*Inputs!$B$48</f>
+        <f>'1 GW data center'!B38*Inputs!$B$49</f>
         <v/>
       </c>
       <c r="K4" s="4">
-        <f>'1 GW data center'!C38*Inputs!$C$48</f>
+        <f>'1 GW data center'!C38*Inputs!$C$49</f>
         <v/>
       </c>
     </row>
@@ -5404,11 +5433,11 @@
         <v/>
       </c>
       <c r="D5" s="4">
-        <f>'1 GW data center'!B42*Inputs!$B$47</f>
+        <f>'1 GW data center'!B42*Inputs!$B$48</f>
         <v/>
       </c>
       <c r="E5" s="4">
-        <f>'1 GW data center'!C42*Inputs!$C$47</f>
+        <f>'1 GW data center'!C42*Inputs!$C$48</f>
         <v/>
       </c>
       <c r="F5" s="4">
@@ -5428,11 +5457,11 @@
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>'1 GW data center'!B42*Inputs!$B$48</f>
+        <f>'1 GW data center'!B42*Inputs!$B$49</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>'1 GW data center'!C42*Inputs!$C$48</f>
+        <f>'1 GW data center'!C42*Inputs!$C$49</f>
         <v/>
       </c>
     </row>

--- a/superwood-datacenter-investor/analyses/materials-mass-and-replacement.xlsx
+++ b/superwood-datacenter-investor/analyses/materials-mass-and-replacement.xlsx
@@ -701,7 +701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -1423,42 +1423,42 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IT: servers and racks</t>
+          <t>Share of mechanical mass that is equipment shells, casings and fan-wall frames — SUPERWOOD in the medium term</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>15</v>
+        <v>0.25</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>70</v>
+        <v>0.25</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>t/MW</t>
+          <t>share</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>estimated [L]</t>
+          <t>estimated [L]; Alex 2026-09-06</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Loaded rack ~1 t; GB200 NVL72 ~1.36 t [H]</t>
+          <t>About half of the steel in the row; compressor and pump bodies, tubes and steel piping excluded</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Share of IT mass that is server rack cabinets (frames, panels, doors) — substitutable soon</t>
+          <t>Share of mechanical mass that is fan blades — long term, needs investigation</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>0.18</v>
+        <v>0.02</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>0.18</v>
+        <v>0.02</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1472,49 +1472,49 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>A loaded rack of 1–1.4 t carries a 150–250 kg steel cabinet</t>
+          <t>Aluminum or composite blades today; SUPERWOOD blades are a research question</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Share of IT mass that is server enclosures (chassis) — long term</t>
+          <t>IT: servers and racks</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>0.22</v>
+        <v>15</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>0.22</v>
+        <v>70</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>share</t>
+          <t>t/MW</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>estimated [L]; Alex 2026-09-04/06</t>
+          <t>estimated [L]</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Server boxes eventually; the electronics never</t>
+          <t>Loaded rack ~1 t; GB200 NVL72 ~1.36 t [H]</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Share of all concrete that is foundations, footings, piers and equipment pads</t>
+          <t>Share of IT mass that is server rack cabinets (frames, panels, doors) — substitutable soon</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>0.5</v>
+        <v>0.18</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1523,26 +1523,26 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>estimated [L]</t>
+          <t>estimated [L]; Alex 2026-09-06</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Remainder is slab on grade, paving and yard</t>
+          <t>A loaded rack of 1–1.4 t carries a 150–250 kg steel cabinet</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Long-term technical potential: share of slab-on-grade and paving concrete replaceable</t>
+          <t>Share of IT mass that is server enclosures (sheet-steel chassis) — long term</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>asserted-internal (Alex, 2026-09-01) [L]</t>
+          <t>estimated [M]; analyses/it-rack-material-stack.md, applied 2026-09-06</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Technical potential, not a plan; no design or code pathway yet</t>
+          <t>Server boxes eventually; the electronics never</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Long-term technical potential: share of foundations, footings, piers and pads replaceable</t>
+          <t>Share of all concrete that is foundations, footings, piers and equipment pads</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1579,195 +1579,203 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>asserted-internal (Alex, 2026-09-01) [L]</t>
+          <t>estimated [L]</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Technical potential, not a plan</t>
+          <t>Remainder is slab on grade, paving and yard</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>kg SUPERWOOD per kg of concrete replaced</t>
+          <t>Long-term technical potential: share of slab-on-grade and paving concrete replaceable</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>0.05</v>
+        <v>0.75</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>0.15</v>
+        <v>0.75</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>kg/kg</t>
+          <t>share</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>estimated [L]</t>
+          <t>asserted-internal (Alex, 2026-09-01) [L]</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lightweight insulated wood-foundation concept; no design exists yet</t>
+          <t>Technical potential, not a plan; no design or code pathway yet</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Ducting, plenums and air-distribution sheet metal</t>
+          <t>Long-term technical potential: share of foundations, footings, piers and pads replaceable</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>8</v>
+        <v>0.9</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>t/MW</t>
+          <t>share</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>estimated [L]</t>
+          <t>asserted-internal (Alex, 2026-09-01) [L]</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Separate from the mechanical-equipment row</t>
+          <t>Technical potential, not a plan</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Concrete emissions</t>
+          <t>kg SUPERWOOD per kg of concrete replaced</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>kg CO₂e/kg</t>
+          <t>kg/kg</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>industry range [M]</t>
+          <t>estimated [L]</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ready-mix, cradle to gate; typical 0.10–0.15</t>
+          <t>Lightweight insulated wood-foundation concept; no design exists yet</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polymers in paints, foam cores and plastic trim (average)</t>
+          <t>Ducting, plenums and air-distribution sheet metal</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>kg CO₂e/kg</t>
+          <t>t/MW</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>industry range [M]; Alex 2026-09-05</t>
+          <t>estimated [L]</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cradle to gate; polyolefins and PVC about 2–2.5, polyurethane foam 3–4, coatings higher</t>
+          <t>Separate from the mechanical-equipment row</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SUPERWOOD average board thickness</t>
+          <t>Concrete emissions</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>7.2</v>
+        <v>0.12</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>7.2</v>
+        <v>0.12</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>kg CO₂e/kg</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>internal TEM basis [H]</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
+          <t>industry range [M]</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Ready-mix, cradle to gate; typical 0.10–0.15</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SUPERWOOD density</t>
+          <t>Polymers in paints, foam cores and plastic trim (average)</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>1300</v>
+        <v>3</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>1300</v>
+        <v>3</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>kg/m³</t>
+          <t>kg CO₂e/kg</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>internal TEM [H]</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
+          <t>industry range [M]; Alex 2026-09-05</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Cradle to gate; polyolefins and PVC about 2–2.5, polyurethane foam 3–4, coatings higher</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SuperMill One output</t>
+          <t>SUPERWOOD average board thickness</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>1000000</v>
+        <v>7.2</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>1000000</v>
+        <v>7.2</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>sf/yr</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>internal [H]</t>
+          <t>internal TEM basis [H]</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -1775,23 +1783,23 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SuperMill Two output</t>
+          <t>SUPERWOOD density</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>36000000</v>
+        <v>1300</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>36000000</v>
+        <v>1300</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>sf/yr</t>
+          <t>kg/m³</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>internal [H]</t>
+          <t>internal TEM [H]</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -1799,74 +1807,66 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Structural substitution: kg SUPERWOOD per kg steel replaced</t>
+          <t>SuperMill One output</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>0.3</v>
+        <v>1000000</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>0.6</v>
+        <v>1000000</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>kg/kg</t>
+          <t>sf/yr</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>estimated [L]</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Engineering-stamped per element (Fast + Epp) before external use</t>
-        </is>
-      </c>
+          <t>internal [H]</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SUPERWOOD in a hybrid wall panel replacing precast</t>
+          <t>SuperMill Two output</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>20</v>
+        <v>36000000</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>40</v>
+        <v>36000000</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>kg/m²</t>
+          <t>sf/yr</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>estimated [L]</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Panel design unsettled</t>
-        </is>
-      </c>
+          <t>internal [H]</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Addressable share of other tray / containment / doors (medium term)</t>
+          <t>Structural substitution: kg SUPERWOOD per kg steel replaced</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>share</t>
+          <t>kg/kg</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1874,56 +1874,60 @@
           <t>estimated [L]</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Engineering-stamped per element (Fast + Epp) before external use</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Count rebar as addressable in the long term? (0/1)</t>
+          <t>SUPERWOOD in a hybrid wall panel replacing precast</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>flag</t>
+          <t>kg/m²</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>choice</t>
+          <t>estimated [L]</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rebar is a frontier market with no pathway; off by default</t>
+          <t>Panel design unsettled</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Steel emissions, global average (BF-BOF)</t>
+          <t>Addressable share of other tray / containment / doors (medium term)</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>kg CO₂e/kg</t>
+          <t>share</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>published-class [M]</t>
+          <t>estimated [L]</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -1931,38 +1935,42 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Steel emissions, recycled (EAF)</t>
+          <t>Count rebar as addressable in the long term? (0/1)</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>kg CO₂e/kg</t>
+          <t>flag</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>industry range [M]</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
+          <t>choice</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Rebar is a frontier market with no pathway; off by default</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SUPERWOOD manufacturing emissions</t>
+          <t>Steel emissions, global average (BF-BOF)</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1971,26 +1979,22 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>internal, pre-LCA [L]</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Canva DCII deck; LCA under way, Prof. Ming Hu, Notre Dame</t>
-        </is>
-      </c>
+          <t>published-class [M]</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SUPERWOOD biogenic carbon stored</t>
+          <t>Steel emissions, recycled (EAF)</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -1999,38 +2003,90 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>internal, pre-LCA [L]</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Report separately; module C release under EN 15804</t>
-        </is>
-      </c>
+          <t>industry range [M]</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>SUPERWOOD manufacturing emissions</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>kg CO₂e/kg</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>internal, pre-LCA [L]</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Canva DCII deck; LCA under way, Prof. Ming Hu, Notre Dame</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SUPERWOOD biogenic carbon stored</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>kg CO₂e/kg</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>internal, pre-LCA [L]</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Report separately; module C release under EN 15804</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>Interior finishes emissions (gypsum, wood, steel studs — mixed)</t>
         </is>
       </c>
-      <c r="B50" s="2" t="n">
+      <c r="B52" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C50" s="2" t="n">
+      <c r="C52" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>kg CO₂e/kg</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>estimated [L]</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Used only for the interior finishes row</t>
         </is>
@@ -2277,11 +2333,11 @@
         </is>
       </c>
       <c r="B3" s="5">
-        <f>Inputs!$B$11*(1-Inputs!$B$31)*Inputs!$B$12*Inputs!$B$2-B5</f>
+        <f>Inputs!$B$11*(1-Inputs!$B$33)*Inputs!$B$12*Inputs!$B$2-B5</f>
         <v/>
       </c>
       <c r="C3" s="5">
-        <f>Inputs!$C$11*(1-Inputs!$C$31)*Inputs!$C$12*Inputs!$C$2-C5</f>
+        <f>Inputs!$C$11*(1-Inputs!$C$33)*Inputs!$C$12*Inputs!$C$2-C5</f>
         <v/>
       </c>
       <c r="D3" s="5">
@@ -2302,7 +2358,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="6">
-        <f>Inputs!$B$32</f>
+        <f>Inputs!$B$34</f>
         <v/>
       </c>
       <c r="J3" s="5">
@@ -2314,11 +2370,11 @@
         <v/>
       </c>
       <c r="L3" s="5">
-        <f>J3*Inputs!$B$34</f>
+        <f>J3*Inputs!$B$36</f>
         <v/>
       </c>
       <c r="M3" s="5">
-        <f>K3*Inputs!$C$34</f>
+        <f>K3*Inputs!$C$36</f>
         <v/>
       </c>
       <c r="N3" t="inlineStr">
@@ -2363,7 +2419,7 @@
         <v/>
       </c>
       <c r="X3" s="7">
-        <f>AC3*Inputs!$B$46+AD3*Inputs!$B$36+AE3*Inputs!$B$37</f>
+        <f>AC3*Inputs!$B$48+AD3*Inputs!$B$38+AE3*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="Y3" s="5">
@@ -2375,7 +2431,7 @@
         <v/>
       </c>
       <c r="AA3" s="7">
-        <f>AC3*Inputs!$C$47+AD3*Inputs!$B$36+AE3*Inputs!$B$37</f>
+        <f>AC3*Inputs!$C$49+AD3*Inputs!$B$38+AE3*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="AB3" t="inlineStr">
@@ -2403,11 +2459,11 @@
         </is>
       </c>
       <c r="B4" s="5">
-        <f>Inputs!$B$11*Inputs!$B$31*Inputs!$B$12*Inputs!$B$2</f>
+        <f>Inputs!$B$11*Inputs!$B$33*Inputs!$B$12*Inputs!$B$2</f>
         <v/>
       </c>
       <c r="C4" s="5">
-        <f>Inputs!$C$11*Inputs!$C$31*Inputs!$C$12*Inputs!$C$2</f>
+        <f>Inputs!$C$11*Inputs!$C$33*Inputs!$C$12*Inputs!$C$2</f>
         <v/>
       </c>
       <c r="D4" s="5">
@@ -2428,7 +2484,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="6">
-        <f>Inputs!$B$33</f>
+        <f>Inputs!$B$35</f>
         <v/>
       </c>
       <c r="J4" s="5">
@@ -2440,11 +2496,11 @@
         <v/>
       </c>
       <c r="L4" s="5">
-        <f>J4*Inputs!$B$34</f>
+        <f>J4*Inputs!$B$36</f>
         <v/>
       </c>
       <c r="M4" s="5">
-        <f>K4*Inputs!$C$34</f>
+        <f>K4*Inputs!$C$36</f>
         <v/>
       </c>
       <c r="N4" t="inlineStr">
@@ -2489,7 +2545,7 @@
         <v/>
       </c>
       <c r="X4" s="7">
-        <f>AC4*Inputs!$B$46+AD4*Inputs!$B$36+AE4*Inputs!$B$37</f>
+        <f>AC4*Inputs!$B$48+AD4*Inputs!$B$38+AE4*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="Y4" s="5">
@@ -2501,7 +2557,7 @@
         <v/>
       </c>
       <c r="AA4" s="7">
-        <f>AC4*Inputs!$C$47+AD4*Inputs!$B$36+AE4*Inputs!$B$37</f>
+        <f>AC4*Inputs!$C$49+AD4*Inputs!$B$38+AE4*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="AB4" t="inlineStr">
@@ -2565,11 +2621,11 @@
         <v/>
       </c>
       <c r="L5" s="5">
-        <f>SUM($F5:$I5)*Inputs!$B$13*Derived!B4*Inputs!$B$43/1000</f>
+        <f>SUM($F5:$I5)*Inputs!$B$13*Derived!B4*Inputs!$B$45/1000</f>
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>SUM($F5:$I5)*Inputs!$C$13*Derived!C4*Inputs!$C$43/1000</f>
+        <f>SUM($F5:$I5)*Inputs!$C$13*Derived!C4*Inputs!$C$45/1000</f>
         <v/>
       </c>
       <c r="N5" t="inlineStr">
@@ -2614,7 +2670,7 @@
         <v/>
       </c>
       <c r="X5" s="7">
-        <f>AC5*Inputs!$B$46+AD5*Inputs!$B$36+AE5*Inputs!$B$37</f>
+        <f>AC5*Inputs!$B$48+AD5*Inputs!$B$38+AE5*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="Y5" s="5">
@@ -2626,7 +2682,7 @@
         <v/>
       </c>
       <c r="AA5" s="7">
-        <f>AC5*Inputs!$C$47+AD5*Inputs!$B$36+AE5*Inputs!$B$37</f>
+        <f>AC5*Inputs!$C$49+AD5*Inputs!$B$38+AE5*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2679,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="6">
-        <f>Inputs!$B$31*Inputs!$B$33+(1-Inputs!$B$31)*Inputs!$B$32</f>
+        <f>Inputs!$B$33*Inputs!$B$35+(1-Inputs!$B$33)*Inputs!$B$34</f>
         <v/>
       </c>
       <c r="J6" s="5">
@@ -2691,11 +2747,11 @@
         <v/>
       </c>
       <c r="L6" s="5">
-        <f>J6*Inputs!$B$42</f>
+        <f>J6*Inputs!$B$44</f>
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>K6*Inputs!$C$42</f>
+        <f>K6*Inputs!$C$44</f>
         <v/>
       </c>
       <c r="N6" t="inlineStr">
@@ -2740,7 +2796,7 @@
         <v/>
       </c>
       <c r="X6" s="7">
-        <f>AC6*Inputs!$B$46+AD6*Inputs!$B$36+AE6*Inputs!$B$37</f>
+        <f>AC6*Inputs!$B$48+AD6*Inputs!$B$38+AE6*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="Y6" s="5">
@@ -2752,7 +2808,7 @@
         <v/>
       </c>
       <c r="AA6" s="7">
-        <f>AC6*Inputs!$C$47+AD6*Inputs!$B$36+AE6*Inputs!$B$37</f>
+        <f>AC6*Inputs!$C$49+AD6*Inputs!$B$38+AE6*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2816,11 +2872,11 @@
         <v/>
       </c>
       <c r="L7" s="5">
-        <f>J7*Inputs!$B$42</f>
+        <f>J7*Inputs!$B$44</f>
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>K7*Inputs!$C$42</f>
+        <f>K7*Inputs!$C$44</f>
         <v/>
       </c>
       <c r="N7" t="inlineStr">
@@ -2865,7 +2921,7 @@
         <v/>
       </c>
       <c r="X7" s="7">
-        <f>AC7*Inputs!$B$46+AD7*Inputs!$B$36+AE7*Inputs!$B$37</f>
+        <f>AC7*Inputs!$B$48+AD7*Inputs!$B$38+AE7*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="Y7" s="5">
@@ -2877,7 +2933,7 @@
         <v/>
       </c>
       <c r="AA7" s="7">
-        <f>AC7*Inputs!$C$47+AD7*Inputs!$B$36+AE7*Inputs!$B$37</f>
+        <f>AC7*Inputs!$C$49+AD7*Inputs!$B$38+AE7*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="AB7" t="inlineStr">
@@ -2941,11 +2997,11 @@
         <v/>
       </c>
       <c r="L8" s="5">
-        <f>J8*Inputs!$B$42</f>
+        <f>J8*Inputs!$B$44</f>
         <v/>
       </c>
       <c r="M8" s="5">
-        <f>K8*Inputs!$C$42</f>
+        <f>K8*Inputs!$C$44</f>
         <v/>
       </c>
       <c r="N8" t="inlineStr">
@@ -2990,7 +3046,7 @@
         <v/>
       </c>
       <c r="X8" s="7">
-        <f>AC8*Inputs!$B$46+AD8*Inputs!$B$36+AE8*Inputs!$B$37</f>
+        <f>AC8*Inputs!$B$48+AD8*Inputs!$B$38+AE8*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="Y8" s="5">
@@ -3002,7 +3058,7 @@
         <v/>
       </c>
       <c r="AA8" s="7">
-        <f>AC8*Inputs!$C$47+AD8*Inputs!$B$36+AE8*Inputs!$B$37</f>
+        <f>AC8*Inputs!$C$49+AD8*Inputs!$B$38+AE8*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3115,7 +3171,7 @@
         <v/>
       </c>
       <c r="X9" s="7">
-        <f>AC9*Inputs!$B$46+AD9*Inputs!$B$36+AE9*Inputs!$B$37</f>
+        <f>AC9*Inputs!$B$48+AD9*Inputs!$B$38+AE9*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="Y9" s="5">
@@ -3127,7 +3183,7 @@
         <v/>
       </c>
       <c r="AA9" s="7">
-        <f>AC9*Inputs!$C$47+AD9*Inputs!$B$36+AE9*Inputs!$B$37</f>
+        <f>AC9*Inputs!$C$49+AD9*Inputs!$B$38+AE9*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3240,7 +3296,7 @@
         <v/>
       </c>
       <c r="X10" s="7">
-        <f>AC10*Inputs!$B$46+AD10*Inputs!$B$36+AE10*Inputs!$B$37</f>
+        <f>AC10*Inputs!$B$48+AD10*Inputs!$B$38+AE10*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="Y10" s="5">
@@ -3252,7 +3308,7 @@
         <v/>
       </c>
       <c r="AA10" s="7">
-        <f>AC10*Inputs!$C$47+AD10*Inputs!$B$36+AE10*Inputs!$B$37</f>
+        <f>AC10*Inputs!$C$49+AD10*Inputs!$B$38+AE10*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="AB10" t="inlineStr">
@@ -3365,7 +3421,7 @@
         <v/>
       </c>
       <c r="X11" s="7">
-        <f>AC11*Inputs!$B$46+AD11*Inputs!$B$36+AE11*Inputs!$B$37</f>
+        <f>AC11*Inputs!$B$48+AD11*Inputs!$B$38+AE11*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="Y11" s="5">
@@ -3377,7 +3433,7 @@
         <v/>
       </c>
       <c r="AA11" s="7">
-        <f>AC11*Inputs!$C$47+AD11*Inputs!$B$36+AE11*Inputs!$B$37</f>
+        <f>AC11*Inputs!$C$49+AD11*Inputs!$B$38+AE11*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="AB11" t="inlineStr">
@@ -3469,11 +3525,11 @@
         <v/>
       </c>
       <c r="L13" s="5">
-        <f>J13*Inputs!$B$42</f>
+        <f>J13*Inputs!$B$44</f>
         <v/>
       </c>
       <c r="M13" s="5">
-        <f>K13*Inputs!$C$42</f>
+        <f>K13*Inputs!$C$44</f>
         <v/>
       </c>
       <c r="N13" t="inlineStr">
@@ -3518,7 +3574,7 @@
         <v/>
       </c>
       <c r="X13" s="7">
-        <f>AC13*Inputs!$B$46+AD13*Inputs!$B$36+AE13*Inputs!$B$37</f>
+        <f>AC13*Inputs!$B$48+AD13*Inputs!$B$38+AE13*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="Y13" s="5">
@@ -3530,7 +3586,7 @@
         <v/>
       </c>
       <c r="AA13" s="7">
-        <f>AC13*Inputs!$C$47+AD13*Inputs!$B$36+AE13*Inputs!$B$37</f>
+        <f>AC13*Inputs!$C$49+AD13*Inputs!$B$38+AE13*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="AB13" t="inlineStr">
@@ -3594,11 +3650,11 @@
         <v/>
       </c>
       <c r="L14" s="5">
-        <f>J14*Inputs!$B$42</f>
+        <f>J14*Inputs!$B$44</f>
         <v/>
       </c>
       <c r="M14" s="5">
-        <f>K14*Inputs!$C$42</f>
+        <f>K14*Inputs!$C$44</f>
         <v/>
       </c>
       <c r="N14" t="inlineStr">
@@ -3643,7 +3699,7 @@
         <v/>
       </c>
       <c r="X14" s="7">
-        <f>AC14*Inputs!$B$46+AD14*Inputs!$B$36+AE14*Inputs!$B$37</f>
+        <f>AC14*Inputs!$B$48+AD14*Inputs!$B$38+AE14*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="Y14" s="5">
@@ -3655,7 +3711,7 @@
         <v/>
       </c>
       <c r="AA14" s="7">
-        <f>AC14*Inputs!$C$47+AD14*Inputs!$B$36+AE14*Inputs!$B$37</f>
+        <f>AC14*Inputs!$C$49+AD14*Inputs!$B$38+AE14*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="AB14" t="inlineStr">
@@ -3719,11 +3775,11 @@
         <v/>
       </c>
       <c r="L15" s="5">
-        <f>J15*Inputs!$B$42</f>
+        <f>J15*Inputs!$B$44</f>
         <v/>
       </c>
       <c r="M15" s="5">
-        <f>K15*Inputs!$C$42</f>
+        <f>K15*Inputs!$C$44</f>
         <v/>
       </c>
       <c r="N15" t="inlineStr">
@@ -3768,7 +3824,7 @@
         <v/>
       </c>
       <c r="X15" s="7">
-        <f>AC15*Inputs!$B$46+AD15*Inputs!$B$36+AE15*Inputs!$B$37</f>
+        <f>AC15*Inputs!$B$48+AD15*Inputs!$B$38+AE15*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="Y15" s="5">
@@ -3780,7 +3836,7 @@
         <v/>
       </c>
       <c r="AA15" s="7">
-        <f>AC15*Inputs!$C$47+AD15*Inputs!$B$36+AE15*Inputs!$B$37</f>
+        <f>AC15*Inputs!$C$49+AD15*Inputs!$B$38+AE15*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="AB15" t="inlineStr">
@@ -3827,7 +3883,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="6">
-        <f>Inputs!$B$44</f>
+        <f>Inputs!$B$46</f>
         <v/>
       </c>
       <c r="H16" s="6" t="n">
@@ -3845,11 +3901,11 @@
         <v/>
       </c>
       <c r="L16" s="5">
-        <f>J16*Inputs!$B$42</f>
+        <f>J16*Inputs!$B$44</f>
         <v/>
       </c>
       <c r="M16" s="5">
-        <f>K16*Inputs!$C$42</f>
+        <f>K16*Inputs!$C$44</f>
         <v/>
       </c>
       <c r="N16" t="inlineStr">
@@ -3894,7 +3950,7 @@
         <v/>
       </c>
       <c r="X16" s="7">
-        <f>AC16*Inputs!$B$46+AD16*Inputs!$B$36+AE16*Inputs!$B$37</f>
+        <f>AC16*Inputs!$B$48+AD16*Inputs!$B$38+AE16*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="Y16" s="5">
@@ -3906,7 +3962,7 @@
         <v/>
       </c>
       <c r="AA16" s="7">
-        <f>AC16*Inputs!$C$47+AD16*Inputs!$B$36+AE16*Inputs!$B$37</f>
+        <f>AC16*Inputs!$C$49+AD16*Inputs!$B$38+AE16*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="AB16" t="inlineStr">
@@ -3934,11 +3990,11 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>Inputs!$B$35*Inputs!$B$2</f>
+        <f>Inputs!$B$37*Inputs!$B$2</f>
         <v/>
       </c>
       <c r="C17" s="5">
-        <f>Inputs!$C$35*Inputs!$C$2</f>
+        <f>Inputs!$C$37*Inputs!$C$2</f>
         <v/>
       </c>
       <c r="D17" s="5">
@@ -3970,11 +4026,11 @@
         <v/>
       </c>
       <c r="L17" s="5">
-        <f>J17*Inputs!$B$42</f>
+        <f>J17*Inputs!$B$44</f>
         <v/>
       </c>
       <c r="M17" s="5">
-        <f>K17*Inputs!$C$42</f>
+        <f>K17*Inputs!$C$44</f>
         <v/>
       </c>
       <c r="N17" t="inlineStr">
@@ -4019,7 +4075,7 @@
         <v/>
       </c>
       <c r="X17" s="7">
-        <f>AC17*Inputs!$B$46+AD17*Inputs!$B$36+AE17*Inputs!$B$37</f>
+        <f>AC17*Inputs!$B$48+AD17*Inputs!$B$38+AE17*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="Y17" s="5">
@@ -4031,7 +4087,7 @@
         <v/>
       </c>
       <c r="AA17" s="7">
-        <f>AC17*Inputs!$C$47+AD17*Inputs!$B$36+AE17*Inputs!$B$37</f>
+        <f>AC17*Inputs!$C$49+AD17*Inputs!$B$38+AE17*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="AB17" t="inlineStr">
@@ -4144,7 +4200,7 @@
         <v/>
       </c>
       <c r="X18" s="7">
-        <f>AC18*Inputs!$B$46+AD18*Inputs!$B$36+AE18*Inputs!$B$37</f>
+        <f>AC18*Inputs!$B$48+AD18*Inputs!$B$38+AE18*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="Y18" s="5">
@@ -4156,7 +4212,7 @@
         <v/>
       </c>
       <c r="AA18" s="7">
-        <f>AC18*Inputs!$C$47+AD18*Inputs!$B$36+AE18*Inputs!$B$37</f>
+        <f>AC18*Inputs!$C$49+AD18*Inputs!$B$38+AE18*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="AB18" t="inlineStr">
@@ -4269,7 +4325,7 @@
         <v/>
       </c>
       <c r="X19" s="7">
-        <f>AC19*Inputs!$B$46+AD19*Inputs!$B$36+AE19*Inputs!$B$37</f>
+        <f>AC19*Inputs!$B$48+AD19*Inputs!$B$38+AE19*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="Y19" s="5">
@@ -4281,7 +4337,7 @@
         <v/>
       </c>
       <c r="AA19" s="7">
-        <f>AC19*Inputs!$C$47+AD19*Inputs!$B$36+AE19*Inputs!$B$37</f>
+        <f>AC19*Inputs!$C$49+AD19*Inputs!$B$38+AE19*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="AB19" t="inlineStr">
@@ -4330,11 +4386,13 @@
       <c r="G20" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="6" t="n">
-        <v>0</v>
+      <c r="H20" s="6">
+        <f>Inputs!$B$28</f>
+        <v/>
+      </c>
+      <c r="I20" s="6">
+        <f>Inputs!$B$29</f>
+        <v/>
       </c>
       <c r="J20" s="5">
         <f>B20*SUM($F20:$I20)</f>
@@ -4345,16 +4403,16 @@
         <v/>
       </c>
       <c r="L20" s="5">
-        <f>0</f>
+        <f>J20*Inputs!$B$44</f>
         <v/>
       </c>
       <c r="M20" s="5">
-        <f>0</f>
+        <f>K20*Inputs!$C$44</f>
         <v/>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Chillers, fan walls, coolers, piping (ductwork is its own row)</t>
+          <t>Shells, casings and fan-wall frames medium term (Alex 2026-09-06); fan blades long term, needs investigation; compressors, pumps, tubes, piping and water stay</t>
         </is>
       </c>
       <c r="O20" s="5">
@@ -4394,7 +4452,7 @@
         <v/>
       </c>
       <c r="X20" s="7">
-        <f>AC20*Inputs!$B$46+AD20*Inputs!$B$36+AE20*Inputs!$B$37</f>
+        <f>AC20*Inputs!$B$48+AD20*Inputs!$B$38+AE20*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="Y20" s="5">
@@ -4406,7 +4464,7 @@
         <v/>
       </c>
       <c r="AA20" s="7">
-        <f>AC20*Inputs!$C$47+AD20*Inputs!$B$36+AE20*Inputs!$B$37</f>
+        <f>AC20*Inputs!$C$49+AD20*Inputs!$B$38+AE20*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="AB20" t="inlineStr">
@@ -4434,11 +4492,11 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>Inputs!$B$28*Inputs!$B$2</f>
+        <f>Inputs!$B$30*Inputs!$B$2</f>
         <v/>
       </c>
       <c r="C21" s="5">
-        <f>Inputs!$C$28*Inputs!$C$2</f>
+        <f>Inputs!$C$30*Inputs!$C$2</f>
         <v/>
       </c>
       <c r="D21" s="5">
@@ -4453,14 +4511,14 @@
         <v>0</v>
       </c>
       <c r="G21" s="6">
-        <f>Inputs!$B$29</f>
+        <f>Inputs!$B$31</f>
         <v/>
       </c>
       <c r="H21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="6">
-        <f>Inputs!$B$30</f>
+        <f>Inputs!$B$32</f>
         <v/>
       </c>
       <c r="J21" s="5">
@@ -4472,16 +4530,16 @@
         <v/>
       </c>
       <c r="L21" s="5">
-        <f>J21*Inputs!$B$42</f>
+        <f>J21*Inputs!$B$44</f>
         <v/>
       </c>
       <c r="M21" s="5">
-        <f>K21*Inputs!$C$42</f>
+        <f>K21*Inputs!$C$44</f>
         <v/>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Rack cabinets soon (18% of IT mass), server enclosures long term (22%), estimates; electronics never. Rack masses [H]; aggregate [L]</t>
+          <t>Rack cabinets soon (18% of IT mass), server enclosures long term (30%), per analyses/it-rack-material-stack.md; electronics never. Rack masses [H]; aggregate [L]</t>
         </is>
       </c>
       <c r="O21" s="5">
@@ -4521,7 +4579,7 @@
         <v/>
       </c>
       <c r="X21" s="7">
-        <f>AC21*Inputs!$B$46+AD21*Inputs!$B$36+AE21*Inputs!$B$37</f>
+        <f>AC21*Inputs!$B$48+AD21*Inputs!$B$38+AE21*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="Y21" s="5">
@@ -4533,7 +4591,7 @@
         <v/>
       </c>
       <c r="AA21" s="7">
-        <f>AC21*Inputs!$C$47+AD21*Inputs!$B$36+AE21*Inputs!$B$37</f>
+        <f>AC21*Inputs!$C$49+AD21*Inputs!$B$38+AE21*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="AB21" t="inlineStr">
@@ -4542,16 +4600,16 @@
         </is>
       </c>
       <c r="AC21" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AD21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AE21" s="2" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="AF21" s="2" t="n">
-        <v>0.5</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="23">
@@ -5140,11 +5198,11 @@
         </is>
       </c>
       <c r="B6" s="15">
-        <f>Inputs!$B$38/1000*Inputs!$B$39*0.092903</f>
+        <f>Inputs!$B$40/1000*Inputs!$B$41*0.092903</f>
         <v/>
       </c>
       <c r="C6" s="15">
-        <f>Inputs!$C$38/1000*Inputs!$C$39*0.092903</f>
+        <f>Inputs!$C$40/1000*Inputs!$C$41*0.092903</f>
         <v/>
       </c>
       <c r="D6" t="inlineStr">
@@ -5160,11 +5218,11 @@
         </is>
       </c>
       <c r="B7" s="15">
-        <f>Inputs!$B$40*B6/1000</f>
+        <f>Inputs!$B$42*B6/1000</f>
         <v/>
       </c>
       <c r="C7" s="15">
-        <f>Inputs!$C$40*C6/1000</f>
+        <f>Inputs!$C$42*C6/1000</f>
         <v/>
       </c>
       <c r="D7" t="inlineStr">
@@ -5180,11 +5238,11 @@
         </is>
       </c>
       <c r="B8" s="15">
-        <f>Inputs!$B$41*B6/1000</f>
+        <f>Inputs!$B$43*B6/1000</f>
         <v/>
       </c>
       <c r="C8" s="15">
-        <f>Inputs!$C$41*C6/1000</f>
+        <f>Inputs!$C$43*C6/1000</f>
         <v/>
       </c>
       <c r="D8" t="inlineStr">
@@ -5292,11 +5350,11 @@
         <v/>
       </c>
       <c r="D2" s="4">
-        <f>'1 GW data center'!B29*Inputs!$B$48</f>
+        <f>'1 GW data center'!B29*Inputs!$B$50</f>
         <v/>
       </c>
       <c r="E2" s="4">
-        <f>'1 GW data center'!C29*Inputs!$C$48</f>
+        <f>'1 GW data center'!C29*Inputs!$C$50</f>
         <v/>
       </c>
       <c r="F2" s="4">
@@ -5316,11 +5374,11 @@
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>'1 GW data center'!B29*Inputs!$B$49</f>
+        <f>'1 GW data center'!B29*Inputs!$B$51</f>
         <v/>
       </c>
       <c r="K2" s="4">
-        <f>'1 GW data center'!C29*Inputs!$C$49</f>
+        <f>'1 GW data center'!C29*Inputs!$C$51</f>
         <v/>
       </c>
     </row>
@@ -5339,11 +5397,11 @@
         <v/>
       </c>
       <c r="D3" s="4">
-        <f>'1 GW data center'!B34*Inputs!$B$48</f>
+        <f>'1 GW data center'!B34*Inputs!$B$50</f>
         <v/>
       </c>
       <c r="E3" s="4">
-        <f>'1 GW data center'!C34*Inputs!$C$48</f>
+        <f>'1 GW data center'!C34*Inputs!$C$50</f>
         <v/>
       </c>
       <c r="F3" s="4">
@@ -5363,11 +5421,11 @@
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>'1 GW data center'!B34*Inputs!$B$49</f>
+        <f>'1 GW data center'!B34*Inputs!$B$51</f>
         <v/>
       </c>
       <c r="K3" s="4">
-        <f>'1 GW data center'!C34*Inputs!$C$49</f>
+        <f>'1 GW data center'!C34*Inputs!$C$51</f>
         <v/>
       </c>
     </row>
@@ -5386,11 +5444,11 @@
         <v/>
       </c>
       <c r="D4" s="4">
-        <f>'1 GW data center'!B38*Inputs!$B$48</f>
+        <f>'1 GW data center'!B38*Inputs!$B$50</f>
         <v/>
       </c>
       <c r="E4" s="4">
-        <f>'1 GW data center'!C38*Inputs!$C$48</f>
+        <f>'1 GW data center'!C38*Inputs!$C$50</f>
         <v/>
       </c>
       <c r="F4" s="4">
@@ -5410,11 +5468,11 @@
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>'1 GW data center'!B38*Inputs!$B$49</f>
+        <f>'1 GW data center'!B38*Inputs!$B$51</f>
         <v/>
       </c>
       <c r="K4" s="4">
-        <f>'1 GW data center'!C38*Inputs!$C$49</f>
+        <f>'1 GW data center'!C38*Inputs!$C$51</f>
         <v/>
       </c>
     </row>
@@ -5433,11 +5491,11 @@
         <v/>
       </c>
       <c r="D5" s="4">
-        <f>'1 GW data center'!B42*Inputs!$B$48</f>
+        <f>'1 GW data center'!B42*Inputs!$B$50</f>
         <v/>
       </c>
       <c r="E5" s="4">
-        <f>'1 GW data center'!C42*Inputs!$C$48</f>
+        <f>'1 GW data center'!C42*Inputs!$C$50</f>
         <v/>
       </c>
       <c r="F5" s="4">
@@ -5457,11 +5515,11 @@
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>'1 GW data center'!B42*Inputs!$B$49</f>
+        <f>'1 GW data center'!B42*Inputs!$B$51</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>'1 GW data center'!C42*Inputs!$C$49</f>
+        <f>'1 GW data center'!C42*Inputs!$C$51</f>
         <v/>
       </c>
     </row>

--- a/superwood-datacenter-investor/analyses/materials-mass-and-replacement.xlsx
+++ b/superwood-datacenter-investor/analyses/materials-mass-and-replacement.xlsx
@@ -11,8 +11,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1 GW data center" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Derived" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carbon" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Steel share" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Foundations" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carbon" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Steel share" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -701,7 +702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -1963,130 +1964,890 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Steel emissions, global average (BF-BOF)</t>
+          <t>Concrete basis: 0 = published per-MW intensity, 1 = footprint bottom-up (Foundations sheet)</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>kg CO₂e/kg</t>
+          <t>switch</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>published-class [M]</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
+          <t>choice</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Scenario switch, added 2026-09-06; the deck prints the per-MW basis until Alex decides</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Steel emissions, recycled (EAF)</t>
+          <t>Soil case for the footprint basis: 1 good (spread footings), 2 moderate (lean concrete, larger footings), 3 poor (piles, pile caps, structural slab)</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>kg CO₂e/kg</t>
+          <t>switch</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>industry range [M]</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
+          <t>choice</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Geotechnical allowance, Foundations sheet</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SUPERWOOD manufacturing emissions</t>
+          <t>Hall slab on grade thickness</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>0.5</v>
+        <v>8</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>kg CO₂e/kg</t>
+          <t>in</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>internal, pre-LCA [L]</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Canva DCII deck; LCA under way, Prof. Ming Hu, Notre Dame</t>
-        </is>
-      </c>
+          <t>estimated [L]</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SUPERWOOD biogenic carbon stored</t>
+          <t>Share of hall floor thickened (electrical rooms, dense rack rows)</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>1.3</v>
+        <v>0.15</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>1.3</v>
+        <v>0.25</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>kg CO₂e/kg</t>
+          <t>share</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>internal, pre-LCA [L]</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Report separately; module C release under EN 15804</t>
-        </is>
-      </c>
+          <t>estimated [L]</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>Thickened slab thickness</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>estimated [L]</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Column bay</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ft</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>estimated [L]</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Square bays</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Spread footing plan dimension</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ft</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>estimated [L]</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Square footings</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Spread footing depth</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ft</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>estimated [L]</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Perimeter grade beam width</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ft</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>estimated [L]</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Perimeter grade beam depth</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ft</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>estimated [L]</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Generator unit size</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>MW</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>estimated [L]</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Smaller units in the high case mean more pads</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Generator redundancy factor</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>factor</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>estimated [L]</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>N+1 to N+25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Generator pad volume</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>480</v>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>787.5</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>cf</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>estimated [L]</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>40x12x1 ft to 45x14x1.25 ft</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Transformer / switchgear pads per generator</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>estimated [L]</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Transformer / switchgear pad volume</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>562.5</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>cf</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>estimated [L]</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>20x15x1 ft to 25x18x1.25 ft</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Mechanical equipment pads as a share of floor area</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>estimated [L]</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Chillers, coolers, fan walls on grade or roof</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Mechanical pad thickness</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>estimated [L]</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Site paving, roads, yards, parking as a multiple of building footprint</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>estimated [L]</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Site paving thickness</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>estimated [L]</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Case 2: share of footprint over-excavated and replaced with lean concrete / CLSM</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>estimated [L]</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Case 2: lean concrete thickness</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>estimated [L]</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Case 2: enlargement of footings, grade beams and pads</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>factor</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>estimated [L]</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Case 3: piles or drilled piers per column</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>estimated [L]</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Case 3: pile diameter</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ft</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>estimated [L]</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Case 3: pile length</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>ft</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>estimated [L]</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Case 3: pile cap volume per column (replaces the spread footing)</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>cf</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>estimated [L]</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>10x10x3 ft to 12x12x3.5 ft</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Case 3: pier spacing under grade beams</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>ft</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>estimated [L]</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Case 3: slab thickening to a structural slab</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>estimated [L]</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Substation / transformer yard mats per GW</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>acres</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>estimated [L]</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Yard mat thickness</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>estimated [L]</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Steel emissions, global average (BF-BOF)</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>kg CO₂e/kg</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>published-class [M]</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Steel emissions, recycled (EAF)</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>kg CO₂e/kg</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>industry range [M]</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>SUPERWOOD manufacturing emissions</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>kg CO₂e/kg</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>internal, pre-LCA [L]</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Canva DCII deck; LCA under way, Prof. Ming Hu, Notre Dame</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>SUPERWOOD biogenic carbon stored</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>kg CO₂e/kg</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>internal, pre-LCA [L]</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Report separately; module C release under EN 15804</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
           <t>Interior finishes emissions (gypsum, wood, steel studs — mixed)</t>
         </is>
       </c>
-      <c r="B52" s="2" t="n">
+      <c r="B82" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C52" s="2" t="n">
+      <c r="C82" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>kg CO₂e/kg</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>estimated [L]</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>Used only for the interior finishes row</t>
         </is>
@@ -2333,11 +3094,11 @@
         </is>
       </c>
       <c r="B3" s="5">
-        <f>Inputs!$B$11*(1-Inputs!$B$33)*Inputs!$B$12*Inputs!$B$2-B5</f>
+        <f>IF(Inputs!$B$48=1,Foundations!B28,Inputs!$B$11*(1-Inputs!$B$33)*Inputs!$B$12*Inputs!$B$2)-B5</f>
         <v/>
       </c>
       <c r="C3" s="5">
-        <f>Inputs!$C$11*(1-Inputs!$C$33)*Inputs!$C$12*Inputs!$C$2-C5</f>
+        <f>IF(Inputs!$C$48=1,Foundations!C28,Inputs!$C$11*(1-Inputs!$C$33)*Inputs!$C$12*Inputs!$C$2)-C5</f>
         <v/>
       </c>
       <c r="D3" s="5">
@@ -2419,7 +3180,7 @@
         <v/>
       </c>
       <c r="X3" s="7">
-        <f>AC3*Inputs!$B$48+AD3*Inputs!$B$38+AE3*Inputs!$B$39</f>
+        <f>AC3*Inputs!$B$78+AD3*Inputs!$B$38+AE3*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="Y3" s="5">
@@ -2431,7 +3192,7 @@
         <v/>
       </c>
       <c r="AA3" s="7">
-        <f>AC3*Inputs!$C$49+AD3*Inputs!$B$38+AE3*Inputs!$B$39</f>
+        <f>AC3*Inputs!$C$79+AD3*Inputs!$B$38+AE3*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="AB3" t="inlineStr">
@@ -2459,11 +3220,11 @@
         </is>
       </c>
       <c r="B4" s="5">
-        <f>Inputs!$B$11*Inputs!$B$33*Inputs!$B$12*Inputs!$B$2</f>
+        <f>IF(Inputs!$B$48=1,Foundations!B29,Inputs!$B$11*Inputs!$B$33*Inputs!$B$12*Inputs!$B$2)</f>
         <v/>
       </c>
       <c r="C4" s="5">
-        <f>Inputs!$C$11*Inputs!$C$33*Inputs!$C$12*Inputs!$C$2</f>
+        <f>IF(Inputs!$C$48=1,Foundations!C29,Inputs!$C$11*Inputs!$C$33*Inputs!$C$12*Inputs!$C$2)</f>
         <v/>
       </c>
       <c r="D4" s="5">
@@ -2545,7 +3306,7 @@
         <v/>
       </c>
       <c r="X4" s="7">
-        <f>AC4*Inputs!$B$48+AD4*Inputs!$B$38+AE4*Inputs!$B$39</f>
+        <f>AC4*Inputs!$B$78+AD4*Inputs!$B$38+AE4*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="Y4" s="5">
@@ -2557,7 +3318,7 @@
         <v/>
       </c>
       <c r="AA4" s="7">
-        <f>AC4*Inputs!$C$49+AD4*Inputs!$B$38+AE4*Inputs!$B$39</f>
+        <f>AC4*Inputs!$C$79+AD4*Inputs!$B$38+AE4*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="AB4" t="inlineStr">
@@ -2670,7 +3431,7 @@
         <v/>
       </c>
       <c r="X5" s="7">
-        <f>AC5*Inputs!$B$48+AD5*Inputs!$B$38+AE5*Inputs!$B$39</f>
+        <f>AC5*Inputs!$B$78+AD5*Inputs!$B$38+AE5*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="Y5" s="5">
@@ -2682,7 +3443,7 @@
         <v/>
       </c>
       <c r="AA5" s="7">
-        <f>AC5*Inputs!$C$49+AD5*Inputs!$B$38+AE5*Inputs!$B$39</f>
+        <f>AC5*Inputs!$C$79+AD5*Inputs!$B$38+AE5*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2710,11 +3471,11 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>Inputs!$B$11*Inputs!$B$17/1000*Inputs!$B$2</f>
+        <f>IF(Inputs!$B$48=1,Foundations!B26+Foundations!B27,Inputs!$B$11*Inputs!$B$2)*Inputs!$B$17/1000</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>Inputs!$C$11*Inputs!$C$17/1000*Inputs!$C$2</f>
+        <f>IF(Inputs!$C$48=1,Foundations!C26+Foundations!C27,Inputs!$C$11*Inputs!$C$2)*Inputs!$C$17/1000</f>
         <v/>
       </c>
       <c r="D6" s="5">
@@ -2796,7 +3557,7 @@
         <v/>
       </c>
       <c r="X6" s="7">
-        <f>AC6*Inputs!$B$48+AD6*Inputs!$B$38+AE6*Inputs!$B$39</f>
+        <f>AC6*Inputs!$B$78+AD6*Inputs!$B$38+AE6*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="Y6" s="5">
@@ -2808,7 +3569,7 @@
         <v/>
       </c>
       <c r="AA6" s="7">
-        <f>AC6*Inputs!$C$49+AD6*Inputs!$B$38+AE6*Inputs!$B$39</f>
+        <f>AC6*Inputs!$C$79+AD6*Inputs!$B$38+AE6*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2921,7 +3682,7 @@
         <v/>
       </c>
       <c r="X7" s="7">
-        <f>AC7*Inputs!$B$48+AD7*Inputs!$B$38+AE7*Inputs!$B$39</f>
+        <f>AC7*Inputs!$B$78+AD7*Inputs!$B$38+AE7*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="Y7" s="5">
@@ -2933,7 +3694,7 @@
         <v/>
       </c>
       <c r="AA7" s="7">
-        <f>AC7*Inputs!$C$49+AD7*Inputs!$B$38+AE7*Inputs!$B$39</f>
+        <f>AC7*Inputs!$C$79+AD7*Inputs!$B$38+AE7*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3046,7 +3807,7 @@
         <v/>
       </c>
       <c r="X8" s="7">
-        <f>AC8*Inputs!$B$48+AD8*Inputs!$B$38+AE8*Inputs!$B$39</f>
+        <f>AC8*Inputs!$B$78+AD8*Inputs!$B$38+AE8*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="Y8" s="5">
@@ -3058,7 +3819,7 @@
         <v/>
       </c>
       <c r="AA8" s="7">
-        <f>AC8*Inputs!$C$49+AD8*Inputs!$B$38+AE8*Inputs!$B$39</f>
+        <f>AC8*Inputs!$C$79+AD8*Inputs!$B$38+AE8*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3171,7 +3932,7 @@
         <v/>
       </c>
       <c r="X9" s="7">
-        <f>AC9*Inputs!$B$48+AD9*Inputs!$B$38+AE9*Inputs!$B$39</f>
+        <f>AC9*Inputs!$B$78+AD9*Inputs!$B$38+AE9*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="Y9" s="5">
@@ -3183,7 +3944,7 @@
         <v/>
       </c>
       <c r="AA9" s="7">
-        <f>AC9*Inputs!$C$49+AD9*Inputs!$B$38+AE9*Inputs!$B$39</f>
+        <f>AC9*Inputs!$C$79+AD9*Inputs!$B$38+AE9*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3296,7 +4057,7 @@
         <v/>
       </c>
       <c r="X10" s="7">
-        <f>AC10*Inputs!$B$48+AD10*Inputs!$B$38+AE10*Inputs!$B$39</f>
+        <f>AC10*Inputs!$B$78+AD10*Inputs!$B$38+AE10*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="Y10" s="5">
@@ -3308,7 +4069,7 @@
         <v/>
       </c>
       <c r="AA10" s="7">
-        <f>AC10*Inputs!$C$49+AD10*Inputs!$B$38+AE10*Inputs!$B$39</f>
+        <f>AC10*Inputs!$C$79+AD10*Inputs!$B$38+AE10*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="AB10" t="inlineStr">
@@ -3421,7 +4182,7 @@
         <v/>
       </c>
       <c r="X11" s="7">
-        <f>AC11*Inputs!$B$48+AD11*Inputs!$B$38+AE11*Inputs!$B$39</f>
+        <f>AC11*Inputs!$B$78+AD11*Inputs!$B$38+AE11*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="Y11" s="5">
@@ -3433,7 +4194,7 @@
         <v/>
       </c>
       <c r="AA11" s="7">
-        <f>AC11*Inputs!$C$49+AD11*Inputs!$B$38+AE11*Inputs!$B$39</f>
+        <f>AC11*Inputs!$C$79+AD11*Inputs!$B$38+AE11*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="AB11" t="inlineStr">
@@ -3574,7 +4335,7 @@
         <v/>
       </c>
       <c r="X13" s="7">
-        <f>AC13*Inputs!$B$48+AD13*Inputs!$B$38+AE13*Inputs!$B$39</f>
+        <f>AC13*Inputs!$B$78+AD13*Inputs!$B$38+AE13*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="Y13" s="5">
@@ -3586,7 +4347,7 @@
         <v/>
       </c>
       <c r="AA13" s="7">
-        <f>AC13*Inputs!$C$49+AD13*Inputs!$B$38+AE13*Inputs!$B$39</f>
+        <f>AC13*Inputs!$C$79+AD13*Inputs!$B$38+AE13*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="AB13" t="inlineStr">
@@ -3699,7 +4460,7 @@
         <v/>
       </c>
       <c r="X14" s="7">
-        <f>AC14*Inputs!$B$48+AD14*Inputs!$B$38+AE14*Inputs!$B$39</f>
+        <f>AC14*Inputs!$B$78+AD14*Inputs!$B$38+AE14*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="Y14" s="5">
@@ -3711,7 +4472,7 @@
         <v/>
       </c>
       <c r="AA14" s="7">
-        <f>AC14*Inputs!$C$49+AD14*Inputs!$B$38+AE14*Inputs!$B$39</f>
+        <f>AC14*Inputs!$C$79+AD14*Inputs!$B$38+AE14*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="AB14" t="inlineStr">
@@ -3824,7 +4585,7 @@
         <v/>
       </c>
       <c r="X15" s="7">
-        <f>AC15*Inputs!$B$48+AD15*Inputs!$B$38+AE15*Inputs!$B$39</f>
+        <f>AC15*Inputs!$B$78+AD15*Inputs!$B$38+AE15*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="Y15" s="5">
@@ -3836,7 +4597,7 @@
         <v/>
       </c>
       <c r="AA15" s="7">
-        <f>AC15*Inputs!$C$49+AD15*Inputs!$B$38+AE15*Inputs!$B$39</f>
+        <f>AC15*Inputs!$C$79+AD15*Inputs!$B$38+AE15*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="AB15" t="inlineStr">
@@ -3950,7 +4711,7 @@
         <v/>
       </c>
       <c r="X16" s="7">
-        <f>AC16*Inputs!$B$48+AD16*Inputs!$B$38+AE16*Inputs!$B$39</f>
+        <f>AC16*Inputs!$B$78+AD16*Inputs!$B$38+AE16*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="Y16" s="5">
@@ -3962,7 +4723,7 @@
         <v/>
       </c>
       <c r="AA16" s="7">
-        <f>AC16*Inputs!$C$49+AD16*Inputs!$B$38+AE16*Inputs!$B$39</f>
+        <f>AC16*Inputs!$C$79+AD16*Inputs!$B$38+AE16*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="AB16" t="inlineStr">
@@ -4075,7 +4836,7 @@
         <v/>
       </c>
       <c r="X17" s="7">
-        <f>AC17*Inputs!$B$48+AD17*Inputs!$B$38+AE17*Inputs!$B$39</f>
+        <f>AC17*Inputs!$B$78+AD17*Inputs!$B$38+AE17*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="Y17" s="5">
@@ -4087,7 +4848,7 @@
         <v/>
       </c>
       <c r="AA17" s="7">
-        <f>AC17*Inputs!$C$49+AD17*Inputs!$B$38+AE17*Inputs!$B$39</f>
+        <f>AC17*Inputs!$C$79+AD17*Inputs!$B$38+AE17*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="AB17" t="inlineStr">
@@ -4200,7 +4961,7 @@
         <v/>
       </c>
       <c r="X18" s="7">
-        <f>AC18*Inputs!$B$48+AD18*Inputs!$B$38+AE18*Inputs!$B$39</f>
+        <f>AC18*Inputs!$B$78+AD18*Inputs!$B$38+AE18*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="Y18" s="5">
@@ -4212,7 +4973,7 @@
         <v/>
       </c>
       <c r="AA18" s="7">
-        <f>AC18*Inputs!$C$49+AD18*Inputs!$B$38+AE18*Inputs!$B$39</f>
+        <f>AC18*Inputs!$C$79+AD18*Inputs!$B$38+AE18*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="AB18" t="inlineStr">
@@ -4325,7 +5086,7 @@
         <v/>
       </c>
       <c r="X19" s="7">
-        <f>AC19*Inputs!$B$48+AD19*Inputs!$B$38+AE19*Inputs!$B$39</f>
+        <f>AC19*Inputs!$B$78+AD19*Inputs!$B$38+AE19*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="Y19" s="5">
@@ -4337,7 +5098,7 @@
         <v/>
       </c>
       <c r="AA19" s="7">
-        <f>AC19*Inputs!$C$49+AD19*Inputs!$B$38+AE19*Inputs!$B$39</f>
+        <f>AC19*Inputs!$C$79+AD19*Inputs!$B$38+AE19*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="AB19" t="inlineStr">
@@ -4452,7 +5213,7 @@
         <v/>
       </c>
       <c r="X20" s="7">
-        <f>AC20*Inputs!$B$48+AD20*Inputs!$B$38+AE20*Inputs!$B$39</f>
+        <f>AC20*Inputs!$B$78+AD20*Inputs!$B$38+AE20*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="Y20" s="5">
@@ -4464,7 +5225,7 @@
         <v/>
       </c>
       <c r="AA20" s="7">
-        <f>AC20*Inputs!$C$49+AD20*Inputs!$B$38+AE20*Inputs!$B$39</f>
+        <f>AC20*Inputs!$C$79+AD20*Inputs!$B$38+AE20*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="AB20" t="inlineStr">
@@ -4579,7 +5340,7 @@
         <v/>
       </c>
       <c r="X21" s="7">
-        <f>AC21*Inputs!$B$48+AD21*Inputs!$B$38+AE21*Inputs!$B$39</f>
+        <f>AC21*Inputs!$B$78+AD21*Inputs!$B$38+AE21*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="Y21" s="5">
@@ -4591,7 +5352,7 @@
         <v/>
       </c>
       <c r="AA21" s="7">
-        <f>AC21*Inputs!$C$49+AD21*Inputs!$B$38+AE21*Inputs!$B$39</f>
+        <f>AC21*Inputs!$C$79+AD21*Inputs!$B$38+AE21*Inputs!$B$39</f>
         <v/>
       </c>
       <c r="AB21" t="inlineStr">
@@ -5262,6 +6023,579 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Low  m³</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>High  m³</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Building floor area, sf</t>
+        </is>
+      </c>
+      <c r="B2" s="5">
+        <f>Inputs!$B$3*Inputs!$B$2</f>
+        <v/>
+      </c>
+      <c r="C2" s="5">
+        <f>Inputs!$C$3*Inputs!$C$2</f>
+        <v/>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>from Inputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Total hall perimeter, ft</t>
+        </is>
+      </c>
+      <c r="B3" s="5">
+        <f>Derived!B2*4*SQRT(Inputs!$B$4)</f>
+        <v/>
+      </c>
+      <c r="C3" s="5">
+        <f>Derived!C2*4*SQRT(Inputs!$C$4)</f>
+        <v/>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>buildings x 4 sides</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Columns</t>
+        </is>
+      </c>
+      <c r="B4" s="5">
+        <f>B2/(Inputs!$B$53^2)</f>
+        <v/>
+      </c>
+      <c r="C4" s="5">
+        <f>C2/(Inputs!$C$53^2)</f>
+        <v/>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>one per bay</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Hall slab on grade</t>
+        </is>
+      </c>
+      <c r="B5" s="5">
+        <f>B2*Inputs!$B$50/12*0.0283168</f>
+        <v/>
+      </c>
+      <c r="C5" s="5">
+        <f>C2*Inputs!$C$50/12*0.0283168</f>
+        <v/>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>6–8 in over the floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Thickened slab zones</t>
+        </is>
+      </c>
+      <c r="B6" s="5">
+        <f>B2*Inputs!$B$51*(Inputs!$B$52-Inputs!$B$50)/12*0.0283168</f>
+        <v/>
+      </c>
+      <c r="C6" s="5">
+        <f>C2*Inputs!$C$51*(Inputs!$C$52-Inputs!$C$50)/12*0.0283168</f>
+        <v/>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>extra depth over 15–25% of the floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Column footings</t>
+        </is>
+      </c>
+      <c r="B7" s="5">
+        <f>B4*Inputs!$B$54^2*Inputs!$B$55*0.0283168</f>
+        <v/>
+      </c>
+      <c r="C7" s="5">
+        <f>C4*Inputs!$C$54^2*Inputs!$C$55*0.0283168</f>
+        <v/>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>spread footings, good soils</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Perimeter grade beams</t>
+        </is>
+      </c>
+      <c r="B8" s="5">
+        <f>B3*Inputs!$B$56*Inputs!$B$57*0.0283168</f>
+        <v/>
+      </c>
+      <c r="C8" s="5">
+        <f>C3*Inputs!$C$56*Inputs!$C$57*0.0283168</f>
+        <v/>
+      </c>
+      <c r="D8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Generators</t>
+        </is>
+      </c>
+      <c r="B9" s="5">
+        <f>Inputs!$B$2/Inputs!$B$58*Inputs!$B$59</f>
+        <v/>
+      </c>
+      <c r="C9" s="5">
+        <f>Inputs!$C$2/Inputs!$C$58*Inputs!$C$59</f>
+        <v/>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>units incl. redundancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Generator pads</t>
+        </is>
+      </c>
+      <c r="B10" s="5">
+        <f>B9*Inputs!$B$60*0.0283168</f>
+        <v/>
+      </c>
+      <c r="C10" s="5">
+        <f>C9*Inputs!$C$60*0.0283168</f>
+        <v/>
+      </c>
+      <c r="D10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Transformer and switchgear pads</t>
+        </is>
+      </c>
+      <c r="B11" s="5">
+        <f>B9*Inputs!$B$61*Inputs!$B$62*0.0283168</f>
+        <v/>
+      </c>
+      <c r="C11" s="5">
+        <f>C9*Inputs!$C$61*Inputs!$C$62*0.0283168</f>
+        <v/>
+      </c>
+      <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Mechanical equipment pads</t>
+        </is>
+      </c>
+      <c r="B12" s="5">
+        <f>B2*Inputs!$B$63*Inputs!$B$64/12*0.0283168</f>
+        <v/>
+      </c>
+      <c r="C12" s="5">
+        <f>C2*Inputs!$C$63*Inputs!$C$64/12*0.0283168</f>
+        <v/>
+      </c>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Case 1 good soils — building and pads</t>
+        </is>
+      </c>
+      <c r="B13" s="5">
+        <f>B5+B6+B7+B8+B10+B11+B12</f>
+        <v/>
+      </c>
+      <c r="C13" s="5">
+        <f>C5+C6+C7+C8+C10+C11+C12</f>
+        <v/>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>sum</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Case 2 — lean concrete / CLSM under footprint</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>B2*Inputs!$B$67*Inputs!$B$68/12*0.0283168</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>C2*Inputs!$C$67*Inputs!$C$68/12*0.0283168</f>
+        <v/>
+      </c>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Case 2 — larger footings, grade beams and pads</t>
+        </is>
+      </c>
+      <c r="B15" s="5">
+        <f>(B7+B8+B10+B11+B12)*Inputs!$B$69</f>
+        <v/>
+      </c>
+      <c r="C15" s="5">
+        <f>(C7+C8+C10+C11+C12)*Inputs!$C$69</f>
+        <v/>
+      </c>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Case 2 moderate soils — allowance</t>
+        </is>
+      </c>
+      <c r="B16" s="5">
+        <f>B14+B15</f>
+        <v/>
+      </c>
+      <c r="C16" s="5">
+        <f>C14+C15</f>
+        <v/>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>added to case 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Case 3 — piles or drilled piers under columns</t>
+        </is>
+      </c>
+      <c r="B17" s="5">
+        <f>B4*Inputs!$B$70*PI()*(Inputs!$B$71/2)^2*Inputs!$B$72*0.0283168</f>
+        <v/>
+      </c>
+      <c r="C17" s="5">
+        <f>C4*Inputs!$C$70*PI()*(Inputs!$C$71/2)^2*Inputs!$C$72*0.0283168</f>
+        <v/>
+      </c>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Case 3 — pile caps net of spread footings</t>
+        </is>
+      </c>
+      <c r="B18" s="5">
+        <f>B4*Inputs!$B$73*0.0283168-B7</f>
+        <v/>
+      </c>
+      <c r="C18" s="5">
+        <f>C4*Inputs!$C$73*0.0283168-C7</f>
+        <v/>
+      </c>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Case 3 — piers under grade beams</t>
+        </is>
+      </c>
+      <c r="B19" s="5">
+        <f>B3/Inputs!$B$74*PI()*(Inputs!$B$71/2)^2*Inputs!$B$72*0.0283168</f>
+        <v/>
+      </c>
+      <c r="C19" s="5">
+        <f>C3/Inputs!$C$74*PI()*(Inputs!$C$71/2)^2*Inputs!$C$72*0.0283168</f>
+        <v/>
+      </c>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Case 3 — structural slab thickening</t>
+        </is>
+      </c>
+      <c r="B20" s="5">
+        <f>B2*Inputs!$B$75/12*0.0283168</f>
+        <v/>
+      </c>
+      <c r="C20" s="5">
+        <f>C2*Inputs!$C$75/12*0.0283168</f>
+        <v/>
+      </c>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>Case 3 poor soils — allowance</t>
+        </is>
+      </c>
+      <c r="B21" s="5">
+        <f>B17+B18+B19+B20</f>
+        <v/>
+      </c>
+      <c r="C21" s="5">
+        <f>C17+C18+C19+C20</f>
+        <v/>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>added to case 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Selected soil allowance</t>
+        </is>
+      </c>
+      <c r="B22" s="5">
+        <f>CHOOSE(Inputs!$B$49,0,B16,B21)</f>
+        <v/>
+      </c>
+      <c r="C22" s="5">
+        <f>CHOOSE(Inputs!$C$49,0,C16,C21)</f>
+        <v/>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Inputs soil_case</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Site paving, roads, yards, parking</t>
+        </is>
+      </c>
+      <c r="B23" s="5">
+        <f>B2*Inputs!$B$65*Inputs!$B$66/12*0.0283168</f>
+        <v/>
+      </c>
+      <c r="C23" s="5">
+        <f>C2*Inputs!$C$65*Inputs!$C$66/12*0.0283168</f>
+        <v/>
+      </c>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Substation / transformer yard mats</t>
+        </is>
+      </c>
+      <c r="B24" s="5">
+        <f>Inputs!$B$76*Inputs!$B$2/1000*43560*Inputs!$B$77/12*0.0283168</f>
+        <v/>
+      </c>
+      <c r="C24" s="5">
+        <f>Inputs!$C$76*Inputs!$C$2/1000*43560*Inputs!$C$77/12*0.0283168</f>
+        <v/>
+      </c>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>All-in with site work, selected soil case</t>
+        </is>
+      </c>
+      <c r="B25" s="5">
+        <f>B13+B22+B23+B24</f>
+        <v/>
+      </c>
+      <c r="C25" s="5">
+        <f>C13+C22+C23+C24</f>
+        <v/>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>sum</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Slab and paving, footprint basis (m³)</t>
+        </is>
+      </c>
+      <c r="B26" s="5">
+        <f>B5+B6+B23+IF(Inputs!$B$49=3,B20,0)</f>
+        <v/>
+      </c>
+      <c r="C26" s="5">
+        <f>C5+C6+C23+IF(Inputs!$C$49=3,C20,0)</f>
+        <v/>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>feeds the main sheet when concrete_basis = 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Foundations, footings and pads, footprint basis (m³)</t>
+        </is>
+      </c>
+      <c r="B27" s="5">
+        <f>B7+B8+B10+B11+B12+B24+IF(Inputs!$B$49=2,B16,IF(Inputs!$B$49=3,B17+B18+B19,0))</f>
+        <v/>
+      </c>
+      <c r="C27" s="5">
+        <f>C7+C8+C10+C11+C12+C24+IF(Inputs!$C$49=2,C16,IF(Inputs!$C$49=3,C17+C18+C19,0))</f>
+        <v/>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>feeds the main sheet when concrete_basis = 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>Slab and paving, footprint basis (t)</t>
+        </is>
+      </c>
+      <c r="B28" s="5">
+        <f>B26*Inputs!$B$12</f>
+        <v/>
+      </c>
+      <c r="C28" s="5">
+        <f>C26*Inputs!$C$12</f>
+        <v/>
+      </c>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>Foundations, footings and pads, footprint basis (t)</t>
+        </is>
+      </c>
+      <c r="B29" s="5">
+        <f>B27*Inputs!$B$12</f>
+        <v/>
+      </c>
+      <c r="C29" s="5">
+        <f>C27*Inputs!$C$12</f>
+        <v/>
+      </c>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Per-MW basis for comparison (m³)</t>
+        </is>
+      </c>
+      <c r="B30" s="5">
+        <f>Inputs!$B$11*Inputs!$B$2</f>
+        <v/>
+      </c>
+      <c r="C30" s="5">
+        <f>Inputs!$C$11*Inputs!$C$2</f>
+        <v/>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>published, secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Wall system: tilt-up versus insulated metal panel is the Inputs walls_precast switch (precast row on the main sheet, steel-share sheet reports both). Soil cases and the concrete basis switch are Inputs soil_case and concrete_basis. All element inputs are estimates [L]; see foundation-bottom-up.md.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -5350,11 +6684,11 @@
         <v/>
       </c>
       <c r="D2" s="4">
-        <f>'1 GW data center'!B29*Inputs!$B$50</f>
+        <f>'1 GW data center'!B29*Inputs!$B$80</f>
         <v/>
       </c>
       <c r="E2" s="4">
-        <f>'1 GW data center'!C29*Inputs!$C$50</f>
+        <f>'1 GW data center'!C29*Inputs!$C$80</f>
         <v/>
       </c>
       <c r="F2" s="4">
@@ -5374,11 +6708,11 @@
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>'1 GW data center'!B29*Inputs!$B$51</f>
+        <f>'1 GW data center'!B29*Inputs!$B$81</f>
         <v/>
       </c>
       <c r="K2" s="4">
-        <f>'1 GW data center'!C29*Inputs!$C$51</f>
+        <f>'1 GW data center'!C29*Inputs!$C$81</f>
         <v/>
       </c>
     </row>
@@ -5397,11 +6731,11 @@
         <v/>
       </c>
       <c r="D3" s="4">
-        <f>'1 GW data center'!B34*Inputs!$B$50</f>
+        <f>'1 GW data center'!B34*Inputs!$B$80</f>
         <v/>
       </c>
       <c r="E3" s="4">
-        <f>'1 GW data center'!C34*Inputs!$C$50</f>
+        <f>'1 GW data center'!C34*Inputs!$C$80</f>
         <v/>
       </c>
       <c r="F3" s="4">
@@ -5421,11 +6755,11 @@
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>'1 GW data center'!B34*Inputs!$B$51</f>
+        <f>'1 GW data center'!B34*Inputs!$B$81</f>
         <v/>
       </c>
       <c r="K3" s="4">
-        <f>'1 GW data center'!C34*Inputs!$C$51</f>
+        <f>'1 GW data center'!C34*Inputs!$C$81</f>
         <v/>
       </c>
     </row>
@@ -5444,11 +6778,11 @@
         <v/>
       </c>
       <c r="D4" s="4">
-        <f>'1 GW data center'!B38*Inputs!$B$50</f>
+        <f>'1 GW data center'!B38*Inputs!$B$80</f>
         <v/>
       </c>
       <c r="E4" s="4">
-        <f>'1 GW data center'!C38*Inputs!$C$50</f>
+        <f>'1 GW data center'!C38*Inputs!$C$80</f>
         <v/>
       </c>
       <c r="F4" s="4">
@@ -5468,11 +6802,11 @@
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>'1 GW data center'!B38*Inputs!$B$51</f>
+        <f>'1 GW data center'!B38*Inputs!$B$81</f>
         <v/>
       </c>
       <c r="K4" s="4">
-        <f>'1 GW data center'!C38*Inputs!$C$51</f>
+        <f>'1 GW data center'!C38*Inputs!$C$81</f>
         <v/>
       </c>
     </row>
@@ -5491,11 +6825,11 @@
         <v/>
       </c>
       <c r="D5" s="4">
-        <f>'1 GW data center'!B42*Inputs!$B$50</f>
+        <f>'1 GW data center'!B42*Inputs!$B$80</f>
         <v/>
       </c>
       <c r="E5" s="4">
-        <f>'1 GW data center'!C42*Inputs!$C$50</f>
+        <f>'1 GW data center'!C42*Inputs!$C$80</f>
         <v/>
       </c>
       <c r="F5" s="4">
@@ -5515,11 +6849,11 @@
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>'1 GW data center'!B42*Inputs!$B$51</f>
+        <f>'1 GW data center'!B42*Inputs!$B$81</f>
         <v/>
       </c>
       <c r="K5" s="4">
-        <f>'1 GW data center'!C42*Inputs!$C$51</f>
+        <f>'1 GW data center'!C42*Inputs!$C$81</f>
         <v/>
       </c>
     </row>
@@ -5535,7 +6869,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/superwood-datacenter-investor/analyses/materials-mass-and-replacement.xlsx
+++ b/superwood-datacenter-investor/analyses/materials-mass-and-replacement.xlsx
@@ -1968,10 +1968,10 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Scenario switch, added 2026-09-06; the deck prints the per-MW basis until Alex decides</t>
+          <t>Deck default since 2026-09-06 (Alex): footprint basis</t>
         </is>
       </c>
     </row>
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Geotechnical allowance, Foundations sheet</t>
+          <t>Deck default since 2026-09-06 (Alex): moderate soils; the web deck has a soils slider</t>
         </is>
       </c>
     </row>

--- a/superwood-datacenter-investor/analyses/materials-mass-and-replacement.xlsx
+++ b/superwood-datacenter-investor/analyses/materials-mass-and-replacement.xlsx
@@ -6397,20 +6397,20 @@
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>Case 3 poor soils — allowance</t>
+          <t>Case 3 poor soils — allowance (includes the case 2 measures)</t>
         </is>
       </c>
       <c r="B21" s="5">
-        <f>B17+B18+B19+B20</f>
+        <f>B16+B17+B18+B19+B20</f>
         <v/>
       </c>
       <c r="C21" s="5">
-        <f>C17+C18+C19+C20</f>
+        <f>C16+C17+C18+C19+C20</f>
         <v/>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>added to case 1</t>
+          <t>nested: ground replacement and larger elements plus piles, caps, piers and a structural slab</t>
         </is>
       </c>
     </row>
@@ -6513,16 +6513,16 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>B7+B8+B10+B11+B12+B24+IF(Inputs!$B$49=2,B16,IF(Inputs!$B$49=3,B17+B18+B19,0))</f>
+        <f>B7+B8+B10+B11+B12+B24+IF(Inputs!$B$49&gt;=2,B16,0)+IF(Inputs!$B$49=3,B17+B18+B19,0)</f>
         <v/>
       </c>
       <c r="C27" s="5">
-        <f>C7+C8+C10+C11+C12+C24+IF(Inputs!$C$49=2,C16,IF(Inputs!$C$49=3,C17+C18+C19,0))</f>
+        <f>C7+C8+C10+C11+C12+C24+IF(Inputs!$C$49&gt;=2,C16,0)+IF(Inputs!$C$49=3,C17+C18+C19,0)</f>
         <v/>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>feeds the main sheet when concrete_basis = 1</t>
+          <t>feeds the main sheet when concrete_basis = 1; soil cases nest</t>
         </is>
       </c>
     </row>
